--- a/fnot.xlsx
+++ b/fnot.xlsx
@@ -470,7 +470,7 @@
         <v>1.63</v>
       </c>
       <c r="I2" s="1">
-        <v>7968718</v>
+        <v>7970096</v>
       </c>
       <c r="J2" s="1">
         <v>523.28</v>
@@ -511,7 +511,7 @@
         <v>-30.86</v>
       </c>
       <c r="I3" s="1">
-        <v>3975439</v>
+        <v>3975991</v>
       </c>
       <c r="J3" s="1">
         <v>4208.93</v>
@@ -552,7 +552,7 @@
         <v>32.77</v>
       </c>
       <c r="I4" s="1">
-        <v>3847622</v>
+        <v>3848670</v>
       </c>
       <c r="J4" s="1">
         <v>1295.5</v>
@@ -593,7 +593,7 @@
         <v>36.48</v>
       </c>
       <c r="I5" s="1">
-        <v>36210036</v>
+        <v>36213929</v>
       </c>
       <c r="J5" s="1">
         <v>189.13</v>
@@ -634,7 +634,7 @@
         <v>61.42</v>
       </c>
       <c r="I6" s="1">
-        <v>37015484</v>
+        <v>37021888</v>
       </c>
       <c r="J6" s="1">
         <v>352.7</v>
@@ -675,7 +675,7 @@
         <v>-31.48</v>
       </c>
       <c r="I7" s="1">
-        <v>582126</v>
+        <v>582137</v>
       </c>
       <c r="J7" s="1">
         <v>2820</v>
@@ -716,7 +716,7 @@
         <v>7.39</v>
       </c>
       <c r="I8" s="1">
-        <v>3909498</v>
+        <v>3910166</v>
       </c>
       <c r="J8" s="1">
         <v>1365.1</v>
@@ -757,7 +757,7 @@
         <v>-19.46</v>
       </c>
       <c r="I9" s="1">
-        <v>51882978</v>
+        <v>51925581</v>
       </c>
       <c r="J9" s="1">
         <v>135.25</v>
@@ -798,7 +798,7 @@
         <v>-21.41</v>
       </c>
       <c r="I10" s="1">
-        <v>1782262</v>
+        <v>1782282</v>
       </c>
       <c r="J10" s="1">
         <v>1252.42</v>
@@ -839,7 +839,7 @@
         <v>-31.88</v>
       </c>
       <c r="I11" s="1">
-        <v>3118282</v>
+        <v>3118394</v>
       </c>
       <c r="J11" s="1">
         <v>633.38</v>
@@ -880,7 +880,7 @@
         <v>-17.12</v>
       </c>
       <c r="I12" s="1">
-        <v>2889529</v>
+        <v>2889530</v>
       </c>
       <c r="J12" s="1">
         <v>1105.23</v>
@@ -921,7 +921,7 @@
         <v>7.55</v>
       </c>
       <c r="I13" s="1">
-        <v>360165</v>
+        <v>360218</v>
       </c>
       <c r="J13" s="1">
         <v>3577.4</v>
@@ -962,7 +962,7 @@
         <v>-12.44</v>
       </c>
       <c r="I14" s="1">
-        <v>25889401</v>
+        <v>25901686</v>
       </c>
       <c r="J14" s="1">
         <v>43.82</v>
@@ -1003,7 +1003,7 @@
         <v>-15.23</v>
       </c>
       <c r="I15" s="1">
-        <v>1107107</v>
+        <v>1107761</v>
       </c>
       <c r="J15" s="1">
         <v>2861.06</v>
@@ -1044,7 +1044,7 @@
         <v>-18.29</v>
       </c>
       <c r="I16" s="1">
-        <v>285160</v>
+        <v>285355</v>
       </c>
       <c r="J16" s="1">
         <v>5512.33</v>
@@ -1085,7 +1085,7 @@
         <v>-22.88</v>
       </c>
       <c r="I17" s="1">
-        <v>2163580</v>
+        <v>2164345</v>
       </c>
       <c r="J17" s="1">
         <v>444.75</v>
@@ -1105,37 +1105,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Infosys Limited</v>
+        <v>Adani Green Energy Ltd</v>
       </c>
       <c r="C18" t="str">
-        <v>INFY</v>
+        <v>ADANIGREEN</v>
       </c>
       <c r="D18" s="1">
-        <v>1088</v>
+        <v>1318.4</v>
       </c>
       <c r="E18" s="2">
         <v>2.44</v>
       </c>
       <c r="F18" s="2">
-        <v>6.31</v>
+        <v>4.98</v>
       </c>
       <c r="G18" s="2">
-        <v>9.45</v>
+        <v>3.16</v>
       </c>
       <c r="H18" s="2">
-        <v>-32.65</v>
+        <v>29.88</v>
       </c>
       <c r="I18" s="1">
-        <v>21158848</v>
+        <v>1762304</v>
       </c>
       <c r="J18" s="1">
-        <v>1242.01</v>
+        <v>1206.83</v>
       </c>
       <c r="K18" s="1">
-        <v>1035.7</v>
+        <v>1287.04</v>
       </c>
       <c r="L18" s="1">
-        <v>1088.67</v>
+        <v>1303.74</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1146,37 +1146,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>Tata Power Company Limited</v>
+        <v>Infosys Limited</v>
       </c>
       <c r="C19" t="str">
-        <v>TATAPOWER</v>
+        <v>INFY</v>
       </c>
       <c r="D19" s="1">
-        <v>353</v>
+        <v>1088</v>
       </c>
       <c r="E19" s="2">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="F19" s="2">
-        <v>3.17</v>
+        <v>6.31</v>
       </c>
       <c r="G19" s="2">
-        <v>-1.67</v>
+        <v>9.45</v>
       </c>
       <c r="H19" s="2">
-        <v>-7.01</v>
+        <v>-32.65</v>
       </c>
       <c r="I19" s="1">
-        <v>4880805</v>
+        <v>21163501</v>
       </c>
       <c r="J19" s="1">
-        <v>384.65</v>
+        <v>1242.01</v>
       </c>
       <c r="K19" s="1">
-        <v>349.16</v>
+        <v>1035.7</v>
       </c>
       <c r="L19" s="1">
-        <v>365.17</v>
+        <v>1088.67</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1187,37 +1187,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>Crompton Greaves Consumer Electricals Limited</v>
+        <v>Tata Power Company Limited</v>
       </c>
       <c r="C20" t="str">
-        <v>CROMPTON</v>
+        <v>TATAPOWER</v>
       </c>
       <c r="D20" s="1">
-        <v>216</v>
+        <v>353</v>
       </c>
       <c r="E20" s="2">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="F20" s="2">
-        <v>5.31</v>
+        <v>3.17</v>
       </c>
       <c r="G20" s="2">
-        <v>3.51</v>
+        <v>-1.67</v>
       </c>
       <c r="H20" s="2">
-        <v>-14.37</v>
+        <v>-7.01</v>
       </c>
       <c r="I20" s="1">
-        <v>8016255</v>
+        <v>4881043</v>
       </c>
       <c r="J20" s="1">
-        <v>251.99</v>
+        <v>384.65</v>
       </c>
       <c r="K20" s="1">
-        <v>210.83</v>
+        <v>349.16</v>
       </c>
       <c r="L20" s="1">
-        <v>231.23</v>
+        <v>365.17</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -1228,37 +1228,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>Adani Green Energy Ltd</v>
+        <v>Crompton Greaves Consumer Electricals Limited</v>
       </c>
       <c r="C21" t="str">
-        <v>ADANIGREEN</v>
+        <v>CROMPTON</v>
       </c>
       <c r="D21" s="1">
-        <v>1314</v>
+        <v>216</v>
       </c>
       <c r="E21" s="2">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="F21" s="2">
-        <v>4.63</v>
+        <v>5.31</v>
       </c>
       <c r="G21" s="2">
-        <v>2.82</v>
+        <v>3.51</v>
       </c>
       <c r="H21" s="2">
-        <v>29.45</v>
+        <v>-14.37</v>
       </c>
       <c r="I21" s="1">
-        <v>1761460</v>
+        <v>8016330</v>
       </c>
       <c r="J21" s="1">
-        <v>1206.81</v>
+        <v>251.99</v>
       </c>
       <c r="K21" s="1">
-        <v>1286.24</v>
+        <v>210.83</v>
       </c>
       <c r="L21" s="1">
-        <v>1303.65</v>
+        <v>231.23</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -1275,28 +1275,28 @@
         <v>COALINDIA</v>
       </c>
       <c r="D22" s="1">
-        <v>416.9</v>
+        <v>417</v>
       </c>
       <c r="E22" s="2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="F22" s="2">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="G22" s="2">
-        <v>-1.91</v>
+        <v>-1.88</v>
       </c>
       <c r="H22" s="2">
-        <v>4.49</v>
+        <v>4.51</v>
       </c>
       <c r="I22" s="1">
-        <v>6907400</v>
+        <v>6909445</v>
       </c>
       <c r="J22" s="1">
         <v>433.82</v>
       </c>
       <c r="K22" s="1">
-        <v>414.06</v>
+        <v>414.08</v>
       </c>
       <c r="L22" s="1">
         <v>414.36</v>
@@ -1331,7 +1331,7 @@
         <v>-0.99</v>
       </c>
       <c r="I23" s="1">
-        <v>3512921</v>
+        <v>3513499</v>
       </c>
       <c r="J23" s="1">
         <v>1516.69</v>
@@ -1372,7 +1372,7 @@
         <v>-55.33</v>
       </c>
       <c r="I24" s="1">
-        <v>4933202</v>
+        <v>4933354</v>
       </c>
       <c r="J24" s="1">
         <v>738.81</v>
@@ -1413,7 +1413,7 @@
         <v>9.6</v>
       </c>
       <c r="I25" s="1">
-        <v>1306957</v>
+        <v>1308525</v>
       </c>
       <c r="J25" s="1">
         <v>931.58</v>
@@ -1454,7 +1454,7 @@
         <v>-1.85</v>
       </c>
       <c r="I26" s="1">
-        <v>93212306</v>
+        <v>93238252</v>
       </c>
       <c r="J26" s="1">
         <v>21.81</v>
@@ -1495,7 +1495,7 @@
         <v>-4.11</v>
       </c>
       <c r="I27" s="1">
-        <v>20988628</v>
+        <v>20998325</v>
       </c>
       <c r="J27" s="1">
         <v>114.25</v>
@@ -1536,7 +1536,7 @@
         <v>-28.11</v>
       </c>
       <c r="I28" s="1">
-        <v>11902416</v>
+        <v>11902735</v>
       </c>
       <c r="J28" s="1">
         <v>2474.47</v>
@@ -1577,7 +1577,7 @@
         <v>-12.61</v>
       </c>
       <c r="I29" s="1">
-        <v>9217025</v>
+        <v>9217475</v>
       </c>
       <c r="J29" s="1">
         <v>345.57</v>
@@ -1618,7 +1618,7 @@
         <v>-22.54</v>
       </c>
       <c r="I30" s="1">
-        <v>64545864</v>
+        <v>64619403</v>
       </c>
       <c r="J30" s="1">
         <v>48.61</v>
@@ -1659,7 +1659,7 @@
         <v>-19.54</v>
       </c>
       <c r="I31" s="1">
-        <v>5049152</v>
+        <v>5056005</v>
       </c>
       <c r="J31" s="1">
         <v>124.18</v>
@@ -1700,7 +1700,7 @@
         <v>-12.01</v>
       </c>
       <c r="I32" s="1">
-        <v>416192</v>
+        <v>416566</v>
       </c>
       <c r="J32" s="1">
         <v>2024.51</v>
@@ -1741,7 +1741,7 @@
         <v>-23.22</v>
       </c>
       <c r="I33" s="1">
-        <v>6462207</v>
+        <v>6464877</v>
       </c>
       <c r="J33" s="1">
         <v>147.25</v>
@@ -1782,7 +1782,7 @@
         <v>12.4</v>
       </c>
       <c r="I34" s="1">
-        <v>686852</v>
+        <v>686891</v>
       </c>
       <c r="J34" s="1">
         <v>4426.83</v>
@@ -1823,7 +1823,7 @@
         <v>-6.19</v>
       </c>
       <c r="I35" s="1">
-        <v>8917996</v>
+        <v>8918599</v>
       </c>
       <c r="J35" s="1">
         <v>256.04</v>
@@ -1864,7 +1864,7 @@
         <v>23.54</v>
       </c>
       <c r="I36" s="1">
-        <v>436423</v>
+        <v>436885</v>
       </c>
       <c r="J36" s="1">
         <v>3092.67</v>
@@ -1905,7 +1905,7 @@
         <v>-12.7</v>
       </c>
       <c r="I37" s="1">
-        <v>1659207</v>
+        <v>1659363</v>
       </c>
       <c r="J37" s="1">
         <v>1756.67</v>
@@ -1946,7 +1946,7 @@
         <v>-6.74</v>
       </c>
       <c r="I38" s="1">
-        <v>457695</v>
+        <v>457745</v>
       </c>
       <c r="J38" s="1">
         <v>1689.77</v>
@@ -1987,7 +1987,7 @@
         <v>-15.06</v>
       </c>
       <c r="I39" s="1">
-        <v>1230255</v>
+        <v>1230336</v>
       </c>
       <c r="J39" s="1">
         <v>2725.65</v>
@@ -2028,7 +2028,7 @@
         <v>-35.08</v>
       </c>
       <c r="I40" s="1">
-        <v>12033136</v>
+        <v>12049195</v>
       </c>
       <c r="J40" s="1">
         <v>197.78</v>
@@ -2069,7 +2069,7 @@
         <v>-18.15</v>
       </c>
       <c r="I41" s="1">
-        <v>3379764</v>
+        <v>3459784</v>
       </c>
       <c r="J41" s="1">
         <v>2169.44</v>
@@ -2110,7 +2110,7 @@
         <v>33.2</v>
       </c>
       <c r="I42" s="1">
-        <v>1625211</v>
+        <v>1626664</v>
       </c>
       <c r="J42" s="1">
         <v>801.23</v>
@@ -2151,7 +2151,7 @@
         <v>13.16</v>
       </c>
       <c r="I43" s="1">
-        <v>23275345</v>
+        <v>23275384</v>
       </c>
       <c r="J43" s="1">
         <v>174.86</v>
@@ -2192,7 +2192,7 @@
         <v>21.56</v>
       </c>
       <c r="I44" s="1">
-        <v>1386679</v>
+        <v>1386775</v>
       </c>
       <c r="J44" s="1">
         <v>2585.54</v>
@@ -2233,7 +2233,7 @@
         <v>3.12</v>
       </c>
       <c r="I45" s="1">
-        <v>2612548</v>
+        <v>2612579</v>
       </c>
       <c r="J45" s="1">
         <v>282.14</v>
@@ -2274,7 +2274,7 @@
         <v>-9.71</v>
       </c>
       <c r="I46" s="1">
-        <v>603230</v>
+        <v>603244</v>
       </c>
       <c r="J46" s="1">
         <v>3983.55</v>
@@ -2315,7 +2315,7 @@
         <v>1.46</v>
       </c>
       <c r="I47" s="1">
-        <v>1405403</v>
+        <v>1406320</v>
       </c>
       <c r="J47" s="1">
         <v>863.38</v>
@@ -2356,7 +2356,7 @@
         <v>5.25</v>
       </c>
       <c r="I48" s="1">
-        <v>2424666</v>
+        <v>2424721</v>
       </c>
       <c r="J48" s="1">
         <v>799.66</v>
@@ -2397,7 +2397,7 @@
         <v>-4.81</v>
       </c>
       <c r="I49" s="1">
-        <v>11150008</v>
+        <v>11151036</v>
       </c>
       <c r="J49" s="1">
         <v>357.22</v>
@@ -2438,7 +2438,7 @@
         <v>36.05</v>
       </c>
       <c r="I50" s="1">
-        <v>171486</v>
+        <v>171493</v>
       </c>
       <c r="J50" s="1">
         <v>1826.91</v>
@@ -2479,7 +2479,7 @@
         <v>0.5</v>
       </c>
       <c r="I51" s="1">
-        <v>1702213</v>
+        <v>1702464</v>
       </c>
       <c r="J51" s="1">
         <v>1005.82</v>
@@ -2520,7 +2520,7 @@
         <v>-24.57</v>
       </c>
       <c r="I52" s="1">
-        <v>3209008</v>
+        <v>3215810</v>
       </c>
       <c r="J52" s="1">
         <v>321.7</v>
@@ -2561,7 +2561,7 @@
         <v>-4.3</v>
       </c>
       <c r="I53" s="1">
-        <v>1141268</v>
+        <v>1141565</v>
       </c>
       <c r="J53" s="1">
         <v>1371.54</v>
@@ -2602,7 +2602,7 @@
         <v>-3.07</v>
       </c>
       <c r="I54" s="1">
-        <v>10073666</v>
+        <v>10073815</v>
       </c>
       <c r="J54" s="1">
         <v>399.39</v>
@@ -2643,7 +2643,7 @@
         <v>-25.2</v>
       </c>
       <c r="I55" s="1">
-        <v>10308148</v>
+        <v>10312209</v>
       </c>
       <c r="J55" s="1">
         <v>1348.77</v>
@@ -2684,7 +2684,7 @@
         <v>2.82</v>
       </c>
       <c r="I56" s="1">
-        <v>5009056</v>
+        <v>5010158</v>
       </c>
       <c r="J56" s="1">
         <v>372.69</v>
@@ -2725,7 +2725,7 @@
         <v>5.93</v>
       </c>
       <c r="I57" s="1">
-        <v>143603</v>
+        <v>143611</v>
       </c>
       <c r="J57" s="1">
         <v>12095.45</v>
@@ -2766,7 +2766,7 @@
         <v>5.51</v>
       </c>
       <c r="I58" s="1">
-        <v>2351478</v>
+        <v>2351569</v>
       </c>
       <c r="J58" s="1">
         <v>462.25</v>
@@ -2807,7 +2807,7 @@
         <v>-4.32</v>
       </c>
       <c r="I59" s="1">
-        <v>9033173</v>
+        <v>9049553</v>
       </c>
       <c r="J59" s="1">
         <v>417.4</v>
@@ -2848,7 +2848,7 @@
         <v>-33.66</v>
       </c>
       <c r="I60" s="1">
-        <v>3132153</v>
+        <v>3132438</v>
       </c>
       <c r="J60" s="1">
         <v>392.69</v>
@@ -2930,7 +2930,7 @@
         <v>-16.03</v>
       </c>
       <c r="I62" s="1">
-        <v>36744</v>
+        <v>36747</v>
       </c>
       <c r="J62" s="1">
         <v>19533.53</v>
@@ -2971,7 +2971,7 @@
         <v>-25.75</v>
       </c>
       <c r="I63" s="1">
-        <v>12306303</v>
+        <v>12311886</v>
       </c>
       <c r="J63" s="1">
         <v>246.09</v>
@@ -3012,7 +3012,7 @@
         <v>9.4</v>
       </c>
       <c r="I64" s="1">
-        <v>1129205</v>
+        <v>1129741</v>
       </c>
       <c r="J64" s="1">
         <v>8418.46</v>
@@ -3053,7 +3053,7 @@
         <v>-32.66</v>
       </c>
       <c r="I65" s="1">
-        <v>173570</v>
+        <v>173618</v>
       </c>
       <c r="J65" s="1">
         <v>2141.11</v>
@@ -3094,7 +3094,7 @@
         <v>68.34</v>
       </c>
       <c r="I66" s="1">
-        <v>3196503</v>
+        <v>3196745</v>
       </c>
       <c r="J66" s="1">
         <v>625.04</v>
@@ -3135,7 +3135,7 @@
         <v>65.97</v>
       </c>
       <c r="I67" s="1">
-        <v>89223</v>
+        <v>89234</v>
       </c>
       <c r="J67" s="1">
         <v>28871.01</v>
@@ -3176,7 +3176,7 @@
         <v>-13.02</v>
       </c>
       <c r="I68" s="1">
-        <v>546894</v>
+        <v>546904</v>
       </c>
       <c r="J68" s="1">
         <v>5309.97</v>
@@ -3217,7 +3217,7 @@
         <v>-8.39</v>
       </c>
       <c r="I69" s="1">
-        <v>286798</v>
+        <v>286799</v>
       </c>
       <c r="J69" s="1">
         <v>11672.92</v>
@@ -3258,7 +3258,7 @@
         <v>64.63</v>
       </c>
       <c r="I70" s="1">
-        <v>114348</v>
+        <v>114350</v>
       </c>
       <c r="J70" s="1">
         <v>16532.13</v>
@@ -3299,7 +3299,7 @@
         <v>-32.4</v>
       </c>
       <c r="I71" s="1">
-        <v>3427297</v>
+        <v>3427739</v>
       </c>
       <c r="J71" s="1">
         <v>439.76</v>
@@ -3340,7 +3340,7 @@
         <v>-2.98</v>
       </c>
       <c r="I72" s="1">
-        <v>2469290</v>
+        <v>2469306</v>
       </c>
       <c r="J72" s="1">
         <v>627.05</v>
@@ -3381,7 +3381,7 @@
         <v>35.38</v>
       </c>
       <c r="I73" s="1">
-        <v>167531</v>
+        <v>167534</v>
       </c>
       <c r="J73" s="1">
         <v>6620.8</v>
@@ -3422,7 +3422,7 @@
         <v>38.07</v>
       </c>
       <c r="I74" s="1">
-        <v>218397</v>
+        <v>218446</v>
       </c>
       <c r="J74" s="1">
         <v>3578.19</v>
@@ -3463,7 +3463,7 @@
         <v>-18.71</v>
       </c>
       <c r="I75" s="1">
-        <v>160337</v>
+        <v>160405</v>
       </c>
       <c r="J75" s="1">
         <v>2672.48</v>
@@ -3504,7 +3504,7 @@
         <v>-6.94</v>
       </c>
       <c r="I76" s="1">
-        <v>12742693</v>
+        <v>12744460</v>
       </c>
       <c r="J76" s="1">
         <v>77.54</v>
@@ -3545,7 +3545,7 @@
         <v>-28.71</v>
       </c>
       <c r="I77" s="1">
-        <v>1159679</v>
+        <v>1159683</v>
       </c>
       <c r="J77" s="1">
         <v>1053.01</v>
@@ -3586,7 +3586,7 @@
         <v>-23.01</v>
       </c>
       <c r="I78" s="1">
-        <v>995386</v>
+        <v>995504</v>
       </c>
       <c r="J78" s="1">
         <v>1306.78</v>
@@ -3627,7 +3627,7 @@
         <v>-30.3</v>
       </c>
       <c r="I79" s="1">
-        <v>520133</v>
+        <v>520286</v>
       </c>
       <c r="J79" s="1">
         <v>4573.74</v>
@@ -3668,7 +3668,7 @@
         <v>24.86</v>
       </c>
       <c r="I80" s="1">
-        <v>26027</v>
+        <v>26032</v>
       </c>
       <c r="J80" s="1">
         <v>39350.68</v>
@@ -3709,7 +3709,7 @@
         <v>-14.69</v>
       </c>
       <c r="I81" s="1">
-        <v>498752</v>
+        <v>498883</v>
       </c>
       <c r="J81" s="1">
         <v>2417.52</v>
@@ -3750,7 +3750,7 @@
         <v>-35.11</v>
       </c>
       <c r="I82" s="1">
-        <v>19112579</v>
+        <v>19116085</v>
       </c>
       <c r="J82" s="1">
         <v>298.2</v>
@@ -3791,7 +3791,7 @@
         <v>-1.82</v>
       </c>
       <c r="I83" s="1">
-        <v>1635711</v>
+        <v>1635769</v>
       </c>
       <c r="J83" s="1">
         <v>688.6</v>
@@ -3832,7 +3832,7 @@
         <v>4.21</v>
       </c>
       <c r="I84" s="1">
-        <v>261037</v>
+        <v>261146</v>
       </c>
       <c r="J84" s="1">
         <v>4840.03</v>
@@ -3873,7 +3873,7 @@
         <v>-23.79</v>
       </c>
       <c r="I85" s="1">
-        <v>1168713</v>
+        <v>1169297</v>
       </c>
       <c r="J85" s="1">
         <v>473.57</v>
@@ -3914,7 +3914,7 @@
         <v>-36.01</v>
       </c>
       <c r="I86" s="1">
-        <v>10229089</v>
+        <v>10234395</v>
       </c>
       <c r="J86" s="1">
         <v>97.88</v>
@@ -3955,7 +3955,7 @@
         <v>-9.64</v>
       </c>
       <c r="I87" s="1">
-        <v>3377516</v>
+        <v>3378726</v>
       </c>
       <c r="J87" s="1">
         <v>463.45</v>
@@ -3996,7 +3996,7 @@
         <v>23.55</v>
       </c>
       <c r="I88" s="1">
-        <v>6399409</v>
+        <v>6399426</v>
       </c>
       <c r="J88" s="1">
         <v>306.54</v>
@@ -4037,7 +4037,7 @@
         <v>1.15</v>
       </c>
       <c r="I89" s="1">
-        <v>783132</v>
+        <v>783206</v>
       </c>
       <c r="J89" s="1">
         <v>1499.99</v>
@@ -4078,7 +4078,7 @@
         <v>-6.51</v>
       </c>
       <c r="I90" s="1">
-        <v>9074222</v>
+        <v>9081220</v>
       </c>
       <c r="J90" s="1">
         <v>146.73</v>
@@ -4119,7 +4119,7 @@
         <v>4.04</v>
       </c>
       <c r="I91" s="1">
-        <v>76621</v>
+        <v>76632</v>
       </c>
       <c r="J91" s="1">
         <v>7230.79</v>
@@ -4160,7 +4160,7 @@
         <v>3.94</v>
       </c>
       <c r="I92" s="1">
-        <v>272967</v>
+        <v>272976</v>
       </c>
       <c r="J92" s="1">
         <v>1502.4</v>
@@ -4201,7 +4201,7 @@
         <v>-18.25</v>
       </c>
       <c r="I93" s="1">
-        <v>9012926</v>
+        <v>9013074</v>
       </c>
       <c r="J93" s="1">
         <v>1338.35</v>
@@ -4242,7 +4242,7 @@
         <v>-22.47</v>
       </c>
       <c r="I94" s="1">
-        <v>2644399</v>
+        <v>2647475</v>
       </c>
       <c r="J94" s="1">
         <v>123.51</v>
@@ -4283,7 +4283,7 @@
         <v>-14.46</v>
       </c>
       <c r="I95" s="1">
-        <v>926924</v>
+        <v>927364</v>
       </c>
       <c r="J95" s="1">
         <v>2049.85</v>
@@ -4324,7 +4324,7 @@
         <v>-7.83</v>
       </c>
       <c r="I96" s="1">
-        <v>4796685</v>
+        <v>4797068</v>
       </c>
       <c r="J96" s="1">
         <v>411.67</v>
@@ -4365,7 +4365,7 @@
         <v>-7.41</v>
       </c>
       <c r="I97" s="1">
-        <v>748169</v>
+        <v>748487</v>
       </c>
       <c r="J97" s="1">
         <v>2251.61</v>
@@ -4406,7 +4406,7 @@
         <v>33.76</v>
       </c>
       <c r="I98" s="1">
-        <v>389842</v>
+        <v>389846</v>
       </c>
       <c r="J98" s="1">
         <v>4106</v>
@@ -4447,7 +4447,7 @@
         <v>0.98</v>
       </c>
       <c r="I99" s="1">
-        <v>2855216</v>
+        <v>2855332</v>
       </c>
       <c r="J99" s="1">
         <v>1239.86</v>
@@ -4488,7 +4488,7 @@
         <v>15.94</v>
       </c>
       <c r="I100" s="1">
-        <v>2711623</v>
+        <v>2711703</v>
       </c>
       <c r="J100" s="1">
         <v>1524.98</v>
@@ -4529,7 +4529,7 @@
         <v>-43.44</v>
       </c>
       <c r="I101" s="1">
-        <v>8170560</v>
+        <v>8173166</v>
       </c>
       <c r="J101" s="1">
         <v>89.48</v>
@@ -4570,7 +4570,7 @@
         <v>-10.99</v>
       </c>
       <c r="I102" s="1">
-        <v>3345929</v>
+        <v>3346005</v>
       </c>
       <c r="J102" s="1">
         <v>393.57</v>
@@ -4611,7 +4611,7 @@
         <v>-8.02</v>
       </c>
       <c r="I103" s="1">
-        <v>13270212</v>
+        <v>13276141</v>
       </c>
       <c r="J103" s="1">
         <v>77.56</v>
@@ -4652,7 +4652,7 @@
         <v>-23.61</v>
       </c>
       <c r="I104" s="1">
-        <v>655857</v>
+        <v>655867</v>
       </c>
       <c r="J104" s="1">
         <v>1318.72</v>
@@ -4693,7 +4693,7 @@
         <v>33.23</v>
       </c>
       <c r="I105" s="1">
-        <v>8537964</v>
+        <v>8542987</v>
       </c>
       <c r="J105" s="1">
         <v>137.47</v>
@@ -4734,7 +4734,7 @@
         <v>-13.56</v>
       </c>
       <c r="I106" s="1">
-        <v>7963816</v>
+        <v>7967418</v>
       </c>
       <c r="J106" s="1">
         <v>99.43</v>
@@ -4775,7 +4775,7 @@
         <v>31.83</v>
       </c>
       <c r="I107" s="1">
-        <v>3736101</v>
+        <v>3736268</v>
       </c>
       <c r="J107" s="1">
         <v>1290.18</v>
@@ -4816,7 +4816,7 @@
         <v>22.93</v>
       </c>
       <c r="I108" s="1">
-        <v>9240611</v>
+        <v>9242270</v>
       </c>
       <c r="J108" s="1">
         <v>60.81</v>
@@ -4898,7 +4898,7 @@
         <v>25.05</v>
       </c>
       <c r="I110" s="1">
-        <v>469943</v>
+        <v>469950</v>
       </c>
       <c r="J110" s="1">
         <v>1866.8</v>
@@ -4939,7 +4939,7 @@
         <v>-9.09</v>
       </c>
       <c r="I111" s="1">
-        <v>398517</v>
+        <v>398615</v>
       </c>
       <c r="J111" s="1">
         <v>551.6</v>
@@ -4980,7 +4980,7 @@
         <v>-8.52</v>
       </c>
       <c r="I112" s="1">
-        <v>1396716</v>
+        <v>1396732</v>
       </c>
       <c r="J112" s="1">
         <v>1142.9</v>
@@ -5021,7 +5021,7 @@
         <v>-44.89</v>
       </c>
       <c r="I113" s="1">
-        <v>2453273</v>
+        <v>2454698</v>
       </c>
       <c r="J113" s="1">
         <v>264.54</v>
@@ -5062,7 +5062,7 @@
         <v>-2.78</v>
       </c>
       <c r="I114" s="1">
-        <v>10856606</v>
+        <v>10858191</v>
       </c>
       <c r="J114" s="1">
         <v>1040.41</v>
@@ -5103,7 +5103,7 @@
         <v>-0.49</v>
       </c>
       <c r="I115" s="1">
-        <v>23706800</v>
+        <v>23707029</v>
       </c>
       <c r="J115" s="1">
         <v>400.01</v>
@@ -5144,7 +5144,7 @@
         <v>-2.33</v>
       </c>
       <c r="I116" s="1">
-        <v>496186</v>
+        <v>496377</v>
       </c>
       <c r="J116" s="1">
         <v>1137.75</v>
@@ -5185,7 +5185,7 @@
         <v>-14.53</v>
       </c>
       <c r="I117" s="1">
-        <v>408225</v>
+        <v>408433</v>
       </c>
       <c r="J117" s="1">
         <v>490.3</v>
@@ -5226,7 +5226,7 @@
         <v>-37.27</v>
       </c>
       <c r="I118" s="1">
-        <v>1418243</v>
+        <v>1418714</v>
       </c>
       <c r="J118" s="1">
         <v>449.05</v>
@@ -5267,7 +5267,7 @@
         <v>-3.1</v>
       </c>
       <c r="I119" s="1">
-        <v>19353597</v>
+        <v>19353981</v>
       </c>
       <c r="J119" s="1">
         <v>194.15</v>
@@ -5349,7 +5349,7 @@
         <v>-0.38</v>
       </c>
       <c r="I121" s="1">
-        <v>11185468</v>
+        <v>11185746</v>
       </c>
       <c r="J121" s="1">
         <v>1284.86</v>
@@ -5390,7 +5390,7 @@
         <v>-4.89</v>
       </c>
       <c r="I122" s="1">
-        <v>21184</v>
+        <v>21194</v>
       </c>
       <c r="J122" s="1">
         <v>10666.22</v>
@@ -5431,7 +5431,7 @@
         <v>-14.54</v>
       </c>
       <c r="I123" s="1">
-        <v>11844395</v>
+        <v>11855186</v>
       </c>
       <c r="J123" s="1">
         <v>83.72</v>
@@ -5513,7 +5513,7 @@
         <v>26.91</v>
       </c>
       <c r="I125" s="1">
-        <v>2885231</v>
+        <v>2885253</v>
       </c>
       <c r="J125" s="1">
         <v>287.67</v>
@@ -5554,7 +5554,7 @@
         <v>-33.41</v>
       </c>
       <c r="I126" s="1">
-        <v>2314094</v>
+        <v>2314969</v>
       </c>
       <c r="J126" s="1">
         <v>546.2</v>
@@ -5595,7 +5595,7 @@
         <v>-18.39</v>
       </c>
       <c r="I127" s="1">
-        <v>364189</v>
+        <v>364242</v>
       </c>
       <c r="J127" s="1">
         <v>3623.49</v>
@@ -5636,7 +5636,7 @@
         <v>-28.3</v>
       </c>
       <c r="I128" s="1">
-        <v>22455352</v>
+        <v>22460624</v>
       </c>
       <c r="J128" s="1">
         <v>805.26</v>
@@ -5677,7 +5677,7 @@
         <v>-10.02</v>
       </c>
       <c r="I129" s="1">
-        <v>3550739</v>
+        <v>3551793</v>
       </c>
       <c r="J129" s="1">
         <v>412.33</v>
@@ -5718,7 +5718,7 @@
         <v>22.23</v>
       </c>
       <c r="I130" s="1">
-        <v>7853831</v>
+        <v>7856997</v>
       </c>
       <c r="J130" s="1">
         <v>347.06</v>
@@ -5800,7 +5800,7 @@
         <v>4.15</v>
       </c>
       <c r="I132" s="1">
-        <v>600946</v>
+        <v>600949</v>
       </c>
       <c r="J132" s="1">
         <v>2780.5</v>
@@ -5841,7 +5841,7 @@
         <v>-33.05</v>
       </c>
       <c r="I133" s="1">
-        <v>450107</v>
+        <v>450300</v>
       </c>
       <c r="J133" s="1">
         <v>13767.3</v>
@@ -5882,7 +5882,7 @@
         <v>11.1</v>
       </c>
       <c r="I134" s="1">
-        <v>525570</v>
+        <v>525591</v>
       </c>
       <c r="J134" s="1">
         <v>8053.62</v>
@@ -5923,7 +5923,7 @@
         <v>-11.06</v>
       </c>
       <c r="I135" s="1">
-        <v>637105</v>
+        <v>637154</v>
       </c>
       <c r="J135" s="1">
         <v>1315.42</v>
@@ -5964,7 +5964,7 @@
         <v>-5.91</v>
       </c>
       <c r="I136" s="1">
-        <v>12992549</v>
+        <v>12995461</v>
       </c>
       <c r="J136" s="1">
         <v>283.36</v>
@@ -6005,7 +6005,7 @@
         <v>-40.21</v>
       </c>
       <c r="I137" s="1">
-        <v>5315902</v>
+        <v>5322217</v>
       </c>
       <c r="J137" s="1">
         <v>285.73</v>
@@ -6046,7 +6046,7 @@
         <v>9.71</v>
       </c>
       <c r="I138" s="1">
-        <v>233880</v>
+        <v>233882</v>
       </c>
       <c r="J138" s="1">
         <v>10240.75</v>
@@ -6087,7 +6087,7 @@
         <v>-14.77</v>
       </c>
       <c r="I139" s="1">
-        <v>4503407</v>
+        <v>4504674</v>
       </c>
       <c r="J139" s="1">
         <v>1899.12</v>
@@ -6128,7 +6128,7 @@
         <v>-41.94</v>
       </c>
       <c r="I140" s="1">
-        <v>2738119</v>
+        <v>2738231</v>
       </c>
       <c r="J140" s="1">
         <v>1594.44</v>
@@ -6169,7 +6169,7 @@
         <v>23.01</v>
       </c>
       <c r="I141" s="1">
-        <v>2257989</v>
+        <v>2258564</v>
       </c>
       <c r="J141" s="1">
         <v>1019.71</v>
@@ -6210,7 +6210,7 @@
         <v>-22.74</v>
       </c>
       <c r="I142" s="1">
-        <v>5661697</v>
+        <v>5662642</v>
       </c>
       <c r="J142" s="1">
         <v>342.02</v>
@@ -6251,7 +6251,7 @@
         <v>-34.08</v>
       </c>
       <c r="I143" s="1">
-        <v>773376</v>
+        <v>773533</v>
       </c>
       <c r="J143" s="1">
         <v>678.14</v>
@@ -6292,7 +6292,7 @@
         <v>33.92</v>
       </c>
       <c r="I144" s="1">
-        <v>15093153</v>
+        <v>15101251</v>
       </c>
       <c r="J144" s="1">
         <v>75.84</v>
@@ -6333,7 +6333,7 @@
         <v>20.2</v>
       </c>
       <c r="I145" s="1">
-        <v>795652</v>
+        <v>795714</v>
       </c>
       <c r="J145" s="1">
         <v>1037.9</v>
@@ -6374,7 +6374,7 @@
         <v>1.82</v>
       </c>
       <c r="I146" s="1">
-        <v>770562</v>
+        <v>770585</v>
       </c>
       <c r="J146" s="1">
         <v>1823.08</v>
@@ -6415,7 +6415,7 @@
         <v>-3.02</v>
       </c>
       <c r="I147" s="1">
-        <v>13007554</v>
+        <v>13008898</v>
       </c>
       <c r="J147" s="1">
         <v>166.17</v>
@@ -6456,7 +6456,7 @@
         <v>18.98</v>
       </c>
       <c r="I148" s="1">
-        <v>1604936</v>
+        <v>1612353</v>
       </c>
       <c r="J148" s="1">
         <v>1637.59</v>
@@ -6497,7 +6497,7 @@
         <v>2.12</v>
       </c>
       <c r="I149" s="1">
-        <v>234901</v>
+        <v>234951</v>
       </c>
       <c r="J149" s="1">
         <v>1686.22</v>
@@ -6538,7 +6538,7 @@
         <v>5.01</v>
       </c>
       <c r="I150" s="1">
-        <v>3779475</v>
+        <v>3826380</v>
       </c>
       <c r="J150" s="1">
         <v>310.87</v>
@@ -6620,7 +6620,7 @@
         <v>-15.16</v>
       </c>
       <c r="I152" s="1">
-        <v>2119577</v>
+        <v>2119606</v>
       </c>
       <c r="J152" s="1">
         <v>905.1</v>
@@ -6661,7 +6661,7 @@
         <v>8.08</v>
       </c>
       <c r="I153" s="1">
-        <v>269203</v>
+        <v>269330</v>
       </c>
       <c r="J153" s="1">
         <v>5011.65</v>
@@ -6702,7 +6702,7 @@
         <v>-10.81</v>
       </c>
       <c r="I154" s="1">
-        <v>1709618</v>
+        <v>1709883</v>
       </c>
       <c r="J154" s="1">
         <v>3953.5</v>
@@ -6743,7 +6743,7 @@
         <v>-5.55</v>
       </c>
       <c r="I155" s="1">
-        <v>72524</v>
+        <v>72527</v>
       </c>
       <c r="J155" s="1">
         <v>5472.14</v>
@@ -6784,7 +6784,7 @@
         <v>-22.66</v>
       </c>
       <c r="I156" s="1">
-        <v>773605</v>
+        <v>773974</v>
       </c>
       <c r="J156" s="1">
         <v>1476.91</v>
@@ -6825,7 +6825,7 @@
         <v>9.69</v>
       </c>
       <c r="I157" s="1">
-        <v>527318</v>
+        <v>527351</v>
       </c>
       <c r="J157" s="1">
         <v>4425.13</v>
@@ -6866,7 +6866,7 @@
         <v>-18.43</v>
       </c>
       <c r="I158" s="1">
-        <v>3217716</v>
+        <v>3218051</v>
       </c>
       <c r="J158" s="1">
         <v>1025.78</v>
@@ -6907,7 +6907,7 @@
         <v>-6.33</v>
       </c>
       <c r="I159" s="1">
-        <v>1025700</v>
+        <v>1026224</v>
       </c>
       <c r="J159" s="1">
         <v>737.1</v>
@@ -6948,7 +6948,7 @@
         <v>17.75</v>
       </c>
       <c r="I160" s="1">
-        <v>191542247</v>
+        <v>192070164</v>
       </c>
       <c r="J160" s="1">
         <v>12.29</v>
@@ -6989,7 +6989,7 @@
         <v>-29.6</v>
       </c>
       <c r="I161" s="1">
-        <v>9987255</v>
+        <v>9995480</v>
       </c>
       <c r="J161" s="1">
         <v>115.43</v>
@@ -7030,7 +7030,7 @@
         <v>6.72</v>
       </c>
       <c r="I162" s="1">
-        <v>460374</v>
+        <v>460461</v>
       </c>
       <c r="J162" s="1">
         <v>3773.35</v>
@@ -7071,7 +7071,7 @@
         <v>83.84</v>
       </c>
       <c r="I163" s="1">
-        <v>1211389</v>
+        <v>1211508</v>
       </c>
       <c r="J163" s="1">
         <v>1393.58</v>
@@ -7112,7 +7112,7 @@
         <v>26.81</v>
       </c>
       <c r="I164" s="1">
-        <v>2976640</v>
+        <v>2977155</v>
       </c>
       <c r="J164" s="1">
         <v>3328.05</v>
@@ -7153,7 +7153,7 @@
         <v>-3.15</v>
       </c>
       <c r="I165" s="1">
-        <v>437637</v>
+        <v>437748</v>
       </c>
       <c r="J165" s="1">
         <v>7400.26</v>
@@ -7194,7 +7194,7 @@
         <v>-13.02</v>
       </c>
       <c r="I166" s="1">
-        <v>884039</v>
+        <v>884233</v>
       </c>
       <c r="J166" s="1">
         <v>1373.32</v>
@@ -7235,7 +7235,7 @@
         <v>12.85</v>
       </c>
       <c r="I167" s="1">
-        <v>673353</v>
+        <v>673666</v>
       </c>
       <c r="J167" s="1">
         <v>1999.53</v>
@@ -7276,7 +7276,7 @@
         <v>-18.72</v>
       </c>
       <c r="I168" s="1">
-        <v>468168</v>
+        <v>468229</v>
       </c>
       <c r="J168" s="1">
         <v>931.31</v>
@@ -7317,7 +7317,7 @@
         <v>16.2</v>
       </c>
       <c r="I169" s="1">
-        <v>3212084</v>
+        <v>3213447</v>
       </c>
       <c r="J169" s="1">
         <v>463.77</v>
@@ -7358,7 +7358,7 @@
         <v>-12.75</v>
       </c>
       <c r="I170" s="1">
-        <v>479534</v>
+        <v>479542</v>
       </c>
       <c r="J170" s="1">
         <v>2388.79</v>
@@ -7440,7 +7440,7 @@
         <v>30.57</v>
       </c>
       <c r="I172" s="1">
-        <v>3439494</v>
+        <v>3441535</v>
       </c>
       <c r="J172" s="1">
         <v>288.52</v>
@@ -7481,7 +7481,7 @@
         <v>-37.41</v>
       </c>
       <c r="I173" s="1">
-        <v>3611905</v>
+        <v>3612009</v>
       </c>
       <c r="J173" s="1">
         <v>94.69</v>
@@ -7522,7 +7522,7 @@
         <v>40.57</v>
       </c>
       <c r="I174" s="1">
-        <v>855793</v>
+        <v>856296</v>
       </c>
       <c r="J174" s="1">
         <v>1434.11</v>
@@ -7563,7 +7563,7 @@
         <v>0.21</v>
       </c>
       <c r="I175" s="1">
-        <v>3370230</v>
+        <v>3370461</v>
       </c>
       <c r="J175" s="1">
         <v>924.09</v>
@@ -7604,7 +7604,7 @@
         <v>-15.34</v>
       </c>
       <c r="I176" s="1">
-        <v>634600</v>
+        <v>634638</v>
       </c>
       <c r="J176" s="1">
         <v>2545.82</v>
@@ -7686,7 +7686,7 @@
         <v>18.96</v>
       </c>
       <c r="I178" s="1">
-        <v>285965</v>
+        <v>285970</v>
       </c>
       <c r="J178" s="1">
         <v>4471.99</v>
@@ -7727,7 +7727,7 @@
         <v>-10.67</v>
       </c>
       <c r="I179" s="1">
-        <v>408734</v>
+        <v>408769</v>
       </c>
       <c r="J179" s="1">
         <v>1103.71</v>
@@ -7768,7 +7768,7 @@
         <v>1.55</v>
       </c>
       <c r="I180" s="1">
-        <v>1649441</v>
+        <v>1649477</v>
       </c>
       <c r="J180" s="1">
         <v>1807.34</v>
@@ -7809,7 +7809,7 @@
         <v>-21.55</v>
       </c>
       <c r="I181" s="1">
-        <v>450961</v>
+        <v>451040</v>
       </c>
       <c r="J181" s="1">
         <v>1817.1</v>
@@ -7850,7 +7850,7 @@
         <v>13.65</v>
       </c>
       <c r="I182" s="1">
-        <v>20518399</v>
+        <v>20520736</v>
       </c>
       <c r="J182" s="1">
         <v>278.03</v>
@@ -7891,7 +7891,7 @@
         <v>-14.04</v>
       </c>
       <c r="I183" s="1">
-        <v>627307</v>
+        <v>627706</v>
       </c>
       <c r="J183" s="1">
         <v>2577.31</v>
@@ -7932,7 +7932,7 @@
         <v>-8.26</v>
       </c>
       <c r="I184" s="1">
-        <v>512856</v>
+        <v>512866</v>
       </c>
       <c r="J184" s="1">
         <v>1479.13</v>
@@ -7973,7 +7973,7 @@
         <v>5.93</v>
       </c>
       <c r="I185" s="1">
-        <v>1289182</v>
+        <v>1289320</v>
       </c>
       <c r="J185" s="1">
         <v>365.53</v>
@@ -8014,7 +8014,7 @@
         <v>-5.96</v>
       </c>
       <c r="I186" s="1">
-        <v>605181</v>
+        <v>605227</v>
       </c>
       <c r="J186" s="1">
         <v>5350.35</v>
@@ -8055,7 +8055,7 @@
         <v>6.31</v>
       </c>
       <c r="I187" s="1">
-        <v>478984</v>
+        <v>478989</v>
       </c>
       <c r="J187" s="1">
         <v>2304.58</v>
@@ -8096,7 +8096,7 @@
         <v>-0.32</v>
       </c>
       <c r="I188" s="1">
-        <v>7664545</v>
+        <v>7664776</v>
       </c>
       <c r="J188" s="1">
         <v>1353</v>
@@ -8137,7 +8137,7 @@
         <v>15.65</v>
       </c>
       <c r="I189" s="1">
-        <v>7934180</v>
+        <v>7943943</v>
       </c>
       <c r="J189" s="1">
         <v>169.82</v>
@@ -8178,7 +8178,7 @@
         <v>-19.08</v>
       </c>
       <c r="I190" s="1">
-        <v>16639765</v>
+        <v>16651593</v>
       </c>
       <c r="J190" s="1">
         <v>170.78</v>
@@ -8198,37 +8198,37 @@
         <v>190</v>
       </c>
       <c r="B191" t="str">
-        <v>Ather Energy Ltd</v>
+        <v>Interglobe Aviation Limited</v>
       </c>
       <c r="C191" t="str">
-        <v>ATHERENERG</v>
+        <v>INDIGO</v>
       </c>
       <c r="D191" s="1">
-        <v>1470.4</v>
+        <v>4718.5</v>
       </c>
       <c r="E191" s="2">
-        <v>-1.64</v>
+        <v>-1.71</v>
       </c>
       <c r="F191" s="2">
-        <v>2.51</v>
+        <v>-2.37</v>
       </c>
       <c r="G191" s="2">
-        <v>3.19</v>
+        <v>-5.33</v>
       </c>
       <c r="H191" s="2">
-        <v>94.82</v>
+        <v>-6.74</v>
       </c>
       <c r="I191" s="1">
-        <v>2205859</v>
+        <v>884924</v>
       </c>
       <c r="J191" s="1">
-        <v>1035.96</v>
+        <v>4818.01</v>
       </c>
       <c r="K191" s="1">
-        <v>1466.46</v>
+        <v>4847.75</v>
       </c>
       <c r="L191" s="1">
-        <v>1519.14</v>
+        <v>5055.98</v>
       </c>
       <c r="M191" t="str">
         <v/>
@@ -8239,37 +8239,37 @@
         <v>191</v>
       </c>
       <c r="B192" t="str">
-        <v>Interglobe Aviation Limited</v>
+        <v>Multi Commodity Exchange Of India Limited</v>
       </c>
       <c r="C192" t="str">
-        <v>INDIGO</v>
+        <v>MCX</v>
       </c>
       <c r="D192" s="1">
-        <v>4718.5</v>
+        <v>3250.5</v>
       </c>
       <c r="E192" s="2">
-        <v>-1.71</v>
+        <v>-1.74</v>
       </c>
       <c r="F192" s="2">
-        <v>-2.37</v>
+        <v>-2.04</v>
       </c>
       <c r="G192" s="2">
-        <v>-5.33</v>
+        <v>-1.51</v>
       </c>
       <c r="H192" s="2">
-        <v>-6.74</v>
+        <v>45.95</v>
       </c>
       <c r="I192" s="1">
-        <v>884753</v>
+        <v>1346455</v>
       </c>
       <c r="J192" s="1">
-        <v>4818.01</v>
+        <v>2792.84</v>
       </c>
       <c r="K192" s="1">
-        <v>4847.75</v>
+        <v>3295.44</v>
       </c>
       <c r="L192" s="1">
-        <v>5055.98</v>
+        <v>3174.8</v>
       </c>
       <c r="M192" t="str">
         <v/>
@@ -8280,37 +8280,37 @@
         <v>192</v>
       </c>
       <c r="B193" t="str">
-        <v>Multi Commodity Exchange Of India Limited</v>
+        <v>Delhivery Ltd</v>
       </c>
       <c r="C193" t="str">
-        <v>MCX</v>
+        <v>DELHIVERY</v>
       </c>
       <c r="D193" s="1">
-        <v>3250.5</v>
+        <v>409.15</v>
       </c>
       <c r="E193" s="2">
         <v>-1.74</v>
       </c>
       <c r="F193" s="2">
-        <v>-2.04</v>
+        <v>2.16</v>
       </c>
       <c r="G193" s="2">
-        <v>-1.51</v>
+        <v>-0.13</v>
       </c>
       <c r="H193" s="2">
-        <v>45.95</v>
+        <v>1.31</v>
       </c>
       <c r="I193" s="1">
-        <v>1346339</v>
+        <v>2022500</v>
       </c>
       <c r="J193" s="1">
-        <v>2792.84</v>
+        <v>444.32</v>
       </c>
       <c r="K193" s="1">
-        <v>3295.44</v>
+        <v>409.41</v>
       </c>
       <c r="L193" s="1">
-        <v>3174.8</v>
+        <v>440.74</v>
       </c>
       <c r="M193" t="str">
         <v/>
@@ -8321,37 +8321,37 @@
         <v>193</v>
       </c>
       <c r="B194" t="str">
-        <v>Delhivery Ltd</v>
+        <v>Muthoot Finance Limited</v>
       </c>
       <c r="C194" t="str">
-        <v>DELHIVERY</v>
+        <v>MUTHOOTFIN</v>
       </c>
       <c r="D194" s="1">
-        <v>409.15</v>
+        <v>2580</v>
       </c>
       <c r="E194" s="2">
-        <v>-1.74</v>
+        <v>-1.75</v>
       </c>
       <c r="F194" s="2">
-        <v>2.16</v>
+        <v>-1.7</v>
       </c>
       <c r="G194" s="2">
-        <v>-0.13</v>
+        <v>-5.74</v>
       </c>
       <c r="H194" s="2">
-        <v>1.31</v>
+        <v>-32.31</v>
       </c>
       <c r="I194" s="1">
-        <v>2022200</v>
+        <v>405025</v>
       </c>
       <c r="J194" s="1">
-        <v>444.32</v>
+        <v>3266.36</v>
       </c>
       <c r="K194" s="1">
-        <v>409.41</v>
+        <v>2652.49</v>
       </c>
       <c r="L194" s="1">
-        <v>440.74</v>
+        <v>2851.95</v>
       </c>
       <c r="M194" t="str">
         <v/>
@@ -8362,37 +8362,37 @@
         <v>194</v>
       </c>
       <c r="B195" t="str">
-        <v>Muthoot Finance Limited</v>
+        <v>Hindustan Zinc Limited</v>
       </c>
       <c r="C195" t="str">
-        <v>MUTHOOTFIN</v>
+        <v>HINDZINC</v>
       </c>
       <c r="D195" s="1">
-        <v>2580</v>
+        <v>540</v>
       </c>
       <c r="E195" s="2">
         <v>-1.75</v>
       </c>
       <c r="F195" s="2">
-        <v>-1.7</v>
+        <v>-0.64</v>
       </c>
       <c r="G195" s="2">
-        <v>-5.74</v>
+        <v>-4.59</v>
       </c>
       <c r="H195" s="2">
-        <v>-32.31</v>
+        <v>-11.83</v>
       </c>
       <c r="I195" s="1">
-        <v>404843</v>
+        <v>2069428</v>
       </c>
       <c r="J195" s="1">
-        <v>3266.36</v>
+        <v>585.96</v>
       </c>
       <c r="K195" s="1">
-        <v>2652.49</v>
+        <v>551.45</v>
       </c>
       <c r="L195" s="1">
-        <v>2851.95</v>
+        <v>579.7</v>
       </c>
       <c r="M195" t="str">
         <v/>
@@ -8403,37 +8403,37 @@
         <v>195</v>
       </c>
       <c r="B196" t="str">
-        <v>Hindustan Zinc Limited</v>
+        <v>Ather Energy Ltd</v>
       </c>
       <c r="C196" t="str">
-        <v>HINDZINC</v>
+        <v>ATHERENERG</v>
       </c>
       <c r="D196" s="1">
-        <v>540</v>
+        <v>1467</v>
       </c>
       <c r="E196" s="2">
-        <v>-1.75</v>
+        <v>-1.87</v>
       </c>
       <c r="F196" s="2">
-        <v>-0.64</v>
+        <v>2.27</v>
       </c>
       <c r="G196" s="2">
-        <v>-4.59</v>
+        <v>2.95</v>
       </c>
       <c r="H196" s="2">
-        <v>-11.83</v>
+        <v>94.37</v>
       </c>
       <c r="I196" s="1">
-        <v>2068878</v>
+        <v>2206109</v>
       </c>
       <c r="J196" s="1">
-        <v>585.96</v>
+        <v>1035.95</v>
       </c>
       <c r="K196" s="1">
-        <v>551.45</v>
+        <v>1465.84</v>
       </c>
       <c r="L196" s="1">
-        <v>579.7</v>
+        <v>1519.07</v>
       </c>
       <c r="M196" t="str">
         <v/>
@@ -8465,7 +8465,7 @@
         <v>-15.6</v>
       </c>
       <c r="I197" s="1">
-        <v>829593</v>
+        <v>829805</v>
       </c>
       <c r="J197" s="1">
         <v>1874.64</v>
@@ -8506,7 +8506,7 @@
         <v>-4.36</v>
       </c>
       <c r="I198" s="1">
-        <v>1520881</v>
+        <v>1521006</v>
       </c>
       <c r="J198" s="1">
         <v>1244.39</v>
@@ -8547,7 +8547,7 @@
         <v>15.61</v>
       </c>
       <c r="I199" s="1">
-        <v>15683835</v>
+        <v>15689934</v>
       </c>
       <c r="J199" s="1">
         <v>176.4</v>
@@ -8588,7 +8588,7 @@
         <v>26.12</v>
       </c>
       <c r="I200" s="1">
-        <v>730891</v>
+        <v>731009</v>
       </c>
       <c r="J200" s="1">
         <v>999.6</v>
@@ -8629,7 +8629,7 @@
         <v>35.55</v>
       </c>
       <c r="I201" s="1">
-        <v>164991</v>
+        <v>165006</v>
       </c>
       <c r="J201" s="1">
         <v>9333.65</v>
@@ -8670,7 +8670,7 @@
         <v>-0.47</v>
       </c>
       <c r="I202" s="1">
-        <v>2868727</v>
+        <v>2869946</v>
       </c>
       <c r="J202" s="1">
         <v>980.68</v>
@@ -8711,7 +8711,7 @@
         <v>-18.91</v>
       </c>
       <c r="I203" s="1">
-        <v>1536372</v>
+        <v>1536626</v>
       </c>
       <c r="J203" s="1">
         <v>1870.31</v>
@@ -8752,7 +8752,7 @@
         <v>14.33</v>
       </c>
       <c r="I204" s="1">
-        <v>13480600</v>
+        <v>13493327</v>
       </c>
       <c r="J204" s="1">
         <v>268.73</v>
@@ -8793,7 +8793,7 @@
         <v>-24.68</v>
       </c>
       <c r="I205" s="1">
-        <v>2791871</v>
+        <v>2792391</v>
       </c>
       <c r="J205" s="1">
         <v>3247.63</v>
@@ -8834,7 +8834,7 @@
         <v>-3.02</v>
       </c>
       <c r="I206" s="1">
-        <v>6697470</v>
+        <v>6697626</v>
       </c>
       <c r="J206" s="1">
         <v>975.17</v>
@@ -8875,7 +8875,7 @@
         <v>21.47</v>
       </c>
       <c r="I207" s="1">
-        <v>524651</v>
+        <v>525924</v>
       </c>
       <c r="J207" s="1">
         <v>865.41</v>
@@ -8916,7 +8916,7 @@
         <v>41.15</v>
       </c>
       <c r="I208" s="1">
-        <v>962619</v>
+        <v>963730</v>
       </c>
       <c r="J208" s="1">
         <v>7155.48</v>
@@ -8957,7 +8957,7 @@
         <v>-27.45</v>
       </c>
       <c r="I209" s="1">
-        <v>2059518</v>
+        <v>2060367</v>
       </c>
       <c r="J209" s="1">
         <v>613.69</v>
@@ -8998,7 +8998,7 @@
         <v>-0.16</v>
       </c>
       <c r="I210" s="1">
-        <v>1163569</v>
+        <v>1163946</v>
       </c>
       <c r="J210" s="1">
         <v>1022.56</v>
@@ -9039,7 +9039,7 @@
         <v>-23.2</v>
       </c>
       <c r="I211" s="1">
-        <v>786690</v>
+        <v>786729</v>
       </c>
       <c r="J211" s="1">
         <v>1605.58</v>
@@ -9080,7 +9080,7 @@
         <v>-18.09</v>
       </c>
       <c r="I212" s="1">
-        <v>5065263</v>
+        <v>5068092</v>
       </c>
       <c r="J212" s="1">
         <v>291.6</v>
@@ -9121,7 +9121,7 @@
         <v>-8.18</v>
       </c>
       <c r="I213" s="1">
-        <v>2507099</v>
+        <v>2507971</v>
       </c>
       <c r="J213" s="1">
         <v>1678.17</v>
@@ -9162,7 +9162,7 @@
         <v>-4.64</v>
       </c>
       <c r="I214" s="1">
-        <v>6097294</v>
+        <v>6098214</v>
       </c>
       <c r="J214" s="1">
         <v>1009.11</v>
@@ -9203,7 +9203,7 @@
         <v>-22.61</v>
       </c>
       <c r="I215" s="1">
-        <v>17520073</v>
+        <v>17530062</v>
       </c>
       <c r="J215" s="1">
         <v>267.86</v>
@@ -9244,7 +9244,7 @@
         <v>-0.84</v>
       </c>
       <c r="I216" s="1">
-        <v>5926759</v>
+        <v>5931126</v>
       </c>
       <c r="J216" s="1">
         <v>533.59</v>

--- a/fnot.xlsx
+++ b/fnot.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S216"/>
+  <dimension ref="A1:T216"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -461,6 +461,9 @@
         <v>MONTLY macd_signal</v>
       </c>
       <c r="S1" t="str">
+        <v>rsi</v>
+      </c>
+      <c r="T1" t="str">
         <v>Add Column</v>
       </c>
     </row>
@@ -490,7 +493,7 @@
         <v>-28.15</v>
       </c>
       <c r="I2" s="1">
-        <v>36561213</v>
+        <v>36571461</v>
       </c>
       <c r="J2" s="1">
         <v>196.08</v>
@@ -502,7 +505,7 @@
         <v>172.49</v>
       </c>
       <c r="M2" s="3">
-        <v>-7.59</v>
+        <v>3.01</v>
       </c>
       <c r="N2" s="3">
         <v>-0.54</v>
@@ -517,9 +520,12 @@
         <v>-18.76</v>
       </c>
       <c r="R2" s="3">
-        <v>-0.54</v>
-      </c>
-      <c r="S2" t="str">
+        <v>-12.29</v>
+      </c>
+      <c r="S2" s="3">
+        <v>72.86</v>
+      </c>
+      <c r="T2" t="str">
         <v/>
       </c>
     </row>
@@ -549,7 +555,7 @@
         <v>-27.7</v>
       </c>
       <c r="I3" s="1">
-        <v>17747791</v>
+        <v>17750752</v>
       </c>
       <c r="J3" s="1">
         <v>1231.69</v>
@@ -561,7 +567,7 @@
         <v>1086.44</v>
       </c>
       <c r="M3" s="3">
-        <v>-41.76</v>
+        <v>17.68</v>
       </c>
       <c r="N3" s="3">
         <v>-2.65</v>
@@ -576,9 +582,12 @@
         <v>-133.64</v>
       </c>
       <c r="R3" s="3">
-        <v>-2.65</v>
-      </c>
-      <c r="S3" t="str">
+        <v>-96.62</v>
+      </c>
+      <c r="S3" s="3">
+        <v>67.05</v>
+      </c>
+      <c r="T3" t="str">
         <v/>
       </c>
     </row>
@@ -608,7 +617,7 @@
         <v>-12.27</v>
       </c>
       <c r="I4" s="1">
-        <v>3983716</v>
+        <v>3984228</v>
       </c>
       <c r="J4" s="1">
         <v>1332.84</v>
@@ -620,7 +629,7 @@
         <v>1288.16</v>
       </c>
       <c r="M4" s="3">
-        <v>1.05</v>
+        <v>29.88</v>
       </c>
       <c r="N4" s="3">
         <v>6.18</v>
@@ -635,9 +644,12 @@
         <v>-53.55</v>
       </c>
       <c r="R4" s="3">
-        <v>6.18</v>
-      </c>
-      <c r="S4" t="str">
+        <v>-30.04</v>
+      </c>
+      <c r="S4" s="3">
+        <v>73.33</v>
+      </c>
+      <c r="T4" t="str">
         <v/>
       </c>
     </row>
@@ -667,7 +679,7 @@
         <v>15.32</v>
       </c>
       <c r="I5" s="1">
-        <v>5283306</v>
+        <v>5285030</v>
       </c>
       <c r="J5" s="1">
         <v>1519.51</v>
@@ -679,7 +691,7 @@
         <v>1583.91</v>
       </c>
       <c r="M5" s="3">
-        <v>53.42</v>
+        <v>47.8</v>
       </c>
       <c r="N5" s="3">
         <v>10.36</v>
@@ -694,9 +706,12 @@
         <v>58.81</v>
       </c>
       <c r="R5" s="3">
-        <v>10.36</v>
-      </c>
-      <c r="S5" t="str">
+        <v>44.51</v>
+      </c>
+      <c r="S5" s="3">
+        <v>76.82</v>
+      </c>
+      <c r="T5" t="str">
         <v/>
       </c>
     </row>
@@ -726,7 +741,7 @@
         <v>-7.75</v>
       </c>
       <c r="I6" s="1">
-        <v>1210684</v>
+        <v>1210799</v>
       </c>
       <c r="J6" s="1">
         <v>2381.47</v>
@@ -738,7 +753,7 @@
         <v>2383.69</v>
       </c>
       <c r="M6" s="3">
-        <v>11</v>
+        <v>47.57</v>
       </c>
       <c r="N6" s="3">
         <v>13.71</v>
@@ -753,9 +768,12 @@
         <v>-60.68</v>
       </c>
       <c r="R6" s="3">
-        <v>13.71</v>
-      </c>
-      <c r="S6" t="str">
+        <v>-37.01</v>
+      </c>
+      <c r="S6" s="3">
+        <v>72.07</v>
+      </c>
+      <c r="T6" t="str">
         <v/>
       </c>
     </row>
@@ -785,7 +803,7 @@
         <v>-6.59</v>
       </c>
       <c r="I7" s="1">
-        <v>899667</v>
+        <v>899892</v>
       </c>
       <c r="J7" s="1">
         <v>5339.15</v>
@@ -797,7 +815,7 @@
         <v>5561.88</v>
       </c>
       <c r="M7" s="3">
-        <v>124.48</v>
+        <v>98.5</v>
       </c>
       <c r="N7" s="3">
         <v>66.67</v>
@@ -812,9 +830,12 @@
         <v>242.69</v>
       </c>
       <c r="R7" s="3">
-        <v>66.67</v>
-      </c>
-      <c r="S7" t="str">
+        <v>314.53</v>
+      </c>
+      <c r="S7" s="3">
+        <v>60.21</v>
+      </c>
+      <c r="T7" t="str">
         <v/>
       </c>
     </row>
@@ -844,7 +865,7 @@
         <v>-21.12</v>
       </c>
       <c r="I8" s="1">
-        <v>5431961</v>
+        <v>5435958</v>
       </c>
       <c r="J8" s="1">
         <v>2457.7</v>
@@ -856,7 +877,7 @@
         <v>2244.91</v>
       </c>
       <c r="M8" s="3">
-        <v>-49.75</v>
+        <v>63.72</v>
       </c>
       <c r="N8" s="3">
         <v>10.16</v>
@@ -871,9 +892,12 @@
         <v>-349.49</v>
       </c>
       <c r="R8" s="3">
-        <v>10.16</v>
-      </c>
-      <c r="S8" t="str">
+        <v>-304.9</v>
+      </c>
+      <c r="S8" s="3">
+        <v>76.09</v>
+      </c>
+      <c r="T8" t="str">
         <v/>
       </c>
     </row>
@@ -903,7 +927,7 @@
         <v>-8.29</v>
       </c>
       <c r="I9" s="1">
-        <v>21667190</v>
+        <v>21680053</v>
       </c>
       <c r="J9" s="1">
         <v>77.42</v>
@@ -915,7 +939,7 @@
         <v>75.16</v>
       </c>
       <c r="M9" s="3">
-        <v>-1.51</v>
+        <v>-0.99</v>
       </c>
       <c r="N9" s="3">
         <v>-0.96</v>
@@ -930,9 +954,12 @@
         <v>0.08</v>
       </c>
       <c r="R9" s="3">
-        <v>-0.96</v>
-      </c>
-      <c r="S9" t="str">
+        <v>1.75</v>
+      </c>
+      <c r="S9" s="3">
+        <v>44.82</v>
+      </c>
+      <c r="T9" t="str">
         <v/>
       </c>
     </row>
@@ -962,7 +989,7 @@
         <v>-7.93</v>
       </c>
       <c r="I10" s="1">
-        <v>383918</v>
+        <v>383988</v>
       </c>
       <c r="J10" s="1">
         <v>11654.09</v>
@@ -974,7 +1001,7 @@
         <v>11154.36</v>
       </c>
       <c r="M10" s="3">
-        <v>-229.02</v>
+        <v>-104.46</v>
       </c>
       <c r="N10" s="3">
         <v>-137.84</v>
@@ -989,9 +1016,12 @@
         <v>214.48</v>
       </c>
       <c r="R10" s="3">
-        <v>-137.84</v>
-      </c>
-      <c r="S10" t="str">
+        <v>450.11</v>
+      </c>
+      <c r="S10" s="3">
+        <v>48.74</v>
+      </c>
+      <c r="T10" t="str">
         <v/>
       </c>
     </row>
@@ -1021,7 +1051,7 @@
         <v>41.37</v>
       </c>
       <c r="I11" s="1">
-        <v>768246</v>
+        <v>768287</v>
       </c>
       <c r="J11" s="1">
         <v>1839.72</v>
@@ -1033,7 +1063,7 @@
         <v>2169.23</v>
       </c>
       <c r="M11" s="3">
-        <v>109.05</v>
+        <v>-2.34</v>
       </c>
       <c r="N11" s="3">
         <v>-10.95</v>
@@ -1048,9 +1078,12 @@
         <v>334.87</v>
       </c>
       <c r="R11" s="3">
-        <v>-10.95</v>
-      </c>
-      <c r="S11" t="str">
+        <v>286.3</v>
+      </c>
+      <c r="S11" s="3">
+        <v>59.14</v>
+      </c>
+      <c r="T11" t="str">
         <v/>
       </c>
     </row>
@@ -1080,7 +1113,7 @@
         <v>-26.56</v>
       </c>
       <c r="I12" s="1">
-        <v>379329</v>
+        <v>379387</v>
       </c>
       <c r="J12" s="1">
         <v>4177.48</v>
@@ -1092,7 +1125,7 @@
         <v>3475.76</v>
       </c>
       <c r="M12" s="3">
-        <v>-235.13</v>
+        <v>94.44</v>
       </c>
       <c r="N12" s="3">
         <v>-3.29</v>
@@ -1107,9 +1140,12 @@
         <v>-781.32</v>
       </c>
       <c r="R12" s="3">
-        <v>-3.29</v>
-      </c>
-      <c r="S12" t="str">
+        <v>-672.5</v>
+      </c>
+      <c r="S12" s="3">
+        <v>71.83</v>
+      </c>
+      <c r="T12" t="str">
         <v/>
       </c>
     </row>
@@ -1139,7 +1175,7 @@
         <v>-53.54</v>
       </c>
       <c r="I13" s="1">
-        <v>2872201</v>
+        <v>2872511</v>
       </c>
       <c r="J13" s="1">
         <v>725.4</v>
@@ -1151,7 +1187,7 @@
         <v>553.96</v>
       </c>
       <c r="M13" s="3">
-        <v>-72.72</v>
+        <v>-4.78</v>
       </c>
       <c r="N13" s="3">
         <v>-14.02</v>
@@ -1166,9 +1202,12 @@
         <v>-185.04</v>
       </c>
       <c r="R13" s="3">
-        <v>-14.02</v>
-      </c>
-      <c r="S13" t="str">
+        <v>-127.74</v>
+      </c>
+      <c r="S13" s="3">
+        <v>56.1</v>
+      </c>
+      <c r="T13" t="str">
         <v/>
       </c>
     </row>
@@ -1198,7 +1237,7 @@
         <v>4.05</v>
       </c>
       <c r="I14" s="1">
-        <v>230238</v>
+        <v>230600</v>
       </c>
       <c r="J14" s="1">
         <v>2306.4</v>
@@ -1210,7 +1249,7 @@
         <v>2385.16</v>
       </c>
       <c r="M14" s="3">
-        <v>4.85</v>
+        <v>-29.34</v>
       </c>
       <c r="N14" s="3">
         <v>-6.82</v>
@@ -1225,9 +1264,12 @@
         <v>60.6</v>
       </c>
       <c r="R14" s="3">
-        <v>-6.82</v>
-      </c>
-      <c r="S14" t="str">
+        <v>72.46</v>
+      </c>
+      <c r="S14" s="3">
+        <v>40.12</v>
+      </c>
+      <c r="T14" t="str">
         <v/>
       </c>
     </row>
@@ -1257,7 +1299,7 @@
         <v>-29.72</v>
       </c>
       <c r="I15" s="1">
-        <v>1808573</v>
+        <v>1808601</v>
       </c>
       <c r="J15" s="1">
         <v>1046.16</v>
@@ -1269,7 +1311,7 @@
         <v>890.14</v>
       </c>
       <c r="M15" s="3">
-        <v>-61.48</v>
+        <v>-9.99</v>
       </c>
       <c r="N15" s="3">
         <v>-12.65</v>
@@ -1284,9 +1326,12 @@
         <v>-63.67</v>
       </c>
       <c r="R15" s="3">
-        <v>-12.65</v>
-      </c>
-      <c r="S15" t="str">
+        <v>-26.4</v>
+      </c>
+      <c r="S15" s="3">
+        <v>44.76</v>
+      </c>
+      <c r="T15" t="str">
         <v/>
       </c>
     </row>
@@ -1316,7 +1361,7 @@
         <v>17.32</v>
       </c>
       <c r="I16" s="1">
-        <v>2007671</v>
+        <v>2007855</v>
       </c>
       <c r="J16" s="1">
         <v>1529.42</v>
@@ -1328,7 +1373,7 @@
         <v>1859.62</v>
       </c>
       <c r="M16" s="3">
-        <v>122.02</v>
+        <v>31.65</v>
       </c>
       <c r="N16" s="3">
         <v>17.8</v>
@@ -1343,9 +1388,12 @@
         <v>107.02</v>
       </c>
       <c r="R16" s="3">
-        <v>17.8</v>
-      </c>
-      <c r="S16" t="str">
+        <v>85.65</v>
+      </c>
+      <c r="S16" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="T16" t="str">
         <v/>
       </c>
     </row>
@@ -1375,7 +1423,7 @@
         <v>-6.9</v>
       </c>
       <c r="I17" s="1">
-        <v>580157</v>
+        <v>580420</v>
       </c>
       <c r="J17" s="1">
         <v>2248.76</v>
@@ -1387,7 +1435,7 @@
         <v>2104.35</v>
       </c>
       <c r="M17" s="3">
-        <v>-79.29</v>
+        <v>-48.17</v>
       </c>
       <c r="N17" s="3">
         <v>-50.29</v>
@@ -1402,9 +1450,12 @@
         <v>123.63</v>
       </c>
       <c r="R17" s="3">
-        <v>-50.29</v>
-      </c>
-      <c r="S17" t="str">
+        <v>172.14</v>
+      </c>
+      <c r="S17" s="3">
+        <v>38.27</v>
+      </c>
+      <c r="T17" t="str">
         <v/>
       </c>
     </row>
@@ -1434,7 +1485,7 @@
         <v>-7.38</v>
       </c>
       <c r="I18" s="1">
-        <v>936510</v>
+        <v>936830</v>
       </c>
       <c r="J18" s="1">
         <v>1140.39</v>
@@ -1446,7 +1497,7 @@
         <v>1284.56</v>
       </c>
       <c r="M18" s="3">
-        <v>36.77</v>
+        <v>-11.13</v>
       </c>
       <c r="N18" s="3">
         <v>-15.03</v>
@@ -1461,9 +1512,12 @@
         <v>-20.16</v>
       </c>
       <c r="R18" s="3">
-        <v>-15.03</v>
-      </c>
-      <c r="S18" t="str">
+        <v>-12.83</v>
+      </c>
+      <c r="S18" s="3">
+        <v>48.68</v>
+      </c>
+      <c r="T18" t="str">
         <v/>
       </c>
     </row>
@@ -1493,7 +1547,7 @@
         <v>43.76</v>
       </c>
       <c r="I19" s="1">
-        <v>664980</v>
+        <v>665483</v>
       </c>
       <c r="J19" s="1">
         <v>7208.78</v>
@@ -1505,7 +1559,7 @@
         <v>9131.22</v>
       </c>
       <c r="M19" s="3">
-        <v>719.27</v>
+        <v>-1.51</v>
       </c>
       <c r="N19" s="3">
         <v>57.79</v>
@@ -1520,9 +1574,12 @@
         <v>959.64</v>
       </c>
       <c r="R19" s="3">
-        <v>57.79</v>
-      </c>
-      <c r="S19" t="str">
+        <v>699.84</v>
+      </c>
+      <c r="S19" s="3">
+        <v>48.83</v>
+      </c>
+      <c r="T19" t="str">
         <v/>
       </c>
     </row>
@@ -1552,7 +1609,7 @@
         <v>6.99</v>
       </c>
       <c r="I20" s="1">
-        <v>1345603</v>
+        <v>1347163</v>
       </c>
       <c r="J20" s="1">
         <v>463.08</v>
@@ -1564,7 +1621,7 @@
         <v>469.98</v>
       </c>
       <c r="M20" s="3">
-        <v>0.08</v>
+        <v>-6.79</v>
       </c>
       <c r="N20" s="3">
         <v>-7.37</v>
@@ -1579,9 +1636,12 @@
         <v>23.6</v>
       </c>
       <c r="R20" s="3">
-        <v>-7.37</v>
-      </c>
-      <c r="S20" t="str">
+        <v>30.3</v>
+      </c>
+      <c r="S20" s="3">
+        <v>47.07</v>
+      </c>
+      <c r="T20" t="str">
         <v/>
       </c>
     </row>
@@ -1611,7 +1671,7 @@
         <v>14.76</v>
       </c>
       <c r="I21" s="1">
-        <v>13770045</v>
+        <v>13770283</v>
       </c>
       <c r="J21" s="1">
         <v>465.13</v>
@@ -1623,7 +1683,7 @@
         <v>584.92</v>
       </c>
       <c r="M21" s="3">
-        <v>32.47</v>
+        <v>-6.76</v>
       </c>
       <c r="N21" s="3">
         <v>-7.17</v>
@@ -1638,9 +1698,12 @@
         <v>26.14</v>
       </c>
       <c r="R21" s="3">
-        <v>-7.17</v>
-      </c>
-      <c r="S21" t="str">
+        <v>20.67</v>
+      </c>
+      <c r="S21" s="3">
+        <v>45.63</v>
+      </c>
+      <c r="T21" t="str">
         <v/>
       </c>
     </row>
@@ -1670,7 +1733,7 @@
         <v>-14.63</v>
       </c>
       <c r="I22" s="1">
-        <v>11521555</v>
+        <v>11532522</v>
       </c>
       <c r="J22" s="1">
         <v>43.66</v>
@@ -1682,7 +1745,7 @@
         <v>44.36</v>
       </c>
       <c r="M22" s="3">
-        <v>0.45</v>
+        <v>0.04</v>
       </c>
       <c r="N22" s="3">
         <v>-0.07</v>
@@ -1697,9 +1760,12 @@
         <v>0.73</v>
       </c>
       <c r="R22" s="3">
-        <v>-0.07</v>
-      </c>
-      <c r="S22" t="str">
+        <v>1.08</v>
+      </c>
+      <c r="S22" s="3">
+        <v>50.44</v>
+      </c>
+      <c r="T22" t="str">
         <v/>
       </c>
     </row>
@@ -1729,7 +1795,7 @@
         <v>-4.04</v>
       </c>
       <c r="I23" s="1">
-        <v>9122205</v>
+        <v>9126631</v>
       </c>
       <c r="J23" s="1">
         <v>146.62</v>
@@ -1741,7 +1807,7 @@
         <v>138.89</v>
       </c>
       <c r="M23" s="3">
-        <v>-2.48</v>
+        <v>-1.03</v>
       </c>
       <c r="N23" s="3">
         <v>-1.78</v>
@@ -1756,9 +1822,12 @@
         <v>7.64</v>
       </c>
       <c r="R23" s="3">
-        <v>-1.78</v>
-      </c>
-      <c r="S23" t="str">
+        <v>9.72</v>
+      </c>
+      <c r="S23" s="3">
+        <v>55.22</v>
+      </c>
+      <c r="T23" t="str">
         <v/>
       </c>
     </row>
@@ -1788,7 +1857,7 @@
         <v>-10.16</v>
       </c>
       <c r="I24" s="1">
-        <v>8484724</v>
+        <v>8490009</v>
       </c>
       <c r="J24" s="1">
         <v>1894.58</v>
@@ -1800,7 +1869,7 @@
         <v>1857.46</v>
       </c>
       <c r="M24" s="3">
-        <v>-15.16</v>
+        <v>6.32</v>
       </c>
       <c r="N24" s="3">
         <v>-9.02</v>
@@ -1815,9 +1884,12 @@
         <v>104.02</v>
       </c>
       <c r="R24" s="3">
-        <v>-9.02</v>
-      </c>
-      <c r="S24" t="str">
+        <v>149.32</v>
+      </c>
+      <c r="S24" s="3">
+        <v>58.77</v>
+      </c>
+      <c r="T24" t="str">
         <v/>
       </c>
     </row>
@@ -1847,7 +1919,7 @@
         <v>-18.37</v>
       </c>
       <c r="I25" s="1">
-        <v>771462</v>
+        <v>771472</v>
       </c>
       <c r="J25" s="1">
         <v>1863.05</v>
@@ -1859,7 +1931,7 @@
         <v>1735.17</v>
       </c>
       <c r="M25" s="3">
-        <v>-50.05</v>
+        <v>-23.94</v>
       </c>
       <c r="N25" s="3">
         <v>-19.83</v>
@@ -1874,9 +1946,12 @@
         <v>48.62</v>
       </c>
       <c r="R25" s="3">
-        <v>-19.83</v>
-      </c>
-      <c r="S25" t="str">
+        <v>92.28</v>
+      </c>
+      <c r="S25" s="3">
+        <v>40.88</v>
+      </c>
+      <c r="T25" t="str">
         <v/>
       </c>
     </row>
@@ -1906,7 +1981,7 @@
         <v>-29.12</v>
       </c>
       <c r="I26" s="1">
-        <v>1414667</v>
+        <v>1414771</v>
       </c>
       <c r="J26" s="1">
         <v>4537.51</v>
@@ -1918,7 +1993,7 @@
         <v>4352.02</v>
       </c>
       <c r="M26" s="3">
-        <v>-77.62</v>
+        <v>-4.03</v>
       </c>
       <c r="N26" s="3">
         <v>-52.53</v>
@@ -1933,9 +2008,12 @@
         <v>-290.22</v>
       </c>
       <c r="R26" s="3">
-        <v>-52.53</v>
-      </c>
-      <c r="S26" t="str">
+        <v>-192.59</v>
+      </c>
+      <c r="S26" s="3">
+        <v>55.49</v>
+      </c>
+      <c r="T26" t="str">
         <v/>
       </c>
     </row>
@@ -1965,7 +2043,7 @@
         <v>-4.71</v>
       </c>
       <c r="I27" s="1">
-        <v>10452819</v>
+        <v>10453862</v>
       </c>
       <c r="J27" s="1">
         <v>283.07</v>
@@ -1977,7 +2055,7 @@
         <v>262.55</v>
       </c>
       <c r="M27" s="3">
-        <v>-9.6</v>
+        <v>-4.42</v>
       </c>
       <c r="N27" s="3">
         <v>-4.51</v>
@@ -1992,9 +2070,12 @@
         <v>0.18</v>
       </c>
       <c r="R27" s="3">
-        <v>-4.51</v>
-      </c>
-      <c r="S27" t="str">
+        <v>6.51</v>
+      </c>
+      <c r="S27" s="3">
+        <v>42</v>
+      </c>
+      <c r="T27" t="str">
         <v/>
       </c>
     </row>
@@ -2024,7 +2105,7 @@
         <v>18.37</v>
       </c>
       <c r="I28" s="1">
-        <v>20883647</v>
+        <v>20884095</v>
       </c>
       <c r="J28" s="1">
         <v>175.38</v>
@@ -2036,7 +2117,7 @@
         <v>179.77</v>
       </c>
       <c r="M28" s="3">
-        <v>1.81</v>
+        <v>-0.43</v>
       </c>
       <c r="N28" s="3">
         <v>-1.78</v>
@@ -2051,9 +2132,12 @@
         <v>15.99</v>
       </c>
       <c r="R28" s="3">
-        <v>-1.78</v>
-      </c>
-      <c r="S28" t="str">
+        <v>15.92</v>
+      </c>
+      <c r="S28" s="3">
+        <v>59.99</v>
+      </c>
+      <c r="T28" t="str">
         <v/>
       </c>
     </row>
@@ -2083,7 +2167,7 @@
         <v>-23.01</v>
       </c>
       <c r="I29" s="1">
-        <v>16905508</v>
+        <v>16912477</v>
       </c>
       <c r="J29" s="1">
         <v>1341.79</v>
@@ -2095,7 +2179,7 @@
         <v>1255.53</v>
       </c>
       <c r="M29" s="3">
-        <v>-44.55</v>
+        <v>-15.5</v>
       </c>
       <c r="N29" s="3">
         <v>-21.72</v>
@@ -2110,9 +2194,12 @@
         <v>-26.91</v>
       </c>
       <c r="R29" s="3">
-        <v>-21.72</v>
-      </c>
-      <c r="S29" t="str">
+        <v>2.87</v>
+      </c>
+      <c r="S29" s="3">
+        <v>48.45</v>
+      </c>
+      <c r="T29" t="str">
         <v/>
       </c>
     </row>
@@ -2142,7 +2229,7 @@
         <v>-0.87</v>
       </c>
       <c r="I30" s="1">
-        <v>30117420</v>
+        <v>30119715</v>
       </c>
       <c r="J30" s="1">
         <v>114.21</v>
@@ -2154,7 +2241,7 @@
         <v>116.1</v>
       </c>
       <c r="M30" s="3">
-        <v>1.68</v>
+        <v>1.15</v>
       </c>
       <c r="N30" s="3">
         <v>0.33</v>
@@ -2169,9 +2256,12 @@
         <v>4.93</v>
       </c>
       <c r="R30" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="S30" t="str">
+        <v>5.88</v>
+      </c>
+      <c r="S30" s="3">
+        <v>63.98</v>
+      </c>
+      <c r="T30" t="str">
         <v/>
       </c>
     </row>
@@ -2201,7 +2291,7 @@
         <v>33.51</v>
       </c>
       <c r="I31" s="1">
-        <v>195039</v>
+        <v>195145</v>
       </c>
       <c r="J31" s="1">
         <v>9383.88</v>
@@ -2213,7 +2303,7 @@
         <v>11297.56</v>
       </c>
       <c r="M31" s="3">
-        <v>376.12</v>
+        <v>-287.7</v>
       </c>
       <c r="N31" s="3">
         <v>-293.05</v>
@@ -2228,9 +2318,12 @@
         <v>847.66</v>
       </c>
       <c r="R31" s="3">
-        <v>-293.05</v>
-      </c>
-      <c r="S31" t="str">
+        <v>672.54</v>
+      </c>
+      <c r="S31" s="3">
+        <v>38.64</v>
+      </c>
+      <c r="T31" t="str">
         <v/>
       </c>
     </row>
@@ -2260,7 +2353,7 @@
         <v>3.84</v>
       </c>
       <c r="I32" s="1">
-        <v>3473847</v>
+        <v>3474028</v>
       </c>
       <c r="J32" s="1">
         <v>282.42</v>
@@ -2272,7 +2365,7 @@
         <v>288.52</v>
       </c>
       <c r="M32" s="3">
-        <v>3.71</v>
+        <v>1.9</v>
       </c>
       <c r="N32" s="3">
         <v>1.5</v>
@@ -2287,9 +2380,12 @@
         <v>0.87</v>
       </c>
       <c r="R32" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="S32" t="str">
+        <v>1.35</v>
+      </c>
+      <c r="S32" s="3">
+        <v>56.58</v>
+      </c>
+      <c r="T32" t="str">
         <v/>
       </c>
     </row>
@@ -2319,7 +2415,7 @@
         <v>-34.99</v>
       </c>
       <c r="I33" s="1">
-        <v>19855183</v>
+        <v>19856272</v>
       </c>
       <c r="J33" s="1">
         <v>295.35</v>
@@ -2331,7 +2427,7 @@
         <v>266.14</v>
       </c>
       <c r="M33" s="3">
-        <v>-13.63</v>
+        <v>-1.37</v>
       </c>
       <c r="N33" s="3">
         <v>-1.53</v>
@@ -2346,9 +2442,12 @@
         <v>-41.09</v>
       </c>
       <c r="R33" s="3">
-        <v>-1.53</v>
-      </c>
-      <c r="S33" t="str">
+        <v>-29.51</v>
+      </c>
+      <c r="S33" s="3">
+        <v>47.91</v>
+      </c>
+      <c r="T33" t="str">
         <v/>
       </c>
     </row>
@@ -2378,7 +2477,7 @@
         <v>-18.57</v>
       </c>
       <c r="I34" s="1">
-        <v>656420</v>
+        <v>656423</v>
       </c>
       <c r="J34" s="1">
         <v>1101.09</v>
@@ -2390,7 +2489,7 @@
         <v>1010.14</v>
       </c>
       <c r="M34" s="3">
-        <v>-42.36</v>
+        <v>-9.92</v>
       </c>
       <c r="N34" s="3">
         <v>-14.06</v>
@@ -2405,9 +2504,12 @@
         <v>1.17</v>
       </c>
       <c r="R34" s="3">
-        <v>-14.06</v>
-      </c>
-      <c r="S34" t="str">
+        <v>27.55</v>
+      </c>
+      <c r="S34" s="3">
+        <v>45.3</v>
+      </c>
+      <c r="T34" t="str">
         <v/>
       </c>
     </row>
@@ -2449,7 +2551,7 @@
         <v>3162.84</v>
       </c>
       <c r="M35" s="3">
-        <v>7.47</v>
+        <v>-85.2</v>
       </c>
       <c r="N35" s="3">
         <v>-84.75</v>
@@ -2464,9 +2566,12 @@
         <v>186.42</v>
       </c>
       <c r="R35" s="3">
-        <v>-84.75</v>
-      </c>
-      <c r="S35" t="str">
+        <v>191.77</v>
+      </c>
+      <c r="S35" s="3">
+        <v>35.97</v>
+      </c>
+      <c r="T35" t="str">
         <v/>
       </c>
     </row>
@@ -2496,7 +2601,7 @@
         <v>22.2</v>
       </c>
       <c r="I36" s="1">
-        <v>732418</v>
+        <v>732436</v>
       </c>
       <c r="J36" s="1">
         <v>1023.87</v>
@@ -2508,7 +2613,7 @@
         <v>1144.75</v>
       </c>
       <c r="M36" s="3">
-        <v>34.24</v>
+        <v>-7.78</v>
       </c>
       <c r="N36" s="3">
         <v>-3.43</v>
@@ -2523,9 +2628,12 @@
         <v>72.93</v>
       </c>
       <c r="R36" s="3">
-        <v>-3.43</v>
-      </c>
-      <c r="S36" t="str">
+        <v>60.39</v>
+      </c>
+      <c r="S36" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="T36" t="str">
         <v/>
       </c>
     </row>
@@ -2555,7 +2663,7 @@
         <v>15.31</v>
       </c>
       <c r="I37" s="1">
-        <v>15112670</v>
+        <v>15118843</v>
       </c>
       <c r="J37" s="1">
         <v>170.56</v>
@@ -2567,7 +2675,7 @@
         <v>179.27</v>
       </c>
       <c r="M37" s="3">
-        <v>1.88</v>
+        <v>-3.06</v>
       </c>
       <c r="N37" s="3">
         <v>-2.52</v>
@@ -2582,9 +2690,12 @@
         <v>16.83</v>
       </c>
       <c r="R37" s="3">
-        <v>-2.52</v>
-      </c>
-      <c r="S37" t="str">
+        <v>15.15</v>
+      </c>
+      <c r="S37" s="3">
+        <v>41.28</v>
+      </c>
+      <c r="T37" t="str">
         <v/>
       </c>
     </row>
@@ -2614,7 +2725,7 @@
         <v>3.14</v>
       </c>
       <c r="I38" s="1">
-        <v>16393703</v>
+        <v>16394963</v>
       </c>
       <c r="J38" s="1">
         <v>1353.68</v>
@@ -2626,7 +2737,7 @@
         <v>1381.97</v>
       </c>
       <c r="M38" s="3">
-        <v>5.7</v>
+        <v>2.01</v>
       </c>
       <c r="N38" s="3">
         <v>-6.97</v>
@@ -2641,9 +2752,12 @@
         <v>51.75</v>
       </c>
       <c r="R38" s="3">
-        <v>-6.97</v>
-      </c>
-      <c r="S38" t="str">
+        <v>63.02</v>
+      </c>
+      <c r="S38" s="3">
+        <v>55.74</v>
+      </c>
+      <c r="T38" t="str">
         <v/>
       </c>
     </row>
@@ -2673,7 +2787,7 @@
         <v>-6.14</v>
       </c>
       <c r="I39" s="1">
-        <v>7701653</v>
+        <v>7704368</v>
       </c>
       <c r="J39" s="1">
         <v>255.83</v>
@@ -2685,7 +2799,7 @@
         <v>232.19</v>
       </c>
       <c r="M39" s="3">
-        <v>-9.57</v>
+        <v>-2.81</v>
       </c>
       <c r="N39" s="3">
         <v>-3.26</v>
@@ -2700,9 +2814,12 @@
         <v>0.64</v>
       </c>
       <c r="R39" s="3">
-        <v>-3.26</v>
-      </c>
-      <c r="S39" t="str">
+        <v>7.03</v>
+      </c>
+      <c r="S39" s="3">
+        <v>46.23</v>
+      </c>
+      <c r="T39" t="str">
         <v/>
       </c>
     </row>
@@ -2732,7 +2849,7 @@
         <v>2.6</v>
       </c>
       <c r="I40" s="1">
-        <v>1397699</v>
+        <v>1398806</v>
       </c>
       <c r="J40" s="1">
         <v>864.78</v>
@@ -2744,7 +2861,7 @@
         <v>853.85</v>
       </c>
       <c r="M40" s="3">
-        <v>-2.19</v>
+        <v>1.35</v>
       </c>
       <c r="N40" s="3">
         <v>-5.19</v>
@@ -2759,9 +2876,12 @@
         <v>87.66</v>
       </c>
       <c r="R40" s="3">
-        <v>-5.19</v>
-      </c>
-      <c r="S40" t="str">
+        <v>99.41</v>
+      </c>
+      <c r="S40" s="3">
+        <v>57.17</v>
+      </c>
+      <c r="T40" t="str">
         <v/>
       </c>
     </row>
@@ -2791,7 +2911,7 @@
         <v>-8.93</v>
       </c>
       <c r="I41" s="1">
-        <v>273302</v>
+        <v>273304</v>
       </c>
       <c r="J41" s="1">
         <v>5462.07</v>
@@ -2803,7 +2923,7 @@
         <v>5280.87</v>
       </c>
       <c r="M41" s="3">
-        <v>-91.31</v>
+        <v>-64.04</v>
       </c>
       <c r="N41" s="3">
         <v>-40.38</v>
@@ -2818,9 +2938,12 @@
         <v>124.36</v>
       </c>
       <c r="R41" s="3">
-        <v>-40.38</v>
-      </c>
-      <c r="S41" t="str">
+        <v>213.97</v>
+      </c>
+      <c r="S41" s="3">
+        <v>37.14</v>
+      </c>
+      <c r="T41" t="str">
         <v/>
       </c>
     </row>
@@ -2862,7 +2985,7 @@
         <v>1577.31</v>
       </c>
       <c r="M42" s="3">
-        <v>1.6</v>
+        <v>-22.32</v>
       </c>
       <c r="N42" s="3">
         <v>-26.95</v>
@@ -2877,9 +3000,12 @@
         <v>31.89</v>
       </c>
       <c r="R42" s="3">
-        <v>-26.95</v>
-      </c>
-      <c r="S42" t="str">
+        <v>31.17</v>
+      </c>
+      <c r="S42" s="3">
+        <v>41.7</v>
+      </c>
+      <c r="T42" t="str">
         <v/>
       </c>
     </row>
@@ -2909,7 +3035,7 @@
         <v>-2.12</v>
       </c>
       <c r="I43" s="1">
-        <v>1146756</v>
+        <v>1146816</v>
       </c>
       <c r="J43" s="1">
         <v>1243.65</v>
@@ -2921,7 +3047,7 @@
         <v>1190.35</v>
       </c>
       <c r="M43" s="3">
-        <v>-12.94</v>
+        <v>13.32</v>
       </c>
       <c r="N43" s="3">
         <v>10.71</v>
@@ -2936,9 +3062,12 @@
         <v>13.96</v>
       </c>
       <c r="R43" s="3">
-        <v>10.71</v>
-      </c>
-      <c r="S43" t="str">
+        <v>25.99</v>
+      </c>
+      <c r="S43" s="3">
+        <v>60.37</v>
+      </c>
+      <c r="T43" t="str">
         <v/>
       </c>
     </row>
@@ -2968,7 +3097,7 @@
         <v>-24.73</v>
       </c>
       <c r="I44" s="1">
-        <v>824371</v>
+        <v>826101</v>
       </c>
       <c r="J44" s="1">
         <v>442.57</v>
@@ -2980,7 +3109,7 @@
         <v>387.69</v>
       </c>
       <c r="M44" s="3">
-        <v>-20.16</v>
+        <v>-1.96</v>
       </c>
       <c r="N44" s="3">
         <v>-2.38</v>
@@ -2995,9 +3124,12 @@
         <v>-38.27</v>
       </c>
       <c r="R44" s="3">
-        <v>-2.38</v>
-      </c>
-      <c r="S44" t="str">
+        <v>-28.08</v>
+      </c>
+      <c r="S44" s="3">
+        <v>46.2</v>
+      </c>
+      <c r="T44" t="str">
         <v/>
       </c>
     </row>
@@ -3027,7 +3159,7 @@
         <v>1.48</v>
       </c>
       <c r="I45" s="1">
-        <v>2141165</v>
+        <v>2141167</v>
       </c>
       <c r="J45" s="1">
         <v>1807.75</v>
@@ -3039,7 +3171,7 @@
         <v>1857.93</v>
       </c>
       <c r="M45" s="3">
-        <v>-6.61</v>
+        <v>-33.45</v>
       </c>
       <c r="N45" s="3">
         <v>-31.95</v>
@@ -3054,9 +3186,12 @@
         <v>91.34</v>
       </c>
       <c r="R45" s="3">
-        <v>-31.95</v>
-      </c>
-      <c r="S45" t="str">
+        <v>102.3</v>
+      </c>
+      <c r="S45" s="3">
+        <v>35.1</v>
+      </c>
+      <c r="T45" t="str">
         <v/>
       </c>
     </row>
@@ -3098,7 +3233,7 @@
         <v>23163.4</v>
       </c>
       <c r="M46" s="3">
-        <v>-937.98</v>
+        <v>-236.7</v>
       </c>
       <c r="N46" s="3">
         <v>-367.21</v>
@@ -3113,9 +3248,12 @@
         <v>-983.34</v>
       </c>
       <c r="R46" s="3">
-        <v>-367.21</v>
-      </c>
-      <c r="S46" t="str">
+        <v>-384.07</v>
+      </c>
+      <c r="S46" s="3">
+        <v>47.23</v>
+      </c>
+      <c r="T46" t="str">
         <v/>
       </c>
     </row>
@@ -3145,7 +3283,7 @@
         <v>-15.22</v>
       </c>
       <c r="I47" s="1">
-        <v>6282959</v>
+        <v>6293238</v>
       </c>
       <c r="J47" s="1">
         <v>344.57</v>
@@ -3157,7 +3295,7 @@
         <v>315.38</v>
       </c>
       <c r="M47" s="3">
-        <v>-14.33</v>
+        <v>-3.02</v>
       </c>
       <c r="N47" s="3">
         <v>-4.67</v>
@@ -3172,9 +3310,12 @@
         <v>-16.85</v>
       </c>
       <c r="R47" s="3">
-        <v>-4.67</v>
-      </c>
-      <c r="S47" t="str">
+        <v>-6.48</v>
+      </c>
+      <c r="S47" s="3">
+        <v>45.31</v>
+      </c>
+      <c r="T47" t="str">
         <v/>
       </c>
     </row>
@@ -3204,7 +3345,7 @@
         <v>-2.88</v>
       </c>
       <c r="I48" s="1">
-        <v>5154328</v>
+        <v>5154360</v>
       </c>
       <c r="J48" s="1">
         <v>166.11</v>
@@ -3216,7 +3357,7 @@
         <v>172.12</v>
       </c>
       <c r="M48" s="3">
-        <v>0.6</v>
+        <v>-1.44</v>
       </c>
       <c r="N48" s="3">
         <v>-1.33</v>
@@ -3231,9 +3372,12 @@
         <v>0.15</v>
       </c>
       <c r="R48" s="3">
-        <v>-1.33</v>
-      </c>
-      <c r="S48" t="str">
+        <v>1.55</v>
+      </c>
+      <c r="S48" s="3">
+        <v>42.65</v>
+      </c>
+      <c r="T48" t="str">
         <v/>
       </c>
     </row>
@@ -3263,7 +3407,7 @@
         <v>-7.27</v>
       </c>
       <c r="I49" s="1">
-        <v>3645391</v>
+        <v>3648211</v>
       </c>
       <c r="J49" s="1">
         <v>384.1</v>
@@ -3275,7 +3419,7 @@
         <v>362.89</v>
       </c>
       <c r="M49" s="3">
-        <v>-11.04</v>
+        <v>-4</v>
       </c>
       <c r="N49" s="3">
         <v>-4.93</v>
@@ -3290,9 +3434,12 @@
         <v>3.2</v>
       </c>
       <c r="R49" s="3">
-        <v>-4.93</v>
-      </c>
-      <c r="S49" t="str">
+        <v>12.13</v>
+      </c>
+      <c r="S49" s="3">
+        <v>46.41</v>
+      </c>
+      <c r="T49" t="str">
         <v/>
       </c>
     </row>
@@ -3322,7 +3469,7 @@
         <v>18.28</v>
       </c>
       <c r="I50" s="1">
-        <v>268181</v>
+        <v>268242</v>
       </c>
       <c r="J50" s="1">
         <v>4486.94</v>
@@ -3334,7 +3481,7 @@
         <v>4854.17</v>
       </c>
       <c r="M50" s="3">
-        <v>91.31</v>
+        <v>-92.32</v>
       </c>
       <c r="N50" s="3">
         <v>-74.66</v>
@@ -3349,9 +3496,12 @@
         <v>518.84</v>
       </c>
       <c r="R50" s="3">
-        <v>-74.66</v>
-      </c>
-      <c r="S50" t="str">
+        <v>486.99</v>
+      </c>
+      <c r="S50" s="3">
+        <v>32.47</v>
+      </c>
+      <c r="T50" t="str">
         <v/>
       </c>
     </row>
@@ -3381,7 +3531,7 @@
         <v>-20.11</v>
       </c>
       <c r="I51" s="1">
-        <v>564307</v>
+        <v>565003</v>
       </c>
       <c r="J51" s="1">
         <v>2161.09</v>
@@ -3393,7 +3543,7 @@
         <v>1952.04</v>
       </c>
       <c r="M51" s="3">
-        <v>-97.19</v>
+        <v>-25.49</v>
       </c>
       <c r="N51" s="3">
         <v>-30.09</v>
@@ -3408,9 +3558,12 @@
         <v>-136.38</v>
       </c>
       <c r="R51" s="3">
-        <v>-30.09</v>
-      </c>
-      <c r="S51" t="str">
+        <v>-85.54</v>
+      </c>
+      <c r="S51" s="3">
+        <v>41.1</v>
+      </c>
+      <c r="T51" t="str">
         <v/>
       </c>
     </row>
@@ -3440,7 +3593,7 @@
         <v>20.44</v>
       </c>
       <c r="I52" s="1">
-        <v>607046</v>
+        <v>607209</v>
       </c>
       <c r="J52" s="1">
         <v>1003.95</v>
@@ -3452,7 +3605,7 @@
         <v>1149.71</v>
       </c>
       <c r="M52" s="3">
-        <v>45.66</v>
+        <v>9.58</v>
       </c>
       <c r="N52" s="3">
         <v>7.48</v>
@@ -3467,9 +3620,12 @@
         <v>82.03</v>
       </c>
       <c r="R52" s="3">
-        <v>7.48</v>
-      </c>
-      <c r="S52" t="str">
+        <v>65.47</v>
+      </c>
+      <c r="S52" s="3">
+        <v>49.47</v>
+      </c>
+      <c r="T52" t="str">
         <v/>
       </c>
     </row>
@@ -3499,7 +3655,7 @@
         <v>3.34</v>
       </c>
       <c r="I53" s="1">
-        <v>1641985</v>
+        <v>1642535</v>
       </c>
       <c r="J53" s="1">
         <v>800.45</v>
@@ -3511,7 +3667,7 @@
         <v>817.2</v>
       </c>
       <c r="M53" s="3">
-        <v>-2.54</v>
+        <v>-10.69</v>
       </c>
       <c r="N53" s="3">
         <v>-10.81</v>
@@ -3526,9 +3682,12 @@
         <v>50.14</v>
       </c>
       <c r="R53" s="3">
-        <v>-10.81</v>
-      </c>
-      <c r="S53" t="str">
+        <v>52.19</v>
+      </c>
+      <c r="S53" s="3">
+        <v>37.4</v>
+      </c>
+      <c r="T53" t="str">
         <v/>
       </c>
     </row>
@@ -3558,7 +3717,7 @@
         <v>-8.28</v>
       </c>
       <c r="I54" s="1">
-        <v>9107106</v>
+        <v>9107843</v>
       </c>
       <c r="J54" s="1">
         <v>411.05</v>
@@ -3570,7 +3729,7 @@
         <v>404.36</v>
       </c>
       <c r="M54" s="3">
-        <v>-5.43</v>
+        <v>-3.33</v>
       </c>
       <c r="N54" s="3">
         <v>-4.24</v>
@@ -3585,9 +3744,12 @@
         <v>-6.93</v>
       </c>
       <c r="R54" s="3">
-        <v>-4.24</v>
-      </c>
-      <c r="S54" t="str">
+        <v>-2.52</v>
+      </c>
+      <c r="S54" s="3">
+        <v>45.21</v>
+      </c>
+      <c r="T54" t="str">
         <v/>
       </c>
     </row>
@@ -3629,7 +3791,7 @@
         <v>23479.08</v>
       </c>
       <c r="M55" s="3">
-        <v>-384.19</v>
+        <v>-170.52</v>
       </c>
       <c r="N55" s="3">
         <v>-253.14</v>
@@ -3644,9 +3806,12 @@
         <v>194.04</v>
       </c>
       <c r="R55" s="3">
-        <v>-253.14</v>
-      </c>
-      <c r="S55" t="str">
+        <v>599.66</v>
+      </c>
+      <c r="S55" s="3">
+        <v>46.27</v>
+      </c>
+      <c r="T55" t="str">
         <v/>
       </c>
     </row>
@@ -3676,7 +3841,7 @@
         <v>-30.41</v>
       </c>
       <c r="I56" s="1">
-        <v>4539672</v>
+        <v>4542790</v>
       </c>
       <c r="J56" s="1">
         <v>390.2</v>
@@ -3688,7 +3853,7 @@
         <v>356.65</v>
       </c>
       <c r="M56" s="3">
-        <v>-14.56</v>
+        <v>-4.1</v>
       </c>
       <c r="N56" s="3">
         <v>-6.12</v>
@@ -3703,9 +3868,12 @@
         <v>7.36</v>
       </c>
       <c r="R56" s="3">
-        <v>-6.12</v>
-      </c>
-      <c r="S56" t="str">
+        <v>22.32</v>
+      </c>
+      <c r="S56" s="3">
+        <v>50.19</v>
+      </c>
+      <c r="T56" t="str">
         <v/>
       </c>
     </row>
@@ -3735,7 +3903,7 @@
         <v>-19.78</v>
       </c>
       <c r="I57" s="1">
-        <v>12773295</v>
+        <v>12773489</v>
       </c>
       <c r="J57" s="1">
         <v>266.74</v>
@@ -3747,7 +3915,7 @@
         <v>237.78</v>
       </c>
       <c r="M57" s="3">
-        <v>-9.5</v>
+        <v>-0.75</v>
       </c>
       <c r="N57" s="3">
         <v>-1.5</v>
@@ -3762,9 +3930,12 @@
         <v>4.18</v>
       </c>
       <c r="R57" s="3">
-        <v>-1.5</v>
-      </c>
-      <c r="S57" t="str">
+        <v>11.7</v>
+      </c>
+      <c r="S57" s="3">
+        <v>53.82</v>
+      </c>
+      <c r="T57" t="str">
         <v/>
       </c>
     </row>
@@ -3794,7 +3965,7 @@
         <v>-22.34</v>
       </c>
       <c r="I58" s="1">
-        <v>250349</v>
+        <v>250350</v>
       </c>
       <c r="J58" s="1">
         <v>5486.52</v>
@@ -3806,7 +3977,7 @@
         <v>5090.41</v>
       </c>
       <c r="M58" s="3">
-        <v>-208.73</v>
+        <v>-87.89</v>
       </c>
       <c r="N58" s="3">
         <v>-91.54</v>
@@ -3821,9 +3992,12 @@
         <v>-37.46</v>
       </c>
       <c r="R58" s="3">
-        <v>-91.54</v>
-      </c>
-      <c r="S58" t="str">
+        <v>113.38</v>
+      </c>
+      <c r="S58" s="3">
+        <v>35.85</v>
+      </c>
+      <c r="T58" t="str">
         <v/>
       </c>
     </row>
@@ -3853,7 +4027,7 @@
         <v>-16.25</v>
       </c>
       <c r="I59" s="1">
-        <v>441346</v>
+        <v>441384</v>
       </c>
       <c r="J59" s="1">
         <v>2536.9</v>
@@ -3865,7 +4039,7 @@
         <v>2501</v>
       </c>
       <c r="M59" s="3">
-        <v>-58.8</v>
+        <v>-47.5</v>
       </c>
       <c r="N59" s="3">
         <v>-50.09</v>
@@ -3880,9 +4054,12 @@
         <v>-59.08</v>
       </c>
       <c r="R59" s="3">
-        <v>-50.09</v>
-      </c>
-      <c r="S59" t="str">
+        <v>-68.62</v>
+      </c>
+      <c r="S59" s="3">
+        <v>36.52</v>
+      </c>
+      <c r="T59" t="str">
         <v/>
       </c>
     </row>
@@ -3912,7 +4089,7 @@
         <v>-22.14</v>
       </c>
       <c r="I60" s="1">
-        <v>13075731</v>
+        <v>13077129</v>
       </c>
       <c r="J60" s="1">
         <v>146.61</v>
@@ -3924,7 +4101,7 @@
         <v>134.79</v>
       </c>
       <c r="M60" s="3">
-        <v>-4.5</v>
+        <v>-1.9</v>
       </c>
       <c r="N60" s="3">
         <v>-2.15</v>
@@ -3939,9 +4116,12 @@
         <v>0.51</v>
       </c>
       <c r="R60" s="3">
-        <v>-2.15</v>
-      </c>
-      <c r="S60" t="str">
+        <v>4.59</v>
+      </c>
+      <c r="S60" s="3">
+        <v>44.4</v>
+      </c>
+      <c r="T60" t="str">
         <v/>
       </c>
     </row>
@@ -3983,7 +4163,7 @@
         <v>1906.01</v>
       </c>
       <c r="M61" s="3">
-        <v>24.96</v>
+        <v>-9.89</v>
       </c>
       <c r="N61" s="3">
         <v>-10.99</v>
@@ -3998,9 +4178,12 @@
         <v>135.85</v>
       </c>
       <c r="R61" s="3">
-        <v>-10.99</v>
-      </c>
-      <c r="S61" t="str">
+        <v>133.93</v>
+      </c>
+      <c r="S61" s="3">
+        <v>46.97</v>
+      </c>
+      <c r="T61" t="str">
         <v/>
       </c>
     </row>
@@ -4030,7 +4213,7 @@
         <v>-35.31</v>
       </c>
       <c r="I62" s="1">
-        <v>1171081</v>
+        <v>1173961</v>
       </c>
       <c r="J62" s="1">
         <v>445.2</v>
@@ -4042,7 +4225,7 @@
         <v>388.82</v>
       </c>
       <c r="M62" s="3">
-        <v>-26.71</v>
+        <v>-10.14</v>
       </c>
       <c r="N62" s="3">
         <v>-11.97</v>
@@ -4057,9 +4240,12 @@
         <v>-38.33</v>
       </c>
       <c r="R62" s="3">
-        <v>-11.97</v>
-      </c>
-      <c r="S62" t="str">
+        <v>-19.5</v>
+      </c>
+      <c r="S62" s="3">
+        <v>42.57</v>
+      </c>
+      <c r="T62" t="str">
         <v/>
       </c>
     </row>
@@ -4089,7 +4275,7 @@
         <v>31.12</v>
       </c>
       <c r="I63" s="1">
-        <v>12753456</v>
+        <v>12754135</v>
       </c>
       <c r="J63" s="1">
         <v>138.25</v>
@@ -4101,7 +4287,7 @@
         <v>163.11</v>
       </c>
       <c r="M63" s="3">
-        <v>7.41</v>
+        <v>-0.93</v>
       </c>
       <c r="N63" s="3">
         <v>-0.98</v>
@@ -4116,9 +4302,12 @@
         <v>17.67</v>
       </c>
       <c r="R63" s="3">
-        <v>-0.98</v>
-      </c>
-      <c r="S63" t="str">
+        <v>13.47</v>
+      </c>
+      <c r="S63" s="3">
+        <v>45.61</v>
+      </c>
+      <c r="T63" t="str">
         <v/>
       </c>
     </row>
@@ -4148,7 +4337,7 @@
         <v>-15.41</v>
       </c>
       <c r="I64" s="1">
-        <v>328399</v>
+        <v>328498</v>
       </c>
       <c r="J64" s="1">
         <v>2042.89</v>
@@ -4160,7 +4349,7 @@
         <v>2122.18</v>
       </c>
       <c r="M64" s="3">
-        <v>-5.23</v>
+        <v>-47.95</v>
       </c>
       <c r="N64" s="3">
         <v>-48.93</v>
@@ -4175,9 +4364,12 @@
         <v>25.61</v>
       </c>
       <c r="R64" s="3">
-        <v>-48.93</v>
-      </c>
-      <c r="S64" t="str">
+        <v>50.05</v>
+      </c>
+      <c r="S64" s="3">
+        <v>36.47</v>
+      </c>
+      <c r="T64" t="str">
         <v/>
       </c>
     </row>
@@ -4207,7 +4399,7 @@
         <v>-17.15</v>
       </c>
       <c r="I65" s="1">
-        <v>1263080</v>
+        <v>1263150</v>
       </c>
       <c r="J65" s="1">
         <v>1868.33</v>
@@ -4219,7 +4411,7 @@
         <v>1879.37</v>
       </c>
       <c r="M65" s="3">
-        <v>-33.78</v>
+        <v>-46.11</v>
       </c>
       <c r="N65" s="3">
         <v>-48.95</v>
@@ -4234,9 +4426,12 @@
         <v>18.43</v>
       </c>
       <c r="R65" s="3">
-        <v>-48.95</v>
-      </c>
-      <c r="S65" t="str">
+        <v>53.77</v>
+      </c>
+      <c r="S65" s="3">
+        <v>32.01</v>
+      </c>
+      <c r="T65" t="str">
         <v/>
       </c>
     </row>
@@ -4266,7 +4461,7 @@
         <v>-16.42</v>
       </c>
       <c r="I66" s="1">
-        <v>513031</v>
+        <v>513070</v>
       </c>
       <c r="J66" s="1">
         <v>1750.91</v>
@@ -4278,7 +4473,7 @@
         <v>1576.78</v>
       </c>
       <c r="M66" s="3">
-        <v>-49.79</v>
+        <v>34.31</v>
       </c>
       <c r="N66" s="3">
         <v>28.88</v>
@@ -4293,9 +4488,12 @@
         <v>-23.77</v>
       </c>
       <c r="R66" s="3">
-        <v>28.88</v>
-      </c>
-      <c r="S66" t="str">
+        <v>23</v>
+      </c>
+      <c r="S66" s="3">
+        <v>54.82</v>
+      </c>
+      <c r="T66" t="str">
         <v/>
       </c>
     </row>
@@ -4325,7 +4523,7 @@
         <v>-22.11</v>
       </c>
       <c r="I67" s="1">
-        <v>2257224</v>
+        <v>2257306</v>
       </c>
       <c r="J67" s="1">
         <v>3233.14</v>
@@ -4337,7 +4535,7 @@
         <v>3124.3</v>
       </c>
       <c r="M67" s="3">
-        <v>-91.98</v>
+        <v>-66.64</v>
       </c>
       <c r="N67" s="3">
         <v>-85.6</v>
@@ -4352,9 +4550,12 @@
         <v>155.83</v>
       </c>
       <c r="R67" s="3">
-        <v>-85.6</v>
-      </c>
-      <c r="S67" t="str">
+        <v>256.94</v>
+      </c>
+      <c r="S67" s="3">
+        <v>43.49</v>
+      </c>
+      <c r="T67" t="str">
         <v/>
       </c>
     </row>
@@ -4384,7 +4585,7 @@
         <v>-18.11</v>
       </c>
       <c r="I68" s="1">
-        <v>7685596</v>
+        <v>7685914</v>
       </c>
       <c r="J68" s="1">
         <v>170.22</v>
@@ -4396,7 +4597,7 @@
         <v>162.78</v>
       </c>
       <c r="M68" s="3">
-        <v>-3.74</v>
+        <v>-4.42</v>
       </c>
       <c r="N68" s="3">
         <v>-4.71</v>
@@ -4411,9 +4612,12 @@
         <v>13.72</v>
       </c>
       <c r="R68" s="3">
-        <v>-4.71</v>
-      </c>
-      <c r="S68" t="str">
+        <v>16.89</v>
+      </c>
+      <c r="S68" s="3">
+        <v>37.79</v>
+      </c>
+      <c r="T68" t="str">
         <v/>
       </c>
     </row>
@@ -4443,7 +4647,7 @@
         <v>-10.96</v>
       </c>
       <c r="I69" s="1">
-        <v>1855497</v>
+        <v>1857648</v>
       </c>
       <c r="J69" s="1">
         <v>3945.3</v>
@@ -4455,7 +4659,7 @@
         <v>3889.71</v>
       </c>
       <c r="M69" s="3">
-        <v>-67.04</v>
+        <v>-72.58</v>
       </c>
       <c r="N69" s="3">
         <v>-72.44</v>
@@ -4470,9 +4674,12 @@
         <v>151.84</v>
       </c>
       <c r="R69" s="3">
-        <v>-72.44</v>
-      </c>
-      <c r="S69" t="str">
+        <v>215.2</v>
+      </c>
+      <c r="S69" s="3">
+        <v>38.72</v>
+      </c>
+      <c r="T69" t="str">
         <v/>
       </c>
     </row>
@@ -4502,7 +4709,7 @@
         <v>-28.68</v>
       </c>
       <c r="I70" s="1">
-        <v>24894172</v>
+        <v>24897649</v>
       </c>
       <c r="J70" s="1">
         <v>799.74</v>
@@ -4514,7 +4721,7 @@
         <v>717.59</v>
       </c>
       <c r="M70" s="3">
-        <v>-28.78</v>
+        <v>-2.04</v>
       </c>
       <c r="N70" s="3">
         <v>-2.69</v>
@@ -4529,9 +4736,12 @@
         <v>-37.97</v>
       </c>
       <c r="R70" s="3">
-        <v>-2.69</v>
-      </c>
-      <c r="S70" t="str">
+        <v>-9.51</v>
+      </c>
+      <c r="S70" s="3">
+        <v>45.95</v>
+      </c>
+      <c r="T70" t="str">
         <v/>
       </c>
     </row>
@@ -4561,7 +4771,7 @@
         <v>7.81</v>
       </c>
       <c r="I71" s="1">
-        <v>529386</v>
+        <v>529389</v>
       </c>
       <c r="J71" s="1">
         <v>2216.15</v>
@@ -4573,7 +4783,7 @@
         <v>2360.35</v>
       </c>
       <c r="M71" s="3">
-        <v>31.79</v>
+        <v>-46.63</v>
       </c>
       <c r="N71" s="3">
         <v>-35.12</v>
@@ -4588,9 +4798,12 @@
         <v>267.73</v>
       </c>
       <c r="R71" s="3">
-        <v>-35.12</v>
-      </c>
-      <c r="S71" t="str">
+        <v>281.79</v>
+      </c>
+      <c r="S71" s="3">
+        <v>36.37</v>
+      </c>
+      <c r="T71" t="str">
         <v/>
       </c>
     </row>
@@ -4620,7 +4833,7 @@
         <v>-13.06</v>
       </c>
       <c r="I72" s="1">
-        <v>1129692</v>
+        <v>1129693</v>
       </c>
       <c r="J72" s="1">
         <v>1369.79</v>
@@ -4632,7 +4845,7 @@
         <v>1384.23</v>
       </c>
       <c r="M72" s="3">
-        <v>-16.1</v>
+        <v>-19.6</v>
       </c>
       <c r="N72" s="3">
         <v>-20.21</v>
@@ -4647,9 +4860,12 @@
         <v>-4.95</v>
       </c>
       <c r="R72" s="3">
-        <v>-20.21</v>
-      </c>
-      <c r="S72" t="str">
+        <v>15.69</v>
+      </c>
+      <c r="S72" s="3">
+        <v>37.29</v>
+      </c>
+      <c r="T72" t="str">
         <v/>
       </c>
     </row>
@@ -4679,7 +4895,7 @@
         <v>91.75</v>
       </c>
       <c r="I73" s="1">
-        <v>2132356</v>
+        <v>2132437</v>
       </c>
       <c r="J73" s="1">
         <v>1050.9</v>
@@ -4691,7 +4907,7 @@
         <v>1518.88</v>
       </c>
       <c r="M73" s="3">
-        <v>151.93</v>
+        <v>-14.64</v>
       </c>
       <c r="N73" s="3">
         <v>-15.81</v>
@@ -4706,9 +4922,12 @@
         <v>282.19</v>
       </c>
       <c r="R73" s="3">
-        <v>-15.81</v>
-      </c>
-      <c r="S73" t="str">
+        <v>196.98</v>
+      </c>
+      <c r="S73" s="3">
+        <v>45.28</v>
+      </c>
+      <c r="T73" t="str">
         <v/>
       </c>
     </row>
@@ -4738,7 +4957,7 @@
         <v>-24.95</v>
       </c>
       <c r="I74" s="1">
-        <v>7410763</v>
+        <v>7417472</v>
       </c>
       <c r="J74" s="1">
         <v>340.46</v>
@@ -4750,7 +4969,7 @@
         <v>304.26</v>
       </c>
       <c r="M74" s="3">
-        <v>-20.23</v>
+        <v>-6.74</v>
       </c>
       <c r="N74" s="3">
         <v>-7.46</v>
@@ -4765,9 +4984,12 @@
         <v>-34.15</v>
       </c>
       <c r="R74" s="3">
-        <v>-7.46</v>
-      </c>
-      <c r="S74" t="str">
+        <v>-23.34</v>
+      </c>
+      <c r="S74" s="3">
+        <v>36.17</v>
+      </c>
+      <c r="T74" t="str">
         <v/>
       </c>
     </row>
@@ -4797,7 +5019,7 @@
         <v>0.69</v>
       </c>
       <c r="I75" s="1">
-        <v>3026448</v>
+        <v>3026454</v>
       </c>
       <c r="J75" s="1">
         <v>981.33</v>
@@ -4809,7 +5031,7 @@
         <v>984.53</v>
       </c>
       <c r="M75" s="3">
-        <v>-11.77</v>
+        <v>-26.11</v>
       </c>
       <c r="N75" s="3">
         <v>-25.82</v>
@@ -4824,9 +5046,12 @@
         <v>93.43</v>
       </c>
       <c r="R75" s="3">
-        <v>-25.82</v>
-      </c>
-      <c r="S75" t="str">
+        <v>98.91</v>
+      </c>
+      <c r="S75" s="3">
+        <v>37</v>
+      </c>
+      <c r="T75" t="str">
         <v/>
       </c>
     </row>
@@ -4856,7 +5081,7 @@
         <v>-9.49</v>
       </c>
       <c r="I76" s="1">
-        <v>2921422</v>
+        <v>2921448</v>
       </c>
       <c r="J76" s="1">
         <v>411.56</v>
@@ -4868,7 +5093,7 @@
         <v>377.76</v>
       </c>
       <c r="M76" s="3">
-        <v>-9.19</v>
+        <v>0.57</v>
       </c>
       <c r="N76" s="3">
         <v>0.06</v>
@@ -4883,9 +5108,12 @@
         <v>18.63</v>
       </c>
       <c r="R76" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="S76" t="str">
+        <v>27.69</v>
+      </c>
+      <c r="S76" s="3">
+        <v>49.99</v>
+      </c>
+      <c r="T76" t="str">
         <v/>
       </c>
     </row>
@@ -4915,7 +5143,7 @@
         <v>-4.24</v>
       </c>
       <c r="I77" s="1">
-        <v>20033739</v>
+        <v>20035734</v>
       </c>
       <c r="J77" s="1">
         <v>194.23</v>
@@ -4927,7 +5155,7 @@
         <v>183.06</v>
       </c>
       <c r="M77" s="3">
-        <v>-4.74</v>
+        <v>-3.15</v>
       </c>
       <c r="N77" s="3">
         <v>-2.82</v>
@@ -4942,9 +5170,12 @@
         <v>10.93</v>
       </c>
       <c r="R77" s="3">
-        <v>-2.82</v>
-      </c>
-      <c r="S77" t="str">
+        <v>13.64</v>
+      </c>
+      <c r="S77" s="3">
+        <v>36.93</v>
+      </c>
+      <c r="T77" t="str">
         <v/>
       </c>
     </row>
@@ -4986,7 +5217,7 @@
         <v>56378.11</v>
       </c>
       <c r="M78" s="3">
-        <v>-347.01</v>
+        <v>-258.91</v>
       </c>
       <c r="N78" s="3">
         <v>-378.44</v>
@@ -5001,9 +5232,12 @@
         <v>1665.08</v>
       </c>
       <c r="R78" s="3">
-        <v>-378.44</v>
-      </c>
-      <c r="S78" t="str">
+        <v>2288.6</v>
+      </c>
+      <c r="S78" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="T78" t="str">
         <v/>
       </c>
     </row>
@@ -5033,7 +5267,7 @@
         <v>1.92</v>
       </c>
       <c r="I79" s="1">
-        <v>4914816</v>
+        <v>4915430</v>
       </c>
       <c r="J79" s="1">
         <v>688.93</v>
@@ -5045,7 +5279,7 @@
         <v>726.56</v>
       </c>
       <c r="M79" s="3">
-        <v>14.81</v>
+        <v>6.84</v>
       </c>
       <c r="N79" s="3">
         <v>2.54</v>
@@ -5060,9 +5294,12 @@
         <v>30.95</v>
       </c>
       <c r="R79" s="3">
-        <v>2.54</v>
-      </c>
-      <c r="S79" t="str">
+        <v>37.18</v>
+      </c>
+      <c r="S79" s="3">
+        <v>57.91</v>
+      </c>
+      <c r="T79" t="str">
         <v/>
       </c>
     </row>
@@ -5092,7 +5329,7 @@
         <v>28.57</v>
       </c>
       <c r="I80" s="1">
-        <v>1656705</v>
+        <v>1657572</v>
       </c>
       <c r="J80" s="1">
         <v>1297.54</v>
@@ -5104,7 +5341,7 @@
         <v>1682.65</v>
       </c>
       <c r="M80" s="3">
-        <v>139.03</v>
+        <v>2.99</v>
       </c>
       <c r="N80" s="3">
         <v>8.62</v>
@@ -5119,9 +5356,12 @@
         <v>187.75</v>
       </c>
       <c r="R80" s="3">
-        <v>8.62</v>
-      </c>
-      <c r="S80" t="str">
+        <v>132.37</v>
+      </c>
+      <c r="S80" s="3">
+        <v>47.67</v>
+      </c>
+      <c r="T80" t="str">
         <v/>
       </c>
     </row>
@@ -5151,7 +5391,7 @@
         <v>18.98</v>
       </c>
       <c r="I81" s="1">
-        <v>2177621</v>
+        <v>2177753</v>
       </c>
       <c r="J81" s="1">
         <v>1642.98</v>
@@ -5163,7 +5403,7 @@
         <v>1729.31</v>
       </c>
       <c r="M81" s="3">
-        <v>33.38</v>
+        <v>2.07</v>
       </c>
       <c r="N81" s="3">
         <v>5.32</v>
@@ -5178,9 +5418,12 @@
         <v>148.06</v>
       </c>
       <c r="R81" s="3">
-        <v>5.32</v>
-      </c>
-      <c r="S81" t="str">
+        <v>135.03</v>
+      </c>
+      <c r="S81" s="3">
+        <v>49.28</v>
+      </c>
+      <c r="T81" t="str">
         <v/>
       </c>
     </row>
@@ -5210,7 +5453,7 @@
         <v>8.13</v>
       </c>
       <c r="I82" s="1">
-        <v>386111</v>
+        <v>386119</v>
       </c>
       <c r="J82" s="1">
         <v>4434.6</v>
@@ -5222,7 +5465,7 @@
         <v>4847.87</v>
       </c>
       <c r="M82" s="3">
-        <v>65.15</v>
+        <v>-127.47</v>
       </c>
       <c r="N82" s="3">
         <v>-126.09</v>
@@ -5237,9 +5480,12 @@
         <v>361.47</v>
       </c>
       <c r="R82" s="3">
-        <v>-126.09</v>
-      </c>
-      <c r="S82" t="str">
+        <v>317.47</v>
+      </c>
+      <c r="S82" s="3">
+        <v>31.81</v>
+      </c>
+      <c r="T82" t="str">
         <v/>
       </c>
     </row>
@@ -5269,7 +5515,7 @@
         <v>-0.55</v>
       </c>
       <c r="I83" s="1">
-        <v>10906363</v>
+        <v>10907420</v>
       </c>
       <c r="J83" s="1">
         <v>400.24</v>
@@ -5281,7 +5527,7 @@
         <v>416.19</v>
       </c>
       <c r="M83" s="3">
-        <v>10.69</v>
+        <v>8.58</v>
       </c>
       <c r="N83" s="3">
         <v>7.63</v>
@@ -5296,9 +5542,12 @@
         <v>9.44</v>
       </c>
       <c r="R83" s="3">
-        <v>7.63</v>
-      </c>
-      <c r="S83" t="str">
+        <v>8.32</v>
+      </c>
+      <c r="S83" s="3">
+        <v>58.48</v>
+      </c>
+      <c r="T83" t="str">
         <v/>
       </c>
     </row>
@@ -5328,7 +5577,7 @@
         <v>2.13</v>
       </c>
       <c r="I84" s="1">
-        <v>4498178</v>
+        <v>4498522</v>
       </c>
       <c r="J84" s="1">
         <v>434.07</v>
@@ -5340,7 +5589,7 @@
         <v>414.17</v>
       </c>
       <c r="M84" s="3">
-        <v>-5.56</v>
+        <v>-1.78</v>
       </c>
       <c r="N84" s="3">
         <v>-0.99</v>
@@ -5355,9 +5604,12 @@
         <v>13.03</v>
       </c>
       <c r="R84" s="3">
-        <v>-0.99</v>
-      </c>
-      <c r="S84" t="str">
+        <v>18.02</v>
+      </c>
+      <c r="S84" s="3">
+        <v>42.9</v>
+      </c>
+      <c r="T84" t="str">
         <v/>
       </c>
     </row>
@@ -5387,7 +5639,7 @@
         <v>-28.03</v>
       </c>
       <c r="I85" s="1">
-        <v>1228549</v>
+        <v>1228670</v>
       </c>
       <c r="J85" s="1">
         <v>609.57</v>
@@ -5399,7 +5651,7 @@
         <v>541.21</v>
       </c>
       <c r="M85" s="3">
-        <v>-22.01</v>
+        <v>2.06</v>
       </c>
       <c r="N85" s="3">
         <v>1.92</v>
@@ -5414,9 +5666,12 @@
         <v>-35.15</v>
       </c>
       <c r="R85" s="3">
-        <v>1.92</v>
-      </c>
-      <c r="S85" t="str">
+        <v>-11.55</v>
+      </c>
+      <c r="S85" s="3">
+        <v>47.6</v>
+      </c>
+      <c r="T85" t="str">
         <v/>
       </c>
     </row>
@@ -5446,7 +5701,7 @@
         <v>-8.21</v>
       </c>
       <c r="I86" s="1">
-        <v>877994</v>
+        <v>878065</v>
       </c>
       <c r="J86" s="1">
         <v>735.93</v>
@@ -5458,7 +5713,7 @@
         <v>723.34</v>
       </c>
       <c r="M86" s="3">
-        <v>-18.03</v>
+        <v>-9.19</v>
       </c>
       <c r="N86" s="3">
         <v>-12.01</v>
@@ -5473,9 +5728,12 @@
         <v>7.42</v>
       </c>
       <c r="R86" s="3">
-        <v>-12.01</v>
-      </c>
-      <c r="S86" t="str">
+        <v>20.24</v>
+      </c>
+      <c r="S86" s="3">
+        <v>42.48</v>
+      </c>
+      <c r="T86" t="str">
         <v/>
       </c>
     </row>
@@ -5505,7 +5763,7 @@
         <v>-10.21</v>
       </c>
       <c r="I87" s="1">
-        <v>135048</v>
+        <v>135247</v>
       </c>
       <c r="J87" s="1">
         <v>1685.99</v>
@@ -5517,7 +5775,7 @@
         <v>1520.1</v>
       </c>
       <c r="M87" s="3">
-        <v>-45.13</v>
+        <v>13.41</v>
       </c>
       <c r="N87" s="3">
         <v>11.43</v>
@@ -5532,9 +5790,12 @@
         <v>20.55</v>
       </c>
       <c r="R87" s="3">
-        <v>11.43</v>
-      </c>
-      <c r="S87" t="str">
+        <v>82.69</v>
+      </c>
+      <c r="S87" s="3">
+        <v>50.67</v>
+      </c>
+      <c r="T87" t="str">
         <v/>
       </c>
     </row>
@@ -5564,7 +5825,7 @@
         <v>-1.95</v>
       </c>
       <c r="I88" s="1">
-        <v>9920369</v>
+        <v>9923465</v>
       </c>
       <c r="J88" s="1">
         <v>1040.35</v>
@@ -5576,7 +5837,7 @@
         <v>1004.78</v>
       </c>
       <c r="M88" s="3">
-        <v>-15.65</v>
+        <v>-11.02</v>
       </c>
       <c r="N88" s="3">
         <v>-14.86</v>
@@ -5591,9 +5852,12 @@
         <v>69.46</v>
       </c>
       <c r="R88" s="3">
-        <v>-14.86</v>
-      </c>
-      <c r="S88" t="str">
+        <v>81.52</v>
+      </c>
+      <c r="S88" s="3">
+        <v>45.41</v>
+      </c>
+      <c r="T88" t="str">
         <v/>
       </c>
     </row>
@@ -5623,7 +5887,7 @@
         <v>-22.15</v>
       </c>
       <c r="I89" s="1">
-        <v>17706129</v>
+        <v>17711620</v>
       </c>
       <c r="J89" s="1">
         <v>134.63</v>
@@ -5635,7 +5899,7 @@
         <v>124.51</v>
       </c>
       <c r="M89" s="3">
-        <v>-3.72</v>
+        <v>-1.15</v>
       </c>
       <c r="N89" s="3">
         <v>-1.52</v>
@@ -5650,9 +5914,12 @@
         <v>7.1</v>
       </c>
       <c r="R89" s="3">
-        <v>-1.52</v>
-      </c>
-      <c r="S89" t="str">
+        <v>10.56</v>
+      </c>
+      <c r="S89" s="3">
+        <v>48.26</v>
+      </c>
+      <c r="T89" t="str">
         <v/>
       </c>
     </row>
@@ -5682,7 +5949,7 @@
         <v>-17.53</v>
       </c>
       <c r="I90" s="1">
-        <v>668445</v>
+        <v>669066</v>
       </c>
       <c r="J90" s="1">
         <v>901.9</v>
@@ -5694,7 +5961,7 @@
         <v>861.12</v>
       </c>
       <c r="M90" s="3">
-        <v>-40.95</v>
+        <v>-39.1</v>
       </c>
       <c r="N90" s="3">
         <v>-37.26</v>
@@ -5709,9 +5976,12 @@
         <v>67.7</v>
       </c>
       <c r="R90" s="3">
-        <v>-37.26</v>
-      </c>
-      <c r="S90" t="str">
+        <v>100.72</v>
+      </c>
+      <c r="S90" s="3">
+        <v>25.93</v>
+      </c>
+      <c r="T90" t="str">
         <v/>
       </c>
     </row>
@@ -5741,7 +6011,7 @@
         <v>-7.6</v>
       </c>
       <c r="I91" s="1">
-        <v>6173132</v>
+        <v>6174902</v>
       </c>
       <c r="J91" s="1">
         <v>399.01</v>
@@ -5753,7 +6023,7 @@
         <v>348.37</v>
       </c>
       <c r="M91" s="3">
-        <v>-23.59</v>
+        <v>-4.55</v>
       </c>
       <c r="N91" s="3">
         <v>-6.36</v>
@@ -5768,9 +6038,12 @@
         <v>-1.54</v>
       </c>
       <c r="R91" s="3">
-        <v>-6.36</v>
-      </c>
-      <c r="S91" t="str">
+        <v>12.45</v>
+      </c>
+      <c r="S91" s="3">
+        <v>40.04</v>
+      </c>
+      <c r="T91" t="str">
         <v/>
       </c>
     </row>
@@ -5800,7 +6073,7 @@
         <v>-17.14</v>
       </c>
       <c r="I92" s="1">
-        <v>405238</v>
+        <v>405356</v>
       </c>
       <c r="J92" s="1">
         <v>2017.79</v>
@@ -5812,7 +6085,7 @@
         <v>1848.17</v>
       </c>
       <c r="M92" s="3">
-        <v>-85.77</v>
+        <v>-28.96</v>
       </c>
       <c r="N92" s="3">
         <v>-27.04</v>
@@ -5827,9 +6100,12 @@
         <v>-156.76</v>
       </c>
       <c r="R92" s="3">
-        <v>-27.04</v>
-      </c>
-      <c r="S92" t="str">
+        <v>-102.73</v>
+      </c>
+      <c r="S92" s="3">
+        <v>39.4</v>
+      </c>
+      <c r="T92" t="str">
         <v/>
       </c>
     </row>
@@ -5859,7 +6135,7 @@
         <v>-21.55</v>
       </c>
       <c r="I93" s="1">
-        <v>3165551</v>
+        <v>3165736</v>
       </c>
       <c r="J93" s="1">
         <v>1021.07</v>
@@ -5871,7 +6147,7 @@
         <v>979.18</v>
       </c>
       <c r="M93" s="3">
-        <v>-44.12</v>
+        <v>-49.07</v>
       </c>
       <c r="N93" s="3">
         <v>-41.24</v>
@@ -5886,9 +6162,12 @@
         <v>18.12</v>
       </c>
       <c r="R93" s="3">
-        <v>-41.24</v>
-      </c>
-      <c r="S93" t="str">
+        <v>58.94</v>
+      </c>
+      <c r="S93" s="3">
+        <v>21.39</v>
+      </c>
+      <c r="T93" t="str">
         <v/>
       </c>
     </row>
@@ -5918,7 +6197,7 @@
         <v>-28.33</v>
       </c>
       <c r="I94" s="1">
-        <v>12638486</v>
+        <v>12651107</v>
       </c>
       <c r="J94" s="1">
         <v>244.45</v>
@@ -5930,7 +6209,7 @@
         <v>231.08</v>
       </c>
       <c r="M94" s="3">
-        <v>-9.83</v>
+        <v>-4.62</v>
       </c>
       <c r="N94" s="3">
         <v>-5.07</v>
@@ -5945,9 +6224,12 @@
         <v>-15.41</v>
       </c>
       <c r="R94" s="3">
-        <v>-5.07</v>
-      </c>
-      <c r="S94" t="str">
+        <v>-8.38</v>
+      </c>
+      <c r="S94" s="3">
+        <v>34.83</v>
+      </c>
+      <c r="T94" t="str">
         <v/>
       </c>
     </row>
@@ -5977,7 +6259,7 @@
         <v>-8.26</v>
       </c>
       <c r="I95" s="1">
-        <v>514359</v>
+        <v>514418</v>
       </c>
       <c r="J95" s="1">
         <v>4810.06</v>
@@ -5989,7 +6271,7 @@
         <v>5003.92</v>
       </c>
       <c r="M95" s="3">
-        <v>-24.64</v>
+        <v>-84.51</v>
       </c>
       <c r="N95" s="3">
         <v>-65.93</v>
@@ -6004,9 +6286,12 @@
         <v>205.21</v>
       </c>
       <c r="R95" s="3">
-        <v>-65.93</v>
-      </c>
-      <c r="S95" t="str">
+        <v>316.07</v>
+      </c>
+      <c r="S95" s="3">
+        <v>35.34</v>
+      </c>
+      <c r="T95" t="str">
         <v/>
       </c>
     </row>
@@ -6036,7 +6321,7 @@
         <v>-16.32</v>
       </c>
       <c r="I96" s="1">
-        <v>16851514</v>
+        <v>16853802</v>
       </c>
       <c r="J96" s="1">
         <v>83.5</v>
@@ -6048,7 +6333,7 @@
         <v>80.36</v>
       </c>
       <c r="M96" s="3">
-        <v>-2.98</v>
+        <v>-3.08</v>
       </c>
       <c r="N96" s="3">
         <v>-2.99</v>
@@ -6063,9 +6348,12 @@
         <v>4.02</v>
       </c>
       <c r="R96" s="3">
-        <v>-2.99</v>
-      </c>
-      <c r="S96" t="str">
+        <v>5.46</v>
+      </c>
+      <c r="S96" s="3">
+        <v>28.86</v>
+      </c>
+      <c r="T96" t="str">
         <v/>
       </c>
     </row>
@@ -6095,7 +6383,7 @@
         <v>7.92</v>
       </c>
       <c r="I97" s="1">
-        <v>239538</v>
+        <v>239550</v>
       </c>
       <c r="J97" s="1">
         <v>8066.59</v>
@@ -6107,7 +6395,7 @@
         <v>8544.13</v>
       </c>
       <c r="M97" s="3">
-        <v>3.14</v>
+        <v>-270.71</v>
       </c>
       <c r="N97" s="3">
         <v>-239.21</v>
@@ -6122,9 +6410,12 @@
         <v>540.48</v>
       </c>
       <c r="R97" s="3">
-        <v>-239.21</v>
-      </c>
-      <c r="S97" t="str">
+        <v>564.06</v>
+      </c>
+      <c r="S97" s="3">
+        <v>31.28</v>
+      </c>
+      <c r="T97" t="str">
         <v/>
       </c>
     </row>
@@ -6154,7 +6445,7 @@
         <v>-2.45</v>
       </c>
       <c r="I98" s="1">
-        <v>1136991</v>
+        <v>1137011</v>
       </c>
       <c r="J98" s="1">
         <v>1138.53</v>
@@ -6166,7 +6457,7 @@
         <v>1113.01</v>
       </c>
       <c r="M98" s="3">
-        <v>-18.21</v>
+        <v>-27.07</v>
       </c>
       <c r="N98" s="3">
         <v>-23.72</v>
@@ -6181,9 +6472,12 @@
         <v>74.18</v>
       </c>
       <c r="R98" s="3">
-        <v>-23.72</v>
-      </c>
-      <c r="S98" t="str">
+        <v>90.32</v>
+      </c>
+      <c r="S98" s="3">
+        <v>36.15</v>
+      </c>
+      <c r="T98" t="str">
         <v/>
       </c>
     </row>
@@ -6213,7 +6507,7 @@
         <v>-3.4</v>
       </c>
       <c r="I99" s="1">
-        <v>2597262</v>
+        <v>2597925</v>
       </c>
       <c r="J99" s="1">
         <v>626.59</v>
@@ -6225,7 +6519,7 @@
         <v>664.97</v>
       </c>
       <c r="M99" s="3">
-        <v>9.59</v>
+        <v>1.55</v>
       </c>
       <c r="N99" s="3">
         <v>0.19</v>
@@ -6240,9 +6534,12 @@
         <v>-11.29</v>
       </c>
       <c r="R99" s="3">
-        <v>0.19</v>
-      </c>
-      <c r="S99" t="str">
+        <v>-7.43</v>
+      </c>
+      <c r="S99" s="3">
+        <v>50.48</v>
+      </c>
+      <c r="T99" t="str">
         <v/>
       </c>
     </row>
@@ -6272,7 +6569,7 @@
         <v>9.12</v>
       </c>
       <c r="I100" s="1">
-        <v>380994</v>
+        <v>381146</v>
       </c>
       <c r="J100" s="1">
         <v>3098.06</v>
@@ -6284,7 +6581,7 @@
         <v>3246.41</v>
       </c>
       <c r="M100" s="3">
-        <v>-48.83</v>
+        <v>-94.04</v>
       </c>
       <c r="N100" s="3">
         <v>-49.84</v>
@@ -6299,9 +6596,12 @@
         <v>41.89</v>
       </c>
       <c r="R100" s="3">
-        <v>-49.84</v>
-      </c>
-      <c r="S100" t="str">
+        <v>51.14</v>
+      </c>
+      <c r="S100" s="3">
+        <v>28.51</v>
+      </c>
+      <c r="T100" t="str">
         <v/>
       </c>
     </row>
@@ -6331,7 +6631,7 @@
         <v>20.65</v>
       </c>
       <c r="I101" s="1">
-        <v>646862</v>
+        <v>646972</v>
       </c>
       <c r="J101" s="1">
         <v>1874.1</v>
@@ -6343,7 +6643,7 @@
         <v>1963.3</v>
       </c>
       <c r="M101" s="3">
-        <v>0.03</v>
+        <v>-49.09</v>
       </c>
       <c r="N101" s="3">
         <v>-46.36</v>
@@ -6358,9 +6658,12 @@
         <v>213.16</v>
       </c>
       <c r="R101" s="3">
-        <v>-46.36</v>
-      </c>
-      <c r="S101" t="str">
+        <v>188.65</v>
+      </c>
+      <c r="S101" s="3">
+        <v>33.16</v>
+      </c>
+      <c r="T101" t="str">
         <v/>
       </c>
     </row>
@@ -6390,7 +6693,7 @@
         <v>28.79</v>
       </c>
       <c r="I102" s="1">
-        <v>5600279</v>
+        <v>5601426</v>
       </c>
       <c r="J102" s="1">
         <v>308.11</v>
@@ -6402,7 +6705,7 @@
         <v>340.33</v>
       </c>
       <c r="M102" s="3">
-        <v>10.64</v>
+        <v>0.67</v>
       </c>
       <c r="N102" s="3">
         <v>-2.62</v>
@@ -6417,9 +6720,12 @@
         <v>43.15</v>
       </c>
       <c r="R102" s="3">
-        <v>-2.62</v>
-      </c>
-      <c r="S102" t="str">
+        <v>37.15</v>
+      </c>
+      <c r="S102" s="3">
+        <v>59.16</v>
+      </c>
+      <c r="T102" t="str">
         <v/>
       </c>
     </row>
@@ -6449,7 +6755,7 @@
         <v>-23.05</v>
       </c>
       <c r="I103" s="1">
-        <v>1974023</v>
+        <v>1974554</v>
       </c>
       <c r="J103" s="1">
         <v>123.54</v>
@@ -6461,7 +6767,7 @@
         <v>115.07</v>
       </c>
       <c r="M103" s="3">
-        <v>-5.93</v>
+        <v>-2.79</v>
       </c>
       <c r="N103" s="3">
         <v>-3.12</v>
@@ -6476,9 +6782,12 @@
         <v>-13.16</v>
       </c>
       <c r="R103" s="3">
-        <v>-3.12</v>
-      </c>
-      <c r="S103" t="str">
+        <v>-10.05</v>
+      </c>
+      <c r="S103" s="3">
+        <v>32.78</v>
+      </c>
+      <c r="T103" t="str">
         <v/>
       </c>
     </row>
@@ -6508,7 +6817,7 @@
         <v>-10.7</v>
       </c>
       <c r="I104" s="1">
-        <v>382702</v>
+        <v>382905</v>
       </c>
       <c r="J104" s="1">
         <v>5300.83</v>
@@ -6520,7 +6829,7 @@
         <v>5375.61</v>
       </c>
       <c r="M104" s="3">
-        <v>-12.17</v>
+        <v>-53.26</v>
       </c>
       <c r="N104" s="3">
         <v>-79.2</v>
@@ -6535,9 +6844,12 @@
         <v>247.51</v>
       </c>
       <c r="R104" s="3">
-        <v>-79.2</v>
-      </c>
-      <c r="S104" t="str">
+        <v>306.78</v>
+      </c>
+      <c r="S104" s="3">
+        <v>48.11</v>
+      </c>
+      <c r="T104" t="str">
         <v/>
       </c>
     </row>
@@ -6567,7 +6879,7 @@
         <v>-4.36</v>
       </c>
       <c r="I105" s="1">
-        <v>1191628</v>
+        <v>1191851</v>
       </c>
       <c r="J105" s="1">
         <v>1021.88</v>
@@ -6579,7 +6891,7 @@
         <v>1160.66</v>
       </c>
       <c r="M105" s="3">
-        <v>18.48</v>
+        <v>-33.66</v>
       </c>
       <c r="N105" s="3">
         <v>-27.8</v>
@@ -6594,9 +6906,12 @@
         <v>-1.48</v>
       </c>
       <c r="R105" s="3">
-        <v>-27.8</v>
-      </c>
-      <c r="S105" t="str">
+        <v>5.44</v>
+      </c>
+      <c r="S105" s="3">
+        <v>32.22</v>
+      </c>
+      <c r="T105" t="str">
         <v/>
       </c>
     </row>
@@ -6626,7 +6941,7 @@
         <v>-14.95</v>
       </c>
       <c r="I106" s="1">
-        <v>2394595</v>
+        <v>2396904</v>
       </c>
       <c r="J106" s="1">
         <v>392.53</v>
@@ -6638,7 +6953,7 @@
         <v>388.42</v>
       </c>
       <c r="M106" s="3">
-        <v>-11.73</v>
+        <v>-13.89</v>
       </c>
       <c r="N106" s="3">
         <v>-12.61</v>
@@ -6653,9 +6968,12 @@
         <v>15</v>
       </c>
       <c r="R106" s="3">
-        <v>-12.61</v>
-      </c>
-      <c r="S106" t="str">
+        <v>19.72</v>
+      </c>
+      <c r="S106" s="3">
+        <v>22.08</v>
+      </c>
+      <c r="T106" t="str">
         <v/>
       </c>
     </row>
@@ -6697,7 +7015,7 @@
         <v>1268.23</v>
       </c>
       <c r="M107" s="3">
-        <v>-0.09</v>
+        <v>-18.14</v>
       </c>
       <c r="N107" s="3">
         <v>-21.12</v>
@@ -6712,9 +7030,12 @@
         <v>92.2</v>
       </c>
       <c r="R107" s="3">
-        <v>-21.12</v>
-      </c>
-      <c r="S107" t="str">
+        <v>97.25</v>
+      </c>
+      <c r="S107" s="3">
+        <v>47.16</v>
+      </c>
+      <c r="T107" t="str">
         <v/>
       </c>
     </row>
@@ -6744,7 +7065,7 @@
         <v>-35.43</v>
       </c>
       <c r="I108" s="1">
-        <v>1219041</v>
+        <v>1219515</v>
       </c>
       <c r="J108" s="1">
         <v>542</v>
@@ -6756,7 +7077,7 @@
         <v>478.99</v>
       </c>
       <c r="M108" s="3">
-        <v>-26.75</v>
+        <v>-10.94</v>
       </c>
       <c r="N108" s="3">
         <v>-9.89</v>
@@ -6771,9 +7092,12 @@
         <v>-36.2</v>
       </c>
       <c r="R108" s="3">
-        <v>-9.89</v>
-      </c>
-      <c r="S108" t="str">
+        <v>-16.68</v>
+      </c>
+      <c r="S108" s="3">
+        <v>31.43</v>
+      </c>
+      <c r="T108" t="str">
         <v/>
       </c>
     </row>
@@ -6815,7 +7139,7 @@
         <v>1756.31</v>
       </c>
       <c r="M109" s="3">
-        <v>-13.97</v>
+        <v>-57.69</v>
       </c>
       <c r="N109" s="3">
         <v>-58.47</v>
@@ -6830,9 +7154,12 @@
         <v>103.87</v>
       </c>
       <c r="R109" s="3">
-        <v>-58.47</v>
-      </c>
-      <c r="S109" t="str">
+        <v>124.41</v>
+      </c>
+      <c r="S109" s="3">
+        <v>32.76</v>
+      </c>
+      <c r="T109" t="str">
         <v/>
       </c>
     </row>
@@ -6862,7 +7189,7 @@
         <v>-1.55</v>
       </c>
       <c r="I110" s="1">
-        <v>860473</v>
+        <v>860651</v>
       </c>
       <c r="J110" s="1">
         <v>523.27</v>
@@ -6874,7 +7201,7 @@
         <v>518.14</v>
       </c>
       <c r="M110" s="3">
-        <v>-13.77</v>
+        <v>-12.27</v>
       </c>
       <c r="N110" s="3">
         <v>-13.6</v>
@@ -6889,9 +7216,12 @@
         <v>5.18</v>
       </c>
       <c r="R110" s="3">
-        <v>-13.6</v>
-      </c>
-      <c r="S110" t="str">
+        <v>12.41</v>
+      </c>
+      <c r="S110" s="3">
+        <v>40.58</v>
+      </c>
+      <c r="T110" t="str">
         <v/>
       </c>
     </row>
@@ -6921,7 +7251,7 @@
         <v>-4.98</v>
       </c>
       <c r="I111" s="1">
-        <v>1544406</v>
+        <v>1544434</v>
       </c>
       <c r="J111" s="1">
         <v>1364.8</v>
@@ -6933,7 +7263,7 @@
         <v>1392.68</v>
       </c>
       <c r="M111" s="3">
-        <v>-19.02</v>
+        <v>-35.55</v>
       </c>
       <c r="N111" s="3">
         <v>-28.56</v>
@@ -6948,9 +7278,12 @@
         <v>55.68</v>
       </c>
       <c r="R111" s="3">
-        <v>-28.56</v>
-      </c>
-      <c r="S111" t="str">
+        <v>58.74</v>
+      </c>
+      <c r="S111" s="3">
+        <v>31.23</v>
+      </c>
+      <c r="T111" t="str">
         <v/>
       </c>
     </row>
@@ -6980,7 +7313,7 @@
         <v>-6.64</v>
       </c>
       <c r="I112" s="1">
-        <v>1596944</v>
+        <v>1596954</v>
       </c>
       <c r="J112" s="1">
         <v>533.18</v>
@@ -6992,7 +7325,7 @@
         <v>532.67</v>
       </c>
       <c r="M112" s="3">
-        <v>-3.26</v>
+        <v>-5.68</v>
       </c>
       <c r="N112" s="3">
         <v>-1.82</v>
@@ -7007,9 +7340,12 @@
         <v>-9.54</v>
       </c>
       <c r="R112" s="3">
-        <v>-1.82</v>
-      </c>
-      <c r="S112" t="str">
+        <v>-3</v>
+      </c>
+      <c r="S112" s="3">
+        <v>38.51</v>
+      </c>
+      <c r="T112" t="str">
         <v/>
       </c>
     </row>
@@ -7039,7 +7375,7 @@
         <v>23.47</v>
       </c>
       <c r="I113" s="1">
-        <v>16490</v>
+        <v>16491</v>
       </c>
       <c r="J113" s="1">
         <v>39532.2</v>
@@ -7051,7 +7387,7 @@
         <v>46924.6</v>
       </c>
       <c r="M113" s="3">
-        <v>2078.76</v>
+        <v>-580.85</v>
       </c>
       <c r="N113" s="3">
         <v>-568.27</v>
@@ -7066,9 +7402,12 @@
         <v>4101.92</v>
       </c>
       <c r="R113" s="3">
-        <v>-568.27</v>
-      </c>
-      <c r="S113" t="str">
+        <v>3348.42</v>
+      </c>
+      <c r="S113" s="3">
+        <v>42.31</v>
+      </c>
+      <c r="T113" t="str">
         <v/>
       </c>
     </row>
@@ -7098,7 +7437,7 @@
         <v>-21.96</v>
       </c>
       <c r="I114" s="1">
-        <v>501670</v>
+        <v>501872</v>
       </c>
       <c r="J114" s="1">
         <v>1808.83</v>
@@ -7110,7 +7449,7 @@
         <v>1808.5</v>
       </c>
       <c r="M114" s="3">
-        <v>-70.77</v>
+        <v>-62.73</v>
       </c>
       <c r="N114" s="3">
         <v>-74.85</v>
@@ -7125,9 +7464,12 @@
         <v>-117.15</v>
       </c>
       <c r="R114" s="3">
-        <v>-74.85</v>
-      </c>
-      <c r="S114" t="str">
+        <v>-83.03</v>
+      </c>
+      <c r="S114" s="3">
+        <v>35.15</v>
+      </c>
+      <c r="T114" t="str">
         <v/>
       </c>
     </row>
@@ -7157,7 +7499,7 @@
         <v>-1.7</v>
       </c>
       <c r="I115" s="1">
-        <v>1924858</v>
+        <v>1925181</v>
       </c>
       <c r="J115" s="1">
         <v>924.53</v>
@@ -7169,7 +7511,7 @@
         <v>954.63</v>
       </c>
       <c r="M115" s="3">
-        <v>-7.9</v>
+        <v>-27.08</v>
       </c>
       <c r="N115" s="3">
         <v>-27.95</v>
@@ -7184,9 +7526,12 @@
         <v>-46</v>
       </c>
       <c r="R115" s="3">
-        <v>-27.95</v>
-      </c>
-      <c r="S115" t="str">
+        <v>-66.54</v>
+      </c>
+      <c r="S115" s="3">
+        <v>34.41</v>
+      </c>
+      <c r="T115" t="str">
         <v/>
       </c>
     </row>
@@ -7216,7 +7561,7 @@
         <v>-7.11</v>
       </c>
       <c r="I116" s="1">
-        <v>7909892</v>
+        <v>7916475</v>
       </c>
       <c r="J116" s="1">
         <v>416.97</v>
@@ -7228,7 +7573,7 @@
         <v>396.59</v>
       </c>
       <c r="M116" s="3">
-        <v>-10.86</v>
+        <v>-6.16</v>
       </c>
       <c r="N116" s="3">
         <v>-6.2</v>
@@ -7243,9 +7588,12 @@
         <v>34.2</v>
       </c>
       <c r="R116" s="3">
-        <v>-6.2</v>
-      </c>
-      <c r="S116" t="str">
+        <v>46.63</v>
+      </c>
+      <c r="S116" s="3">
+        <v>36.73</v>
+      </c>
+      <c r="T116" t="str">
         <v/>
       </c>
     </row>
@@ -7275,7 +7623,7 @@
         <v>-14.05</v>
       </c>
       <c r="I117" s="1">
-        <v>436932</v>
+        <v>437098</v>
       </c>
       <c r="J117" s="1">
         <v>3973.91</v>
@@ -7287,7 +7635,7 @@
         <v>3748.84</v>
       </c>
       <c r="M117" s="3">
-        <v>-170.03</v>
+        <v>-132.57</v>
       </c>
       <c r="N117" s="3">
         <v>-101.83</v>
@@ -7302,9 +7650,12 @@
         <v>-84.35</v>
       </c>
       <c r="R117" s="3">
-        <v>-101.83</v>
-      </c>
-      <c r="S117" t="str">
+        <v>-7.79</v>
+      </c>
+      <c r="S117" s="3">
+        <v>25.05</v>
+      </c>
+      <c r="T117" t="str">
         <v/>
       </c>
     </row>
@@ -7346,7 +7697,7 @@
         <v>2440.54</v>
       </c>
       <c r="M118" s="3">
-        <v>-79.57</v>
+        <v>-26.97</v>
       </c>
       <c r="N118" s="3">
         <v>-39.13</v>
@@ -7361,9 +7712,12 @@
         <v>130.23</v>
       </c>
       <c r="R118" s="3">
-        <v>-39.13</v>
-      </c>
-      <c r="S118" t="str">
+        <v>201.08</v>
+      </c>
+      <c r="S118" s="3">
+        <v>44.6</v>
+      </c>
+      <c r="T118" t="str">
         <v/>
       </c>
     </row>
@@ -7393,7 +7747,7 @@
         <v>-12.77</v>
       </c>
       <c r="I119" s="1">
-        <v>1022488</v>
+        <v>1022739</v>
       </c>
       <c r="J119" s="1">
         <v>1101.28</v>
@@ -7405,7 +7759,7 @@
         <v>1112.56</v>
       </c>
       <c r="M119" s="3">
-        <v>-11.04</v>
+        <v>-12.35</v>
       </c>
       <c r="N119" s="3">
         <v>-15.22</v>
@@ -7420,9 +7774,12 @@
         <v>58.1</v>
       </c>
       <c r="R119" s="3">
-        <v>-15.22</v>
-      </c>
-      <c r="S119" t="str">
+        <v>80.96</v>
+      </c>
+      <c r="S119" s="3">
+        <v>40.07</v>
+      </c>
+      <c r="T119" t="str">
         <v/>
       </c>
     </row>
@@ -7452,7 +7809,7 @@
         <v>2.6</v>
       </c>
       <c r="I120" s="1">
-        <v>2995363</v>
+        <v>2997059</v>
       </c>
       <c r="J120" s="1">
         <v>366.1</v>
@@ -7464,7 +7821,7 @@
         <v>393.77</v>
       </c>
       <c r="M120" s="3">
-        <v>6.53</v>
+        <v>-5.56</v>
       </c>
       <c r="N120" s="3">
         <v>-5.33</v>
@@ -7479,9 +7836,12 @@
         <v>47.47</v>
       </c>
       <c r="R120" s="3">
-        <v>-5.33</v>
-      </c>
-      <c r="S120" t="str">
+        <v>45.35</v>
+      </c>
+      <c r="S120" s="3">
+        <v>37.79</v>
+      </c>
+      <c r="T120" t="str">
         <v/>
       </c>
     </row>
@@ -7511,7 +7871,7 @@
         <v>-27.04</v>
       </c>
       <c r="I121" s="1">
-        <v>723173</v>
+        <v>723489</v>
       </c>
       <c r="J121" s="1">
         <v>1299.45</v>
@@ -7523,7 +7883,7 @@
         <v>1212.44</v>
       </c>
       <c r="M121" s="3">
-        <v>-65.81</v>
+        <v>-29.52</v>
       </c>
       <c r="N121" s="3">
         <v>-34.69</v>
@@ -7538,9 +7898,12 @@
         <v>9.54</v>
       </c>
       <c r="R121" s="3">
-        <v>-34.69</v>
-      </c>
-      <c r="S121" t="str">
+        <v>75.94</v>
+      </c>
+      <c r="S121" s="3">
+        <v>36.12</v>
+      </c>
+      <c r="T121" t="str">
         <v/>
       </c>
     </row>
@@ -7570,7 +7933,7 @@
         <v>-12.32</v>
       </c>
       <c r="I122" s="1">
-        <v>16189397</v>
+        <v>16190874</v>
       </c>
       <c r="J122" s="1">
         <v>77.4</v>
@@ -7582,7 +7945,7 @@
         <v>83.54</v>
       </c>
       <c r="M122" s="3">
-        <v>1.08</v>
+        <v>-2.02</v>
       </c>
       <c r="N122" s="3">
         <v>-1.59</v>
@@ -7597,9 +7960,12 @@
         <v>2.66</v>
       </c>
       <c r="R122" s="3">
-        <v>-1.59</v>
-      </c>
-      <c r="S122" t="str">
+        <v>2.19</v>
+      </c>
+      <c r="S122" s="3">
+        <v>29.44</v>
+      </c>
+      <c r="T122" t="str">
         <v/>
       </c>
     </row>
@@ -7629,7 +7995,7 @@
         <v>-35.25</v>
       </c>
       <c r="I123" s="1">
-        <v>938188</v>
+        <v>939483</v>
       </c>
       <c r="J123" s="1">
         <v>672.21</v>
@@ -7641,7 +8007,7 @@
         <v>619.25</v>
       </c>
       <c r="M123" s="3">
-        <v>-31.08</v>
+        <v>-17.74</v>
       </c>
       <c r="N123" s="3">
         <v>-18.98</v>
@@ -7656,9 +8022,12 @@
         <v>-55.64</v>
       </c>
       <c r="R123" s="3">
-        <v>-18.98</v>
-      </c>
-      <c r="S123" t="str">
+        <v>-31.59</v>
+      </c>
+      <c r="S123" s="3">
+        <v>36.36</v>
+      </c>
+      <c r="T123" t="str">
         <v/>
       </c>
     </row>
@@ -7688,7 +8057,7 @@
         <v>-1.39</v>
       </c>
       <c r="I124" s="1">
-        <v>288100</v>
+        <v>288160</v>
       </c>
       <c r="J124" s="1">
         <v>1686.47</v>
@@ -7700,7 +8069,7 @@
         <v>1799.73</v>
       </c>
       <c r="M124" s="3">
-        <v>8.02</v>
+        <v>-35.99</v>
       </c>
       <c r="N124" s="3">
         <v>-30.08</v>
@@ -7715,9 +8084,12 @@
         <v>56.28</v>
       </c>
       <c r="R124" s="3">
-        <v>-30.08</v>
-      </c>
-      <c r="S124" t="str">
+        <v>63.55</v>
+      </c>
+      <c r="S124" s="3">
+        <v>32.78</v>
+      </c>
+      <c r="T124" t="str">
         <v/>
       </c>
     </row>
@@ -7747,7 +8119,7 @@
         <v>32.07</v>
       </c>
       <c r="I125" s="1">
-        <v>222007</v>
+        <v>222232</v>
       </c>
       <c r="J125" s="1">
         <v>3601.14</v>
@@ -7759,7 +8131,7 @@
         <v>4509.08</v>
       </c>
       <c r="M125" s="3">
-        <v>280.38</v>
+        <v>-4.14</v>
       </c>
       <c r="N125" s="3">
         <v>1.51</v>
@@ -7774,9 +8146,12 @@
         <v>602.98</v>
       </c>
       <c r="R125" s="3">
-        <v>1.51</v>
-      </c>
-      <c r="S125" t="str">
+        <v>493.62</v>
+      </c>
+      <c r="S125" s="3">
+        <v>43.96</v>
+      </c>
+      <c r="T125" t="str">
         <v/>
       </c>
     </row>
@@ -7806,7 +8181,7 @@
         <v>-4.07</v>
       </c>
       <c r="I126" s="1">
-        <v>1859441</v>
+        <v>1860213</v>
       </c>
       <c r="J126" s="1">
         <v>1005.83</v>
@@ -7818,7 +8193,7 @@
         <v>1044.61</v>
       </c>
       <c r="M126" s="3">
-        <v>1.36</v>
+        <v>-19.01</v>
       </c>
       <c r="N126" s="3">
         <v>-17.29</v>
@@ -7833,9 +8208,12 @@
         <v>92.33</v>
       </c>
       <c r="R126" s="3">
-        <v>-17.29</v>
-      </c>
-      <c r="S126" t="str">
+        <v>87.83</v>
+      </c>
+      <c r="S126" s="3">
+        <v>35.74</v>
+      </c>
+      <c r="T126" t="str">
         <v/>
       </c>
     </row>
@@ -7865,7 +8243,7 @@
         <v>-0.67</v>
       </c>
       <c r="I127" s="1">
-        <v>3667834</v>
+        <v>3668970</v>
       </c>
       <c r="J127" s="1">
         <v>373.09</v>
@@ -7877,7 +8255,7 @@
         <v>360.79</v>
       </c>
       <c r="M127" s="3">
-        <v>-8.98</v>
+        <v>-12.5</v>
       </c>
       <c r="N127" s="3">
         <v>-12.26</v>
@@ -7892,9 +8270,12 @@
         <v>48.96</v>
       </c>
       <c r="R127" s="3">
-        <v>-12.26</v>
-      </c>
-      <c r="S127" t="str">
+        <v>52.01</v>
+      </c>
+      <c r="S127" s="3">
+        <v>34.15</v>
+      </c>
+      <c r="T127" t="str">
         <v/>
       </c>
     </row>
@@ -7924,7 +8305,7 @@
         <v>5.98</v>
       </c>
       <c r="I128" s="1">
-        <v>199455</v>
+        <v>199497</v>
       </c>
       <c r="J128" s="1">
         <v>3583.24</v>
@@ -7936,7 +8317,7 @@
         <v>3516.77</v>
       </c>
       <c r="M128" s="3">
-        <v>-24.12</v>
+        <v>27.31</v>
       </c>
       <c r="N128" s="3">
         <v>12.9</v>
@@ -7951,9 +8332,12 @@
         <v>-136.46</v>
       </c>
       <c r="R128" s="3">
-        <v>12.9</v>
-      </c>
-      <c r="S128" t="str">
+        <v>-92.32</v>
+      </c>
+      <c r="S128" s="3">
+        <v>52.95</v>
+      </c>
+      <c r="T128" t="str">
         <v/>
       </c>
     </row>
@@ -7983,7 +8367,7 @@
         <v>-8.06</v>
       </c>
       <c r="I129" s="1">
-        <v>8501773</v>
+        <v>8504092</v>
       </c>
       <c r="J129" s="1">
         <v>356.95</v>
@@ -7995,7 +8379,7 @@
         <v>327.27</v>
       </c>
       <c r="M129" s="3">
-        <v>-13.62</v>
+        <v>-5.7</v>
       </c>
       <c r="N129" s="3">
         <v>-5.17</v>
@@ -8010,9 +8394,12 @@
         <v>5.46</v>
       </c>
       <c r="R129" s="3">
-        <v>-5.17</v>
-      </c>
-      <c r="S129" t="str">
+        <v>14.8</v>
+      </c>
+      <c r="S129" s="3">
+        <v>29.73</v>
+      </c>
+      <c r="T129" t="str">
         <v/>
       </c>
     </row>
@@ -8042,7 +8429,7 @@
         <v>7.33</v>
       </c>
       <c r="I130" s="1">
-        <v>450625</v>
+        <v>450641</v>
       </c>
       <c r="J130" s="1">
         <v>3781.45</v>
@@ -8054,7 +8441,7 @@
         <v>4171.41</v>
       </c>
       <c r="M130" s="3">
-        <v>116.43</v>
+        <v>-33.9</v>
       </c>
       <c r="N130" s="3">
         <v>-46.31</v>
@@ -8069,9 +8456,12 @@
         <v>466.85</v>
       </c>
       <c r="R130" s="3">
-        <v>-46.31</v>
-      </c>
-      <c r="S130" t="str">
+        <v>453.61</v>
+      </c>
+      <c r="S130" s="3">
+        <v>45.4</v>
+      </c>
+      <c r="T130" t="str">
         <v/>
       </c>
     </row>
@@ -8101,7 +8491,7 @@
         <v>4.61</v>
       </c>
       <c r="I131" s="1">
-        <v>1168078</v>
+        <v>1168138</v>
       </c>
       <c r="J131" s="1">
         <v>932.05</v>
@@ -8113,7 +8503,7 @@
         <v>956.98</v>
       </c>
       <c r="M131" s="3">
-        <v>-22.5</v>
+        <v>-14.67</v>
       </c>
       <c r="N131" s="3">
         <v>-18.44</v>
@@ -8128,9 +8518,12 @@
         <v>-28.73</v>
       </c>
       <c r="R131" s="3">
-        <v>-18.44</v>
-      </c>
-      <c r="S131" t="str">
+        <v>-29.41</v>
+      </c>
+      <c r="S131" s="3">
+        <v>39.2</v>
+      </c>
+      <c r="T131" t="str">
         <v/>
       </c>
     </row>
@@ -8160,7 +8553,7 @@
         <v>-9.39</v>
       </c>
       <c r="I132" s="1">
-        <v>367877</v>
+        <v>367884</v>
       </c>
       <c r="J132" s="1">
         <v>1476.53</v>
@@ -8172,7 +8565,7 @@
         <v>1522.64</v>
       </c>
       <c r="M132" s="3">
-        <v>-7.2</v>
+        <v>-14.04</v>
       </c>
       <c r="N132" s="3">
         <v>-21</v>
@@ -8187,9 +8580,12 @@
         <v>59.36</v>
       </c>
       <c r="R132" s="3">
-        <v>-21</v>
-      </c>
-      <c r="S132" t="str">
+        <v>82.94</v>
+      </c>
+      <c r="S132" s="3">
+        <v>44.69</v>
+      </c>
+      <c r="T132" t="str">
         <v/>
       </c>
     </row>
@@ -8219,7 +8615,7 @@
         <v>-24.93</v>
       </c>
       <c r="I133" s="1">
-        <v>402233</v>
+        <v>402274</v>
       </c>
       <c r="J133" s="1">
         <v>1597.63</v>
@@ -8231,7 +8627,7 @@
         <v>1467.43</v>
       </c>
       <c r="M133" s="3">
-        <v>-76.7</v>
+        <v>-60.26</v>
       </c>
       <c r="N133" s="3">
         <v>-54.74</v>
@@ -8246,9 +8642,12 @@
         <v>75.69</v>
       </c>
       <c r="R133" s="3">
-        <v>-54.74</v>
-      </c>
-      <c r="S133" t="str">
+        <v>131.91</v>
+      </c>
+      <c r="S133" s="3">
+        <v>30.4</v>
+      </c>
+      <c r="T133" t="str">
         <v/>
       </c>
     </row>
@@ -8278,7 +8677,7 @@
         <v>-27.5</v>
       </c>
       <c r="I134" s="1">
-        <v>1284595</v>
+        <v>1286302</v>
       </c>
       <c r="J134" s="1">
         <v>470.6</v>
@@ -8290,7 +8689,7 @@
         <v>472.59</v>
       </c>
       <c r="M134" s="3">
-        <v>-12.59</v>
+        <v>-17.29</v>
       </c>
       <c r="N134" s="3">
         <v>-13.96</v>
@@ -8305,9 +8704,12 @@
         <v>-43.1</v>
       </c>
       <c r="R134" s="3">
-        <v>-13.96</v>
-      </c>
-      <c r="S134" t="str">
+        <v>-27.92</v>
+      </c>
+      <c r="S134" s="3">
+        <v>29.14</v>
+      </c>
+      <c r="T134" t="str">
         <v/>
       </c>
     </row>
@@ -8337,7 +8739,7 @@
         <v>24.34</v>
       </c>
       <c r="I135" s="1">
-        <v>2705926</v>
+        <v>2706388</v>
       </c>
       <c r="J135" s="1">
         <v>289.25</v>
@@ -8349,7 +8751,7 @@
         <v>334.1</v>
       </c>
       <c r="M135" s="3">
-        <v>16.35</v>
+        <v>1.01</v>
       </c>
       <c r="N135" s="3">
         <v>1.2</v>
@@ -8364,9 +8766,12 @@
         <v>32.7</v>
       </c>
       <c r="R135" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="S135" t="str">
+        <v>22.94</v>
+      </c>
+      <c r="S135" s="3">
+        <v>45.91</v>
+      </c>
+      <c r="T135" t="str">
         <v/>
       </c>
     </row>
@@ -8396,7 +8801,7 @@
         <v>-17.18</v>
       </c>
       <c r="I136" s="1">
-        <v>488307</v>
+        <v>488782</v>
       </c>
       <c r="J136" s="1">
         <v>1156.39</v>
@@ -8408,7 +8813,7 @@
         <v>1203.21</v>
       </c>
       <c r="M136" s="3">
-        <v>-5.71</v>
+        <v>-33.53</v>
       </c>
       <c r="N136" s="3">
         <v>-31.02</v>
@@ -8423,9 +8828,12 @@
         <v>68.21</v>
       </c>
       <c r="R136" s="3">
-        <v>-31.02</v>
-      </c>
-      <c r="S136" t="str">
+        <v>91.59</v>
+      </c>
+      <c r="S136" s="3">
+        <v>32.13</v>
+      </c>
+      <c r="T136" t="str">
         <v/>
       </c>
     </row>
@@ -8455,7 +8863,7 @@
         <v>-26.65</v>
       </c>
       <c r="I137" s="1">
-        <v>491203</v>
+        <v>491840</v>
       </c>
       <c r="J137" s="1">
         <v>1311.51</v>
@@ -8467,7 +8875,7 @@
         <v>1147.25</v>
       </c>
       <c r="M137" s="3">
-        <v>-83.28</v>
+        <v>-37.85</v>
       </c>
       <c r="N137" s="3">
         <v>-37.91</v>
@@ -8482,9 +8890,12 @@
         <v>-38.26</v>
       </c>
       <c r="R137" s="3">
-        <v>-37.91</v>
-      </c>
-      <c r="S137" t="str">
+        <v>11.02</v>
+      </c>
+      <c r="S137" s="3">
+        <v>30.02</v>
+      </c>
+      <c r="T137" t="str">
         <v/>
       </c>
     </row>
@@ -8514,7 +8925,7 @@
         <v>7.8</v>
       </c>
       <c r="I138" s="1">
-        <v>142058</v>
+        <v>142114</v>
       </c>
       <c r="J138" s="1">
         <v>10264.39</v>
@@ -8526,7 +8937,7 @@
         <v>11236.16</v>
       </c>
       <c r="M138" s="3">
-        <v>114.36</v>
+        <v>-314.59</v>
       </c>
       <c r="N138" s="3">
         <v>-350.58</v>
@@ -8541,9 +8952,12 @@
         <v>817.41</v>
       </c>
       <c r="R138" s="3">
-        <v>-350.58</v>
-      </c>
-      <c r="S138" t="str">
+        <v>768.72</v>
+      </c>
+      <c r="S138" s="3">
+        <v>36.39</v>
+      </c>
+      <c r="T138" t="str">
         <v/>
       </c>
     </row>
@@ -8573,7 +8987,7 @@
         <v>-38.37</v>
       </c>
       <c r="I139" s="1">
-        <v>8624465</v>
+        <v>8630450</v>
       </c>
       <c r="J139" s="1">
         <v>96.94</v>
@@ -8585,7 +8999,7 @@
         <v>81.71</v>
       </c>
       <c r="M139" s="3">
-        <v>-6.5</v>
+        <v>-0.96</v>
       </c>
       <c r="N139" s="3">
         <v>-1.31</v>
@@ -8600,9 +9014,12 @@
         <v>-9.44</v>
       </c>
       <c r="R139" s="3">
-        <v>-1.31</v>
-      </c>
-      <c r="S139" t="str">
+        <v>-3.63</v>
+      </c>
+      <c r="S139" s="3">
+        <v>41.79</v>
+      </c>
+      <c r="T139" t="str">
         <v/>
       </c>
     </row>
@@ -8632,7 +9049,7 @@
         <v>-4.68</v>
       </c>
       <c r="I140" s="1">
-        <v>4797614</v>
+        <v>4797915</v>
       </c>
       <c r="J140" s="1">
         <v>1285.42</v>
@@ -8644,7 +9061,7 @@
         <v>1243.73</v>
       </c>
       <c r="M140" s="3">
-        <v>-11.02</v>
+        <v>2.37</v>
       </c>
       <c r="N140" s="3">
         <v>2.56</v>
@@ -8659,9 +9076,12 @@
         <v>48.24</v>
       </c>
       <c r="R140" s="3">
-        <v>2.56</v>
-      </c>
-      <c r="S140" t="str">
+        <v>60.1</v>
+      </c>
+      <c r="S140" s="3">
+        <v>41.2</v>
+      </c>
+      <c r="T140" t="str">
         <v/>
       </c>
     </row>
@@ -8691,7 +9111,7 @@
         <v>10.61</v>
       </c>
       <c r="I141" s="1">
-        <v>681407</v>
+        <v>681443</v>
       </c>
       <c r="J141" s="1">
         <v>4437.33</v>
@@ -8703,7 +9123,7 @@
         <v>4851.1</v>
       </c>
       <c r="M141" s="3">
-        <v>123.87</v>
+        <v>31.02</v>
       </c>
       <c r="N141" s="3">
         <v>5.19</v>
@@ -8718,9 +9138,12 @@
         <v>287.58</v>
       </c>
       <c r="R141" s="3">
-        <v>5.19</v>
-      </c>
-      <c r="S141" t="str">
+        <v>314.86</v>
+      </c>
+      <c r="S141" s="3">
+        <v>52.24</v>
+      </c>
+      <c r="T141" t="str">
         <v/>
       </c>
     </row>
@@ -8750,7 +9173,7 @@
         <v>-34.56</v>
       </c>
       <c r="I142" s="1">
-        <v>3529560</v>
+        <v>3530562</v>
       </c>
       <c r="J142" s="1">
         <v>436.09</v>
@@ -8762,7 +9185,7 @@
         <v>359.32</v>
       </c>
       <c r="M142" s="3">
-        <v>-26.19</v>
+        <v>-0.33</v>
       </c>
       <c r="N142" s="3">
         <v>0.98</v>
@@ -8777,9 +9200,12 @@
         <v>-42.29</v>
       </c>
       <c r="R142" s="3">
-        <v>0.98</v>
-      </c>
-      <c r="S142" t="str">
+        <v>-16.64</v>
+      </c>
+      <c r="S142" s="3">
+        <v>44.33</v>
+      </c>
+      <c r="T142" t="str">
         <v/>
       </c>
     </row>
@@ -8809,7 +9235,7 @@
         <v>-25</v>
       </c>
       <c r="I143" s="1">
-        <v>3998245</v>
+        <v>3999098</v>
       </c>
       <c r="J143" s="1">
         <v>320.18</v>
@@ -8821,7 +9247,7 @@
         <v>306.73</v>
       </c>
       <c r="M143" s="3">
-        <v>-6.31</v>
+        <v>-5.12</v>
       </c>
       <c r="N143" s="3">
         <v>-5.14</v>
@@ -8836,9 +9262,12 @@
         <v>6.06</v>
       </c>
       <c r="R143" s="3">
-        <v>-5.14</v>
-      </c>
-      <c r="S143" t="str">
+        <v>14.46</v>
+      </c>
+      <c r="S143" s="3">
+        <v>38.31</v>
+      </c>
+      <c r="T143" t="str">
         <v/>
       </c>
     </row>
@@ -8868,7 +9297,7 @@
         <v>0.53</v>
       </c>
       <c r="I144" s="1">
-        <v>308094</v>
+        <v>308201</v>
       </c>
       <c r="J144" s="1">
         <v>1502.99</v>
@@ -8880,7 +9309,7 @@
         <v>1453.68</v>
       </c>
       <c r="M144" s="3">
-        <v>-29.43</v>
+        <v>-3.34</v>
       </c>
       <c r="N144" s="3">
         <v>-8.15</v>
@@ -8895,9 +9324,12 @@
         <v>-57.03</v>
       </c>
       <c r="R144" s="3">
-        <v>-8.15</v>
-      </c>
-      <c r="S144" t="str">
+        <v>-56.17</v>
+      </c>
+      <c r="S144" s="3">
+        <v>43.54</v>
+      </c>
+      <c r="T144" t="str">
         <v/>
       </c>
     </row>
@@ -8927,7 +9359,7 @@
         <v>-9.16</v>
       </c>
       <c r="I145" s="1">
-        <v>5341315</v>
+        <v>5342228</v>
       </c>
       <c r="J145" s="1">
         <v>1008.45</v>
@@ -8939,7 +9371,7 @@
         <v>1028.73</v>
       </c>
       <c r="M145" s="3">
-        <v>-6.97</v>
+        <v>-26.47</v>
       </c>
       <c r="N145" s="3">
         <v>-25.63</v>
@@ -8954,9 +9386,12 @@
         <v>122.32</v>
       </c>
       <c r="R145" s="3">
-        <v>-25.63</v>
-      </c>
-      <c r="S145" t="str">
+        <v>126.38</v>
+      </c>
+      <c r="S145" s="3">
+        <v>35.64</v>
+      </c>
+      <c r="T145" t="str">
         <v/>
       </c>
     </row>
@@ -8986,7 +9421,7 @@
         <v>-42.1</v>
       </c>
       <c r="I146" s="1">
-        <v>10460435</v>
+        <v>10467955</v>
       </c>
       <c r="J146" s="1">
         <v>282.35</v>
@@ -8998,7 +9433,7 @@
         <v>264.7</v>
       </c>
       <c r="M146" s="3">
-        <v>-14.62</v>
+        <v>-11.52</v>
       </c>
       <c r="N146" s="3">
         <v>-10.59</v>
@@ -9013,9 +9448,12 @@
         <v>-49.91</v>
       </c>
       <c r="R146" s="3">
-        <v>-10.59</v>
-      </c>
-      <c r="S146" t="str">
+        <v>-42.97</v>
+      </c>
+      <c r="S146" s="3">
+        <v>29.29</v>
+      </c>
+      <c r="T146" t="str">
         <v/>
       </c>
     </row>
@@ -9045,7 +9483,7 @@
         <v>53.2</v>
       </c>
       <c r="I147" s="1">
-        <v>97231</v>
+        <v>97243</v>
       </c>
       <c r="J147" s="1">
         <v>29075.58</v>
@@ -9057,7 +9495,7 @@
         <v>32075.2</v>
       </c>
       <c r="M147" s="3">
-        <v>198.25</v>
+        <v>-817.37</v>
       </c>
       <c r="N147" s="3">
         <v>-572.49</v>
@@ -9072,9 +9510,12 @@
         <v>5445.16</v>
       </c>
       <c r="R147" s="3">
-        <v>-572.49</v>
-      </c>
-      <c r="S147" t="str">
+        <v>5250.9</v>
+      </c>
+      <c r="S147" s="3">
+        <v>31.61</v>
+      </c>
+      <c r="T147" t="str">
         <v/>
       </c>
     </row>
@@ -9104,7 +9545,7 @@
         <v>15.84</v>
       </c>
       <c r="I148" s="1">
-        <v>906574</v>
+        <v>906844</v>
       </c>
       <c r="J148" s="1">
         <v>2594.24</v>
@@ -9116,7 +9557,7 @@
         <v>2912.33</v>
       </c>
       <c r="M148" s="3">
-        <v>34.68</v>
+        <v>-85.55</v>
       </c>
       <c r="N148" s="3">
         <v>-75.42</v>
@@ -9131,9 +9572,12 @@
         <v>71.84</v>
       </c>
       <c r="R148" s="3">
-        <v>-75.42</v>
-      </c>
-      <c r="S148" t="str">
+        <v>15.89</v>
+      </c>
+      <c r="S148" s="3">
+        <v>34.35</v>
+      </c>
+      <c r="T148" t="str">
         <v/>
       </c>
     </row>
@@ -9163,7 +9607,7 @@
         <v>27.38</v>
       </c>
       <c r="I149" s="1">
-        <v>11058537</v>
+        <v>11064613</v>
       </c>
       <c r="J149" s="1">
         <v>76.29</v>
@@ -9175,7 +9619,7 @@
         <v>82.06</v>
       </c>
       <c r="M149" s="3">
-        <v>1.8</v>
+        <v>-0.46</v>
       </c>
       <c r="N149" s="3">
         <v>-0.18</v>
@@ -9190,9 +9634,12 @@
         <v>8.45</v>
       </c>
       <c r="R149" s="3">
-        <v>-0.18</v>
-      </c>
-      <c r="S149" t="str">
+        <v>7.51</v>
+      </c>
+      <c r="S149" s="3">
+        <v>42.21</v>
+      </c>
+      <c r="T149" t="str">
         <v/>
       </c>
     </row>
@@ -9222,7 +9669,7 @@
         <v>-17.29</v>
       </c>
       <c r="I150" s="1">
-        <v>688898</v>
+        <v>688981</v>
       </c>
       <c r="J150" s="1">
         <v>2850.18</v>
@@ -9234,7 +9681,7 @@
         <v>2545.24</v>
       </c>
       <c r="M150" s="3">
-        <v>-146.45</v>
+        <v>-15.87</v>
       </c>
       <c r="N150" s="3">
         <v>-38.04</v>
@@ -9249,9 +9696,12 @@
         <v>-52.73</v>
       </c>
       <c r="R150" s="3">
-        <v>-38.04</v>
-      </c>
-      <c r="S150" t="str">
+        <v>27.93</v>
+      </c>
+      <c r="S150" s="3">
+        <v>47.98</v>
+      </c>
+      <c r="T150" t="str">
         <v/>
       </c>
     </row>
@@ -9281,7 +9731,7 @@
         <v>-32.92</v>
       </c>
       <c r="I151" s="1">
-        <v>382056</v>
+        <v>382080</v>
       </c>
       <c r="J151" s="1">
         <v>13663.22</v>
@@ -9293,7 +9743,7 @@
         <v>12541.24</v>
       </c>
       <c r="M151" s="3">
-        <v>-661.34</v>
+        <v>-343.61</v>
       </c>
       <c r="N151" s="3">
         <v>-382.13</v>
@@ -9308,9 +9758,12 @@
         <v>202.96</v>
       </c>
       <c r="R151" s="3">
-        <v>-382.13</v>
-      </c>
-      <c r="S151" t="str">
+        <v>659.51</v>
+      </c>
+      <c r="S151" s="3">
+        <v>33.14</v>
+      </c>
+      <c r="T151" t="str">
         <v/>
       </c>
     </row>
@@ -9340,7 +9793,7 @@
         <v>-1.08</v>
       </c>
       <c r="I152" s="1">
-        <v>755034</v>
+        <v>755043</v>
       </c>
       <c r="J152" s="1">
         <v>2781.98</v>
@@ -9352,7 +9805,7 @@
         <v>2850.43</v>
       </c>
       <c r="M152" s="3">
-        <v>-8.97</v>
+        <v>28.53</v>
       </c>
       <c r="N152" s="3">
         <v>15.1</v>
@@ -9367,9 +9820,12 @@
         <v>-42.98</v>
       </c>
       <c r="R152" s="3">
-        <v>15.1</v>
-      </c>
-      <c r="S152" t="str">
+        <v>27.97</v>
+      </c>
+      <c r="S152" s="3">
+        <v>47.85</v>
+      </c>
+      <c r="T152" t="str">
         <v/>
       </c>
     </row>
@@ -9399,7 +9855,7 @@
         <v>-1.94</v>
       </c>
       <c r="I153" s="1">
-        <v>553560</v>
+        <v>553565</v>
       </c>
       <c r="J153" s="1">
         <v>7399.34</v>
@@ -9411,7 +9867,7 @@
         <v>7574.2</v>
       </c>
       <c r="M153" s="3">
-        <v>-16.27</v>
+        <v>-92.45</v>
       </c>
       <c r="N153" s="3">
         <v>-139.55</v>
@@ -9426,9 +9882,12 @@
         <v>701.84</v>
       </c>
       <c r="R153" s="3">
-        <v>-139.55</v>
-      </c>
-      <c r="S153" t="str">
+        <v>759.53</v>
+      </c>
+      <c r="S153" s="3">
+        <v>45.46</v>
+      </c>
+      <c r="T153" t="str">
         <v/>
       </c>
     </row>
@@ -9458,7 +9917,7 @@
         <v>-25.19</v>
       </c>
       <c r="I154" s="1">
-        <v>60903532</v>
+        <v>60945986</v>
       </c>
       <c r="J154" s="1">
         <v>48.36</v>
@@ -9470,7 +9929,7 @@
         <v>43.53</v>
       </c>
       <c r="M154" s="3">
-        <v>-3.22</v>
+        <v>-0.97</v>
       </c>
       <c r="N154" s="3">
         <v>-1.39</v>
@@ -9485,9 +9944,12 @@
         <v>-0.87</v>
       </c>
       <c r="R154" s="3">
-        <v>-1.39</v>
-      </c>
-      <c r="S154" t="str">
+        <v>1.68</v>
+      </c>
+      <c r="S154" s="3">
+        <v>41.41</v>
+      </c>
+      <c r="T154" t="str">
         <v/>
       </c>
     </row>
@@ -9517,7 +9979,7 @@
         <v>12.34</v>
       </c>
       <c r="I155" s="1">
-        <v>27841130</v>
+        <v>27884023</v>
       </c>
       <c r="J155" s="1">
         <v>278.77</v>
@@ -9529,7 +9991,7 @@
         <v>323.91</v>
       </c>
       <c r="M155" s="3">
-        <v>14.73</v>
+        <v>-1.4</v>
       </c>
       <c r="N155" s="3">
         <v>-0.14</v>
@@ -9544,9 +10006,12 @@
         <v>26.27</v>
       </c>
       <c r="R155" s="3">
-        <v>-0.14</v>
-      </c>
-      <c r="S155" t="str">
+        <v>26.21</v>
+      </c>
+      <c r="S155" s="3">
+        <v>41.32</v>
+      </c>
+      <c r="T155" t="str">
         <v/>
       </c>
     </row>
@@ -9576,7 +10041,7 @@
         <v>-36.18</v>
       </c>
       <c r="I156" s="1">
-        <v>162501</v>
+        <v>162544</v>
       </c>
       <c r="J156" s="1">
         <v>2121.04</v>
@@ -9588,7 +10053,7 @@
         <v>1992.8</v>
       </c>
       <c r="M156" s="3">
-        <v>-122.49</v>
+        <v>-53.68</v>
       </c>
       <c r="N156" s="3">
         <v>-53.72</v>
@@ -9603,9 +10068,12 @@
         <v>44.14</v>
       </c>
       <c r="R156" s="3">
-        <v>-53.72</v>
-      </c>
-      <c r="S156" t="str">
+        <v>194.56</v>
+      </c>
+      <c r="S156" s="3">
+        <v>35.1</v>
+      </c>
+      <c r="T156" t="str">
         <v/>
       </c>
     </row>
@@ -9635,7 +10103,7 @@
         <v>-14.28</v>
       </c>
       <c r="I157" s="1">
-        <v>10494868</v>
+        <v>10500918</v>
       </c>
       <c r="J157" s="1">
         <v>584.19</v>
@@ -9647,7 +10115,7 @@
         <v>575.33</v>
       </c>
       <c r="M157" s="3">
-        <v>-4.19</v>
+        <v>-12.68</v>
       </c>
       <c r="N157" s="3">
         <v>-10.42</v>
@@ -9662,9 +10130,12 @@
         <v>34.59</v>
       </c>
       <c r="R157" s="3">
-        <v>-10.42</v>
-      </c>
-      <c r="S157" t="str">
+        <v>39.36</v>
+      </c>
+      <c r="S157" s="3">
+        <v>35.67</v>
+      </c>
+      <c r="T157" t="str">
         <v/>
       </c>
     </row>
@@ -9694,7 +10165,7 @@
         <v>-3.26</v>
       </c>
       <c r="I158" s="1">
-        <v>11973</v>
+        <v>11989</v>
       </c>
       <c r="J158" s="1">
         <v>36376.33</v>
@@ -9706,7 +10177,7 @@
         <v>36361</v>
       </c>
       <c r="M158" s="3">
-        <v>-478.94</v>
+        <v>-201.13</v>
       </c>
       <c r="N158" s="3">
         <v>-0.71</v>
@@ -9721,9 +10192,12 @@
         <v>-1280.8</v>
       </c>
       <c r="R158" s="3">
-        <v>-0.71</v>
-      </c>
-      <c r="S158" t="str">
+        <v>-923.44</v>
+      </c>
+      <c r="S158" s="3">
+        <v>36.15</v>
+      </c>
+      <c r="T158" t="str">
         <v/>
       </c>
     </row>
@@ -9753,7 +10227,7 @@
         <v>-3.12</v>
       </c>
       <c r="I159" s="1">
-        <v>34886</v>
+        <v>34899</v>
       </c>
       <c r="J159" s="1">
         <v>10664.99</v>
@@ -9765,7 +10239,7 @@
         <v>11120.74</v>
       </c>
       <c r="M159" s="3">
-        <v>74.93</v>
+        <v>-1.18</v>
       </c>
       <c r="N159" s="3">
         <v>-57.9</v>
@@ -9780,9 +10254,12 @@
         <v>268.87</v>
       </c>
       <c r="R159" s="3">
-        <v>-57.9</v>
-      </c>
-      <c r="S159" t="str">
+        <v>476.99</v>
+      </c>
+      <c r="S159" s="3">
+        <v>50.19</v>
+      </c>
+      <c r="T159" t="str">
         <v/>
       </c>
     </row>
@@ -9812,7 +10289,7 @@
         <v>-14.3</v>
       </c>
       <c r="I160" s="1">
-        <v>638982</v>
+        <v>639399</v>
       </c>
       <c r="J160" s="1">
         <v>1311.06</v>
@@ -9824,7 +10301,7 @@
         <v>1333.99</v>
       </c>
       <c r="M160" s="3">
-        <v>-14.95</v>
+        <v>-20.03</v>
       </c>
       <c r="N160" s="3">
         <v>-21.15</v>
@@ -9839,9 +10316,12 @@
         <v>28.14</v>
       </c>
       <c r="R160" s="3">
-        <v>-21.15</v>
-      </c>
-      <c r="S160" t="str">
+        <v>65.7</v>
+      </c>
+      <c r="S160" s="3">
+        <v>36.11</v>
+      </c>
+      <c r="T160" t="str">
         <v/>
       </c>
     </row>
@@ -9871,7 +10351,7 @@
         <v>-19.13</v>
       </c>
       <c r="I161" s="1">
-        <v>287159</v>
+        <v>287187</v>
       </c>
       <c r="J161" s="1">
         <v>2716.98</v>
@@ -9883,7 +10363,7 @@
         <v>2586.34</v>
       </c>
       <c r="M161" s="3">
-        <v>-163.16</v>
+        <v>-127.88</v>
       </c>
       <c r="N161" s="3">
         <v>-119.78</v>
@@ -9898,9 +10378,12 @@
         <v>-164.35</v>
       </c>
       <c r="R161" s="3">
-        <v>-119.78</v>
-      </c>
-      <c r="S161" t="str">
+        <v>-100.88</v>
+      </c>
+      <c r="S161" s="3">
+        <v>25.24</v>
+      </c>
+      <c r="T161" t="str">
         <v/>
       </c>
     </row>
@@ -9930,7 +10413,7 @@
         <v>-21.13</v>
       </c>
       <c r="I162" s="1">
-        <v>410818</v>
+        <v>411515</v>
       </c>
       <c r="J162" s="1">
         <v>3606.74</v>
@@ -9942,7 +10425,7 @@
         <v>3561.77</v>
       </c>
       <c r="M162" s="3">
-        <v>-146.9</v>
+        <v>-93.86</v>
       </c>
       <c r="N162" s="3">
         <v>-83.16</v>
@@ -9957,9 +10440,12 @@
         <v>-217.29</v>
       </c>
       <c r="R162" s="3">
-        <v>-83.16</v>
-      </c>
-      <c r="S162" t="str">
+        <v>53.3</v>
+      </c>
+      <c r="S162" s="3">
+        <v>34.22</v>
+      </c>
+      <c r="T162" t="str">
         <v/>
       </c>
     </row>
@@ -9989,7 +10475,7 @@
         <v>-44.79</v>
       </c>
       <c r="I163" s="1">
-        <v>2690703</v>
+        <v>2690829</v>
       </c>
       <c r="J163" s="1">
         <v>1577.19</v>
@@ -10001,7 +10487,7 @@
         <v>1527.99</v>
       </c>
       <c r="M163" s="3">
-        <v>-140.21</v>
+        <v>-151.99</v>
       </c>
       <c r="N163" s="3">
         <v>-166.93</v>
@@ -10016,9 +10502,12 @@
         <v>-14.37</v>
       </c>
       <c r="R163" s="3">
-        <v>-166.93</v>
-      </c>
-      <c r="S163" t="str">
+        <v>76.57</v>
+      </c>
+      <c r="S163" s="3">
+        <v>28.8</v>
+      </c>
+      <c r="T163" t="str">
         <v/>
       </c>
     </row>
@@ -10048,7 +10537,7 @@
         <v>8.32</v>
       </c>
       <c r="I164" s="1">
-        <v>11319288</v>
+        <v>11328812</v>
       </c>
       <c r="J164" s="1">
         <v>269.28</v>
@@ -10060,7 +10549,7 @@
         <v>265.47</v>
       </c>
       <c r="M164" s="3">
-        <v>-3.81</v>
+        <v>-6.12</v>
       </c>
       <c r="N164" s="3">
         <v>-4.23</v>
@@ -10075,9 +10564,12 @@
         <v>33.31</v>
       </c>
       <c r="R164" s="3">
-        <v>-4.23</v>
-      </c>
-      <c r="S164" t="str">
+        <v>33.66</v>
+      </c>
+      <c r="S164" s="3">
+        <v>33.78</v>
+      </c>
+      <c r="T164" t="str">
         <v/>
       </c>
     </row>
@@ -10107,7 +10599,7 @@
         <v>23.41</v>
       </c>
       <c r="I165" s="1">
-        <v>2317228</v>
+        <v>2317996</v>
       </c>
       <c r="J165" s="1">
         <v>3341.5</v>
@@ -10119,7 +10611,7 @@
         <v>3310.77</v>
       </c>
       <c r="M165" s="3">
-        <v>-34.05</v>
+        <v>10.09</v>
       </c>
       <c r="N165" s="3">
         <v>-1.97</v>
@@ -10134,9 +10626,12 @@
         <v>547.15</v>
       </c>
       <c r="R165" s="3">
-        <v>-1.97</v>
-      </c>
-      <c r="S165" t="str">
+        <v>577.04</v>
+      </c>
+      <c r="S165" s="3">
+        <v>46.88</v>
+      </c>
+      <c r="T165" t="str">
         <v/>
       </c>
     </row>
@@ -10166,7 +10661,7 @@
         <v>33.46</v>
       </c>
       <c r="I166" s="1">
-        <v>1188561</v>
+        <v>1188669</v>
       </c>
       <c r="J166" s="1">
         <v>1442.66</v>
@@ -10178,7 +10673,7 @@
         <v>1665.49</v>
       </c>
       <c r="M166" s="3">
-        <v>71.64</v>
+        <v>-9.65</v>
       </c>
       <c r="N166" s="3">
         <v>2.08</v>
@@ -10193,9 +10688,12 @@
         <v>143.44</v>
       </c>
       <c r="R166" s="3">
-        <v>2.08</v>
-      </c>
-      <c r="S166" t="str">
+        <v>108.74</v>
+      </c>
+      <c r="S166" s="3">
+        <v>34.95</v>
+      </c>
+      <c r="T166" t="str">
         <v/>
       </c>
     </row>
@@ -10225,7 +10723,7 @@
         <v>-19.79</v>
       </c>
       <c r="I167" s="1">
-        <v>431638</v>
+        <v>432028</v>
       </c>
       <c r="J167" s="1">
         <v>2408.09</v>
@@ -10237,7 +10735,7 @@
         <v>2323.67</v>
       </c>
       <c r="M167" s="3">
-        <v>-111.73</v>
+        <v>-71.84</v>
       </c>
       <c r="N167" s="3">
         <v>-79.89</v>
@@ -10252,9 +10750,12 @@
         <v>89.86</v>
       </c>
       <c r="R167" s="3">
-        <v>-79.89</v>
-      </c>
-      <c r="S167" t="str">
+        <v>212.97</v>
+      </c>
+      <c r="S167" s="3">
+        <v>32.24</v>
+      </c>
+      <c r="T167" t="str">
         <v/>
       </c>
     </row>
@@ -10284,7 +10785,7 @@
         <v>-21.55</v>
       </c>
       <c r="I168" s="1">
-        <v>334233</v>
+        <v>334299</v>
       </c>
       <c r="J168" s="1">
         <v>926.87</v>
@@ -10296,7 +10797,7 @@
         <v>908.74</v>
       </c>
       <c r="M168" s="3">
-        <v>-18.71</v>
+        <v>-9.48</v>
       </c>
       <c r="N168" s="3">
         <v>-12.26</v>
@@ -10311,9 +10812,12 @@
         <v>6.13</v>
       </c>
       <c r="R168" s="3">
-        <v>-12.26</v>
-      </c>
-      <c r="S168" t="str">
+        <v>43.41</v>
+      </c>
+      <c r="S168" s="3">
+        <v>41.56</v>
+      </c>
+      <c r="T168" t="str">
         <v/>
       </c>
     </row>
@@ -10343,7 +10847,7 @@
         <v>81.63</v>
       </c>
       <c r="I169" s="1">
-        <v>1184253</v>
+        <v>1186293</v>
       </c>
       <c r="J169" s="1">
         <v>1412.78</v>
@@ -10355,7 +10859,7 @@
         <v>1938.26</v>
       </c>
       <c r="M169" s="3">
-        <v>207.36</v>
+        <v>32.58</v>
       </c>
       <c r="N169" s="3">
         <v>37.93</v>
@@ -10370,9 +10874,12 @@
         <v>349.18</v>
       </c>
       <c r="R169" s="3">
-        <v>37.93</v>
-      </c>
-      <c r="S169" t="str">
+        <v>249.17</v>
+      </c>
+      <c r="S169" s="3">
+        <v>52.3</v>
+      </c>
+      <c r="T169" t="str">
         <v/>
       </c>
     </row>
@@ -10402,7 +10909,7 @@
         <v>-3.65</v>
       </c>
       <c r="I170" s="1">
-        <v>1985198</v>
+        <v>1985612</v>
       </c>
       <c r="J170" s="1">
         <v>444.2</v>
@@ -10414,7 +10921,7 @@
         <v>435.09</v>
       </c>
       <c r="M170" s="3">
-        <v>-13.11</v>
+        <v>-10.14</v>
       </c>
       <c r="N170" s="3">
         <v>-10.56</v>
@@ -10429,9 +10936,12 @@
         <v>9.58</v>
       </c>
       <c r="R170" s="3">
-        <v>-10.56</v>
-      </c>
-      <c r="S170" t="str">
+        <v>11.06</v>
+      </c>
+      <c r="S170" s="3">
+        <v>33.36</v>
+      </c>
+      <c r="T170" t="str">
         <v/>
       </c>
     </row>
@@ -10473,7 +10983,7 @@
         <v>20036</v>
       </c>
       <c r="M171" s="3">
-        <v>1022.26</v>
+        <v>-40.57</v>
       </c>
       <c r="N171" s="3">
         <v>-19.78</v>
@@ -10488,9 +10998,12 @@
         <v>2571.16</v>
       </c>
       <c r="R171" s="3">
-        <v>-19.78</v>
-      </c>
-      <c r="S171" t="str">
+        <v>2227.43</v>
+      </c>
+      <c r="S171" s="3">
+        <v>43.15</v>
+      </c>
+      <c r="T171" t="str">
         <v/>
       </c>
     </row>
@@ -10520,7 +11033,7 @@
         <v>-25.95</v>
       </c>
       <c r="I172" s="1">
-        <v>7785261</v>
+        <v>7792466</v>
       </c>
       <c r="J172" s="1">
         <v>122.87</v>
@@ -10532,7 +11045,7 @@
         <v>112.29</v>
       </c>
       <c r="M172" s="3">
-        <v>-5.8</v>
+        <v>-1.88</v>
       </c>
       <c r="N172" s="3">
         <v>-1.82</v>
@@ -10547,9 +11060,12 @@
         <v>-9.97</v>
       </c>
       <c r="R172" s="3">
-        <v>-1.82</v>
-      </c>
-      <c r="S172" t="str">
+        <v>-4.72</v>
+      </c>
+      <c r="S172" s="3">
+        <v>35.7</v>
+      </c>
+      <c r="T172" t="str">
         <v/>
       </c>
     </row>
@@ -10579,7 +11095,7 @@
         <v>-24.03</v>
       </c>
       <c r="I173" s="1">
-        <v>203543214</v>
+        <v>203693471</v>
       </c>
       <c r="J173" s="1">
         <v>21.72</v>
@@ -10591,7 +11107,7 @@
         <v>21.81</v>
       </c>
       <c r="M173" s="3">
-        <v>-0.79</v>
+        <v>-1.28</v>
       </c>
       <c r="N173" s="3">
         <v>-0.82</v>
@@ -10606,9 +11122,12 @@
         <v>-0.12</v>
       </c>
       <c r="R173" s="3">
-        <v>-0.82</v>
-      </c>
-      <c r="S173" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="S173" s="3">
+        <v>19.15</v>
+      </c>
+      <c r="T173" t="str">
         <v/>
       </c>
     </row>
@@ -10638,7 +11157,7 @@
         <v>-35.06</v>
       </c>
       <c r="I174" s="1">
-        <v>636876</v>
+        <v>636882</v>
       </c>
       <c r="J174" s="1">
         <v>2798.64</v>
@@ -10650,7 +11169,7 @@
         <v>2360.11</v>
       </c>
       <c r="M174" s="3">
-        <v>-212.83</v>
+        <v>-66.69</v>
       </c>
       <c r="N174" s="3">
         <v>-67.09</v>
@@ -10665,9 +11184,12 @@
         <v>-344.57</v>
       </c>
       <c r="R174" s="3">
-        <v>-67.09</v>
-      </c>
-      <c r="S174" t="str">
+        <v>-215.24</v>
+      </c>
+      <c r="S174" s="3">
+        <v>34.1</v>
+      </c>
+      <c r="T174" t="str">
         <v/>
       </c>
     </row>
@@ -10697,7 +11219,7 @@
         <v>-24.79</v>
       </c>
       <c r="I175" s="1">
-        <v>445885</v>
+        <v>445970</v>
       </c>
       <c r="J175" s="1">
         <v>1246.05</v>
@@ -10709,7 +11231,7 @@
         <v>1153.82</v>
       </c>
       <c r="M175" s="3">
-        <v>-53.69</v>
+        <v>-12.07</v>
       </c>
       <c r="N175" s="3">
         <v>-22.3</v>
@@ -10724,9 +11246,12 @@
         <v>-104.18</v>
       </c>
       <c r="R175" s="3">
-        <v>-22.3</v>
-      </c>
-      <c r="S175" t="str">
+        <v>-66.33</v>
+      </c>
+      <c r="S175" s="3">
+        <v>44.2</v>
+      </c>
+      <c r="T175" t="str">
         <v/>
       </c>
     </row>
@@ -10756,7 +11281,7 @@
         <v>21.75</v>
       </c>
       <c r="I176" s="1">
-        <v>749701</v>
+        <v>750238</v>
       </c>
       <c r="J176" s="1">
         <v>4122.03</v>
@@ -10768,7 +11293,7 @@
         <v>4275.89</v>
       </c>
       <c r="M176" s="3">
-        <v>-17.26</v>
+        <v>-105.81</v>
       </c>
       <c r="N176" s="3">
         <v>-65.48</v>
@@ -10783,9 +11308,12 @@
         <v>759.42</v>
       </c>
       <c r="R176" s="3">
-        <v>-65.48</v>
-      </c>
-      <c r="S176" t="str">
+        <v>776.17</v>
+      </c>
+      <c r="S176" s="3">
+        <v>29.8</v>
+      </c>
+      <c r="T176" t="str">
         <v/>
       </c>
     </row>
@@ -10815,7 +11343,7 @@
         <v>23.98</v>
       </c>
       <c r="I177" s="1">
-        <v>1690990</v>
+        <v>1691292</v>
       </c>
       <c r="J177" s="1">
         <v>1212.38</v>
@@ -10827,7 +11355,7 @@
         <v>1296.83</v>
       </c>
       <c r="M177" s="3">
-        <v>11.2</v>
+        <v>-4.1</v>
       </c>
       <c r="N177" s="3">
         <v>-5.53</v>
@@ -10842,9 +11370,12 @@
         <v>6.88</v>
       </c>
       <c r="R177" s="3">
-        <v>-5.53</v>
-      </c>
-      <c r="S177" t="str">
+        <v>-34.85</v>
+      </c>
+      <c r="S177" s="3">
+        <v>44.54</v>
+      </c>
+      <c r="T177" t="str">
         <v/>
       </c>
     </row>
@@ -10874,7 +11405,7 @@
         <v>-16.13</v>
       </c>
       <c r="I178" s="1">
-        <v>12295373</v>
+        <v>12300519</v>
       </c>
       <c r="J178" s="1">
         <v>99.16</v>
@@ -10886,7 +11417,7 @@
         <v>96.32</v>
       </c>
       <c r="M178" s="3">
-        <v>-2.38</v>
+        <v>-2.31</v>
       </c>
       <c r="N178" s="3">
         <v>-2.14</v>
@@ -10901,9 +11432,12 @@
         <v>5.43</v>
       </c>
       <c r="R178" s="3">
-        <v>-2.14</v>
-      </c>
-      <c r="S178" t="str">
+        <v>7.2</v>
+      </c>
+      <c r="S178" s="3">
+        <v>35.9</v>
+      </c>
+      <c r="T178" t="str">
         <v/>
       </c>
     </row>
@@ -10933,7 +11467,7 @@
         <v>9.11</v>
       </c>
       <c r="I179" s="1">
-        <v>8555378</v>
+        <v>8556692</v>
       </c>
       <c r="J179" s="1">
         <v>176.77</v>
@@ -10945,7 +11479,7 @@
         <v>171.48</v>
       </c>
       <c r="M179" s="3">
-        <v>-4.09</v>
+        <v>-3.15</v>
       </c>
       <c r="N179" s="3">
         <v>-2.45</v>
@@ -10960,9 +11494,12 @@
         <v>-5.85</v>
       </c>
       <c r="R179" s="3">
-        <v>-2.45</v>
-      </c>
-      <c r="S179" t="str">
+        <v>-8.64</v>
+      </c>
+      <c r="S179" s="3">
+        <v>40.27</v>
+      </c>
+      <c r="T179" t="str">
         <v/>
       </c>
     </row>
@@ -10992,7 +11529,7 @@
         <v>-16.63</v>
       </c>
       <c r="I180" s="1">
-        <v>4798154</v>
+        <v>4798889</v>
       </c>
       <c r="J180" s="1">
         <v>462.27</v>
@@ -11004,7 +11541,7 @@
         <v>426.1</v>
       </c>
       <c r="M180" s="3">
-        <v>-15.01</v>
+        <v>-0.62</v>
       </c>
       <c r="N180" s="3">
         <v>1.84</v>
@@ -11019,9 +11556,12 @@
         <v>-9.59</v>
       </c>
       <c r="R180" s="3">
-        <v>1.84</v>
-      </c>
-      <c r="S180" t="str">
+        <v>2.71</v>
+      </c>
+      <c r="S180" s="3">
+        <v>37.39</v>
+      </c>
+      <c r="T180" t="str">
         <v/>
       </c>
     </row>
@@ -11051,7 +11591,7 @@
         <v>-0.74</v>
       </c>
       <c r="I181" s="1">
-        <v>101996</v>
+        <v>101998</v>
       </c>
       <c r="J181" s="1">
         <v>7229.63</v>
@@ -11063,7 +11603,7 @@
         <v>7058.47</v>
       </c>
       <c r="M181" s="3">
-        <v>-232.21</v>
+        <v>-166.85</v>
       </c>
       <c r="N181" s="3">
         <v>-162.81</v>
@@ -11078,9 +11618,12 @@
         <v>506.06</v>
       </c>
       <c r="R181" s="3">
-        <v>-162.81</v>
-      </c>
-      <c r="S181" t="str">
+        <v>722.3</v>
+      </c>
+      <c r="S181" s="3">
+        <v>34.65</v>
+      </c>
+      <c r="T181" t="str">
         <v/>
       </c>
     </row>
@@ -11110,7 +11653,7 @@
         <v>-22.27</v>
       </c>
       <c r="I182" s="1">
-        <v>3385491</v>
+        <v>3390042</v>
       </c>
       <c r="J182" s="1">
         <v>290.63</v>
@@ -11122,7 +11665,7 @@
         <v>295.23</v>
       </c>
       <c r="M182" s="3">
-        <v>-6.2</v>
+        <v>-12.77</v>
       </c>
       <c r="N182" s="3">
         <v>-12.15</v>
@@ -11137,9 +11680,12 @@
         <v>31.46</v>
       </c>
       <c r="R182" s="3">
-        <v>-12.15</v>
-      </c>
-      <c r="S182" t="str">
+        <v>36.01</v>
+      </c>
+      <c r="S182" s="3">
+        <v>27.59</v>
+      </c>
+      <c r="T182" t="str">
         <v/>
       </c>
     </row>
@@ -11169,7 +11715,7 @@
         <v>-34.68</v>
       </c>
       <c r="I183" s="1">
-        <v>942622</v>
+        <v>942681</v>
       </c>
       <c r="J183" s="1">
         <v>3241.9</v>
@@ -11181,7 +11727,7 @@
         <v>2826.11</v>
       </c>
       <c r="M183" s="3">
-        <v>-173.86</v>
+        <v>-82.53</v>
       </c>
       <c r="N183" s="3">
         <v>-74.26</v>
@@ -11196,9 +11742,12 @@
         <v>225.91</v>
       </c>
       <c r="R183" s="3">
-        <v>-74.26</v>
-      </c>
-      <c r="S183" t="str">
+        <v>361.88</v>
+      </c>
+      <c r="S183" s="3">
+        <v>27.93</v>
+      </c>
+      <c r="T183" t="str">
         <v/>
       </c>
     </row>
@@ -11228,7 +11777,7 @@
         <v>-35.3</v>
       </c>
       <c r="I184" s="1">
-        <v>2003160</v>
+        <v>2003415</v>
       </c>
       <c r="J184" s="1">
         <v>628.49</v>
@@ -11240,7 +11789,7 @@
         <v>553.16</v>
       </c>
       <c r="M184" s="3">
-        <v>-32.44</v>
+        <v>-9.45</v>
       </c>
       <c r="N184" s="3">
         <v>-12.45</v>
@@ -11255,9 +11804,12 @@
         <v>-19.53</v>
       </c>
       <c r="R184" s="3">
-        <v>-12.45</v>
-      </c>
-      <c r="S184" t="str">
+        <v>-0.55</v>
+      </c>
+      <c r="S184" s="3">
+        <v>41.87</v>
+      </c>
+      <c r="T184" t="str">
         <v/>
       </c>
     </row>
@@ -11287,7 +11839,7 @@
         <v>28.88</v>
       </c>
       <c r="I185" s="1">
-        <v>1266673</v>
+        <v>1266824</v>
       </c>
       <c r="J185" s="1">
         <v>1302.52</v>
@@ -11299,7 +11851,7 @@
         <v>1424.99</v>
       </c>
       <c r="M185" s="3">
-        <v>8.55</v>
+        <v>-21.68</v>
       </c>
       <c r="N185" s="3">
         <v>-33.51</v>
@@ -11314,9 +11866,12 @@
         <v>101.64</v>
       </c>
       <c r="R185" s="3">
-        <v>-33.51</v>
-      </c>
-      <c r="S185" t="str">
+        <v>49.88</v>
+      </c>
+      <c r="S185" s="3">
+        <v>44.65</v>
+      </c>
+      <c r="T185" t="str">
         <v/>
       </c>
     </row>
@@ -11346,7 +11901,7 @@
         <v>-41.32</v>
       </c>
       <c r="I186" s="1">
-        <v>5935192</v>
+        <v>5936727</v>
       </c>
       <c r="J186" s="1">
         <v>93.79</v>
@@ -11358,7 +11913,7 @@
         <v>83.17</v>
       </c>
       <c r="M186" s="3">
-        <v>-6.33</v>
+        <v>-2.85</v>
       </c>
       <c r="N186" s="3">
         <v>-2.76</v>
@@ -11373,9 +11928,12 @@
         <v>-0.36</v>
       </c>
       <c r="R186" s="3">
-        <v>-2.76</v>
-      </c>
-      <c r="S186" t="str">
+        <v>4.74</v>
+      </c>
+      <c r="S186" s="3">
+        <v>26.87</v>
+      </c>
+      <c r="T186" t="str">
         <v/>
       </c>
     </row>
@@ -11405,7 +11963,7 @@
         <v>38.6</v>
       </c>
       <c r="I187" s="1">
-        <v>1242045</v>
+        <v>1242596</v>
       </c>
       <c r="J187" s="1">
         <v>2812.45</v>
@@ -11417,7 +11975,7 @@
         <v>3216.67</v>
       </c>
       <c r="M187" s="3">
-        <v>159.16</v>
+        <v>-10.64</v>
       </c>
       <c r="N187" s="3">
         <v>16.91</v>
@@ -11432,9 +11990,12 @@
         <v>569.1</v>
       </c>
       <c r="R187" s="3">
-        <v>16.91</v>
-      </c>
-      <c r="S187" t="str">
+        <v>504.22</v>
+      </c>
+      <c r="S187" s="3">
+        <v>41.02</v>
+      </c>
+      <c r="T187" t="str">
         <v/>
       </c>
     </row>
@@ -11464,7 +12025,7 @@
         <v>-14.42</v>
       </c>
       <c r="I188" s="1">
-        <v>1045070</v>
+        <v>1045140</v>
       </c>
       <c r="J188" s="1">
         <v>550.26</v>
@@ -11476,7 +12037,7 @@
         <v>549.66</v>
       </c>
       <c r="M188" s="3">
-        <v>-12.8</v>
+        <v>-9.09</v>
       </c>
       <c r="N188" s="3">
         <v>-10.71</v>
@@ -11491,9 +12052,12 @@
         <v>8.45</v>
       </c>
       <c r="R188" s="3">
-        <v>-10.71</v>
-      </c>
-      <c r="S188" t="str">
+        <v>33.99</v>
+      </c>
+      <c r="S188" s="3">
+        <v>35.92</v>
+      </c>
+      <c r="T188" t="str">
         <v/>
       </c>
     </row>
@@ -11523,7 +12087,7 @@
         <v>-47.26</v>
       </c>
       <c r="I189" s="1">
-        <v>3382642</v>
+        <v>3390719</v>
       </c>
       <c r="J189" s="1">
         <v>261.22</v>
@@ -11535,7 +12099,7 @@
         <v>208.85</v>
       </c>
       <c r="M189" s="3">
-        <v>-21.72</v>
+        <v>-4.39</v>
       </c>
       <c r="N189" s="3">
         <v>-4.61</v>
@@ -11550,9 +12114,12 @@
         <v>-28.67</v>
       </c>
       <c r="R189" s="3">
-        <v>-4.61</v>
-      </c>
-      <c r="S189" t="str">
+        <v>-7.91</v>
+      </c>
+      <c r="S189" s="3">
+        <v>36.37</v>
+      </c>
+      <c r="T189" t="str">
         <v/>
       </c>
     </row>
@@ -11582,7 +12149,7 @@
         <v>1.99</v>
       </c>
       <c r="I190" s="1">
-        <v>299556</v>
+        <v>299588</v>
       </c>
       <c r="J190" s="1">
         <v>8427.94</v>
@@ -11594,7 +12161,7 @@
         <v>8569.47</v>
       </c>
       <c r="M190" s="3">
-        <v>-106.93</v>
+        <v>-125.61</v>
       </c>
       <c r="N190" s="3">
         <v>-118.52</v>
@@ -11609,9 +12176,12 @@
         <v>804.75</v>
       </c>
       <c r="R190" s="3">
-        <v>-118.52</v>
-      </c>
-      <c r="S190" t="str">
+        <v>857.1</v>
+      </c>
+      <c r="S190" s="3">
+        <v>32.93</v>
+      </c>
+      <c r="T190" t="str">
         <v/>
       </c>
     </row>
@@ -11641,7 +12211,7 @@
         <v>25.09</v>
       </c>
       <c r="I191" s="1">
-        <v>3965430</v>
+        <v>3966785</v>
       </c>
       <c r="J191" s="1">
         <v>289.57</v>
@@ -11653,7 +12223,7 @@
         <v>293.52</v>
       </c>
       <c r="M191" s="3">
-        <v>-0.82</v>
+        <v>2.3</v>
       </c>
       <c r="N191" s="3">
         <v>1.37</v>
@@ -11668,9 +12238,12 @@
         <v>16.05</v>
       </c>
       <c r="R191" s="3">
-        <v>1.37</v>
-      </c>
-      <c r="S191" t="str">
+        <v>15.22</v>
+      </c>
+      <c r="S191" s="3">
+        <v>47.96</v>
+      </c>
+      <c r="T191" t="str">
         <v/>
       </c>
     </row>
@@ -11700,7 +12273,7 @@
         <v>-6.16</v>
       </c>
       <c r="I192" s="1">
-        <v>18051709</v>
+        <v>18054314</v>
       </c>
       <c r="J192" s="1">
         <v>974.22</v>
@@ -11712,7 +12285,7 @@
         <v>1027.43</v>
       </c>
       <c r="M192" s="3">
-        <v>0.39</v>
+        <v>-20.4</v>
       </c>
       <c r="N192" s="3">
         <v>-20.99</v>
@@ -11727,9 +12300,12 @@
         <v>56.73</v>
       </c>
       <c r="R192" s="3">
-        <v>-20.99</v>
-      </c>
-      <c r="S192" t="str">
+        <v>64.1</v>
+      </c>
+      <c r="S192" s="3">
+        <v>35.76</v>
+      </c>
+      <c r="T192" t="str">
         <v/>
       </c>
     </row>
@@ -11759,7 +12335,7 @@
         <v>-18.63</v>
       </c>
       <c r="I193" s="1">
-        <v>1777332</v>
+        <v>1777922</v>
       </c>
       <c r="J193" s="1">
         <v>488.8</v>
@@ -11771,7 +12347,7 @@
         <v>484.17</v>
       </c>
       <c r="M193" s="3">
-        <v>-12.67</v>
+        <v>-12.68</v>
       </c>
       <c r="N193" s="3">
         <v>-13.55</v>
@@ -11786,9 +12362,12 @@
         <v>-40.56</v>
       </c>
       <c r="R193" s="3">
-        <v>-13.55</v>
-      </c>
-      <c r="S193" t="str">
+        <v>-35.65</v>
+      </c>
+      <c r="S193" s="3">
+        <v>30.66</v>
+      </c>
+      <c r="T193" t="str">
         <v/>
       </c>
     </row>
@@ -11818,7 +12397,7 @@
         <v>-3.41</v>
       </c>
       <c r="I194" s="1">
-        <v>498076</v>
+        <v>498181</v>
       </c>
       <c r="J194" s="1">
         <v>12091.19</v>
@@ -11830,7 +12409,7 @@
         <v>13612.54</v>
       </c>
       <c r="M194" s="3">
-        <v>54.71</v>
+        <v>-394.06</v>
       </c>
       <c r="N194" s="3">
         <v>-317.94</v>
@@ -11845,9 +12424,12 @@
         <v>388.29</v>
       </c>
       <c r="R194" s="3">
-        <v>-317.94</v>
-      </c>
-      <c r="S194" t="str">
+        <v>701.56</v>
+      </c>
+      <c r="S194" s="3">
+        <v>26.32</v>
+      </c>
+      <c r="T194" t="str">
         <v/>
       </c>
     </row>
@@ -11877,7 +12459,7 @@
         <v>-49.31</v>
       </c>
       <c r="I195" s="1">
-        <v>8085936</v>
+        <v>8087711</v>
       </c>
       <c r="J195" s="1">
         <v>88.28</v>
@@ -11889,7 +12471,7 @@
         <v>72.23</v>
       </c>
       <c r="M195" s="3">
-        <v>-8.15</v>
+        <v>-2.26</v>
       </c>
       <c r="N195" s="3">
         <v>-1.93</v>
@@ -11904,9 +12486,12 @@
         <v>-17.22</v>
       </c>
       <c r="R195" s="3">
-        <v>-1.93</v>
-      </c>
-      <c r="S195" t="str">
+        <v>-8.5</v>
+      </c>
+      <c r="S195" s="3">
+        <v>33.62</v>
+      </c>
+      <c r="T195" t="str">
         <v/>
       </c>
     </row>
@@ -11936,7 +12521,7 @@
         <v>15.1</v>
       </c>
       <c r="I196" s="1">
-        <v>1017639</v>
+        <v>1018366</v>
       </c>
       <c r="J196" s="1">
         <v>868.57</v>
@@ -11948,7 +12533,7 @@
         <v>1004.55</v>
       </c>
       <c r="M196" s="3">
-        <v>45.43</v>
+        <v>7.5</v>
       </c>
       <c r="N196" s="3">
         <v>12.31</v>
@@ -11963,9 +12548,12 @@
         <v>95.05</v>
       </c>
       <c r="R196" s="3">
-        <v>12.31</v>
-      </c>
-      <c r="S196" t="str">
+        <v>93.08</v>
+      </c>
+      <c r="S196" s="3">
+        <v>43.52</v>
+      </c>
+      <c r="T196" t="str">
         <v/>
       </c>
     </row>
@@ -11995,7 +12583,7 @@
         <v>59.76</v>
       </c>
       <c r="I197" s="1">
-        <v>2337783</v>
+        <v>2338457</v>
       </c>
       <c r="J197" s="1">
         <v>631.19</v>
@@ -12007,7 +12595,7 @@
         <v>803.65</v>
       </c>
       <c r="M197" s="3">
-        <v>55.91</v>
+        <v>-2.72</v>
       </c>
       <c r="N197" s="3">
         <v>1.18</v>
@@ -12022,9 +12610,12 @@
         <v>57.31</v>
       </c>
       <c r="R197" s="3">
-        <v>1.18</v>
-      </c>
-      <c r="S197" t="str">
+        <v>20.97</v>
+      </c>
+      <c r="S197" s="3">
+        <v>39.59</v>
+      </c>
+      <c r="T197" t="str">
         <v/>
       </c>
     </row>
@@ -12054,7 +12645,7 @@
         <v>-20.29</v>
       </c>
       <c r="I198" s="1">
-        <v>5812132</v>
+        <v>5812673</v>
       </c>
       <c r="J198" s="1">
         <v>251.05</v>
@@ -12066,7 +12657,7 @@
         <v>227.06</v>
       </c>
       <c r="M198" s="3">
-        <v>-15.56</v>
+        <v>-5.52</v>
       </c>
       <c r="N198" s="3">
         <v>-6.21</v>
@@ -12081,9 +12672,12 @@
         <v>-31.31</v>
       </c>
       <c r="R198" s="3">
-        <v>-6.21</v>
-      </c>
-      <c r="S198" t="str">
+        <v>-25.32</v>
+      </c>
+      <c r="S198" s="3">
+        <v>34.2</v>
+      </c>
+      <c r="T198" t="str">
         <v/>
       </c>
     </row>
@@ -12113,7 +12707,7 @@
         <v>30.84</v>
       </c>
       <c r="I199" s="1">
-        <v>18556828</v>
+        <v>18562784</v>
       </c>
       <c r="J199" s="1">
         <v>190.14</v>
@@ -12125,7 +12719,7 @@
         <v>202.6</v>
       </c>
       <c r="M199" s="3">
-        <v>0.7</v>
+        <v>-3.75</v>
       </c>
       <c r="N199" s="3">
         <v>-3.64</v>
@@ -12140,9 +12734,12 @@
         <v>27.2</v>
       </c>
       <c r="R199" s="3">
-        <v>-3.64</v>
-      </c>
-      <c r="S199" t="str">
+        <v>25.08</v>
+      </c>
+      <c r="S199" s="3">
+        <v>39</v>
+      </c>
+      <c r="T199" t="str">
         <v/>
       </c>
     </row>
@@ -12172,7 +12769,7 @@
         <v>7.98</v>
       </c>
       <c r="I200" s="1">
-        <v>542798</v>
+        <v>542809</v>
       </c>
       <c r="J200" s="1">
         <v>2004.54</v>
@@ -12184,7 +12781,7 @@
         <v>2150.62</v>
       </c>
       <c r="M200" s="3">
-        <v>63.59</v>
+        <v>-6.44</v>
       </c>
       <c r="N200" s="3">
         <v>0.71</v>
@@ -12199,9 +12796,12 @@
         <v>151.36</v>
       </c>
       <c r="R200" s="3">
-        <v>0.71</v>
-      </c>
-      <c r="S200" t="str">
+        <v>140.26</v>
+      </c>
+      <c r="S200" s="3">
+        <v>41.94</v>
+      </c>
+      <c r="T200" t="str">
         <v/>
       </c>
     </row>
@@ -12231,7 +12831,7 @@
         <v>13.68</v>
       </c>
       <c r="I201" s="1">
-        <v>325061</v>
+        <v>325172</v>
       </c>
       <c r="J201" s="1">
         <v>1041.3</v>
@@ -12243,7 +12843,7 @@
         <v>1141.02</v>
       </c>
       <c r="M201" s="3">
-        <v>9.86</v>
+        <v>-30.01</v>
       </c>
       <c r="N201" s="3">
         <v>-28.5</v>
@@ -12258,9 +12858,12 @@
         <v>134.23</v>
       </c>
       <c r="R201" s="3">
-        <v>-28.5</v>
-      </c>
-      <c r="S201" t="str">
+        <v>130.78</v>
+      </c>
+      <c r="S201" s="3">
+        <v>32.5</v>
+      </c>
+      <c r="T201" t="str">
         <v/>
       </c>
     </row>
@@ -12290,7 +12893,7 @@
         <v>0.13</v>
       </c>
       <c r="I202" s="1">
-        <v>431657</v>
+        <v>431830</v>
       </c>
       <c r="J202" s="1">
         <v>5014.8</v>
@@ -12302,7 +12905,7 @@
         <v>5024.87</v>
       </c>
       <c r="M202" s="3">
-        <v>-104.31</v>
+        <v>-127.34</v>
       </c>
       <c r="N202" s="3">
         <v>-102.61</v>
@@ -12317,9 +12920,12 @@
         <v>559.28</v>
       </c>
       <c r="R202" s="3">
-        <v>-102.61</v>
-      </c>
-      <c r="S202" t="str">
+        <v>614.02</v>
+      </c>
+      <c r="S202" s="3">
+        <v>26.24</v>
+      </c>
+      <c r="T202" t="str">
         <v/>
       </c>
     </row>
@@ -12349,7 +12955,7 @@
         <v>-17.9</v>
       </c>
       <c r="I203" s="1">
-        <v>54065</v>
+        <v>54096</v>
       </c>
       <c r="J203" s="1">
         <v>19510.96</v>
@@ -12361,7 +12967,7 @@
         <v>17532.08</v>
       </c>
       <c r="M203" s="3">
-        <v>-598.96</v>
+        <v>-50.64</v>
       </c>
       <c r="N203" s="3">
         <v>-111.43</v>
@@ -12376,9 +12982,12 @@
         <v>2452.76</v>
       </c>
       <c r="R203" s="3">
-        <v>-111.43</v>
-      </c>
-      <c r="S203" t="str">
+        <v>3159.19</v>
+      </c>
+      <c r="S203" s="3">
+        <v>43.61</v>
+      </c>
+      <c r="T203" t="str">
         <v/>
       </c>
     </row>
@@ -12408,7 +13017,7 @@
         <v>26.72</v>
       </c>
       <c r="I204" s="1">
-        <v>2527726</v>
+        <v>2529772</v>
       </c>
       <c r="J204" s="1">
         <v>804.78</v>
@@ -12420,7 +13029,7 @@
         <v>879.92</v>
       </c>
       <c r="M204" s="3">
-        <v>12.83</v>
+        <v>-12.82</v>
       </c>
       <c r="N204" s="3">
         <v>-8.4</v>
@@ -12435,9 +13044,12 @@
         <v>81.22</v>
       </c>
       <c r="R204" s="3">
-        <v>-8.4</v>
-      </c>
-      <c r="S204" t="str">
+        <v>77.11</v>
+      </c>
+      <c r="S204" s="3">
+        <v>40.1</v>
+      </c>
+      <c r="T204" t="str">
         <v/>
       </c>
     </row>
@@ -12467,7 +13079,7 @@
         <v>42.7</v>
       </c>
       <c r="I205" s="1">
-        <v>12820249</v>
+        <v>12823785</v>
       </c>
       <c r="J205" s="1">
         <v>355.62</v>
@@ -12479,7 +13091,7 @@
         <v>426.07</v>
       </c>
       <c r="M205" s="3">
-        <v>22.74</v>
+        <v>1.74</v>
       </c>
       <c r="N205" s="3">
         <v>3.75</v>
@@ -12494,9 +13106,12 @@
         <v>56.04</v>
       </c>
       <c r="R205" s="3">
-        <v>3.75</v>
-      </c>
-      <c r="S205" t="str">
+        <v>44.57</v>
+      </c>
+      <c r="S205" s="3">
+        <v>42.17</v>
+      </c>
+      <c r="T205" t="str">
         <v/>
       </c>
     </row>
@@ -12526,7 +13141,7 @@
         <v>14.08</v>
       </c>
       <c r="I206" s="1">
-        <v>17344650</v>
+        <v>17358378</v>
       </c>
       <c r="J206" s="1">
         <v>61.01</v>
@@ -12538,7 +13153,7 @@
         <v>66.4</v>
       </c>
       <c r="M206" s="3">
-        <v>1.24</v>
+        <v>-0.88</v>
       </c>
       <c r="N206" s="3">
         <v>-0.7</v>
@@ -12553,9 +13168,12 @@
         <v>6.13</v>
       </c>
       <c r="R206" s="3">
-        <v>-0.7</v>
-      </c>
-      <c r="S206" t="str">
+        <v>5.16</v>
+      </c>
+      <c r="S206" s="3">
+        <v>38.32</v>
+      </c>
+      <c r="T206" t="str">
         <v/>
       </c>
     </row>
@@ -12585,7 +13203,7 @@
         <v>13.62</v>
       </c>
       <c r="I207" s="1">
-        <v>5339172</v>
+        <v>5340711</v>
       </c>
       <c r="J207" s="1">
         <v>348.41</v>
@@ -12597,7 +13215,7 @@
         <v>398.29</v>
       </c>
       <c r="M207" s="3">
-        <v>15.53</v>
+        <v>-7.82</v>
       </c>
       <c r="N207" s="3">
         <v>-1.89</v>
@@ -12612,9 +13230,12 @@
         <v>42.31</v>
       </c>
       <c r="R207" s="3">
-        <v>-1.89</v>
-      </c>
-      <c r="S207" t="str">
+        <v>35.78</v>
+      </c>
+      <c r="S207" s="3">
+        <v>31.97</v>
+      </c>
+      <c r="T207" t="str">
         <v/>
       </c>
     </row>
@@ -12644,7 +13265,7 @@
         <v>-34</v>
       </c>
       <c r="I208" s="1">
-        <v>53940673</v>
+        <v>53949754</v>
       </c>
       <c r="J208" s="1">
         <v>114.58</v>
@@ -12656,7 +13277,7 @@
         <v>103.11</v>
       </c>
       <c r="M208" s="3">
-        <v>-6.34</v>
+        <v>-2.89</v>
       </c>
       <c r="N208" s="3">
         <v>-2.32</v>
@@ -12671,9 +13292,12 @@
         <v>-3.28</v>
       </c>
       <c r="R208" s="3">
-        <v>-2.32</v>
-      </c>
-      <c r="S208" t="str">
+        <v>1.26</v>
+      </c>
+      <c r="S208" s="3">
+        <v>28.09</v>
+      </c>
+      <c r="T208" t="str">
         <v/>
       </c>
     </row>
@@ -12703,7 +13327,7 @@
         <v>-5.15</v>
       </c>
       <c r="I209" s="1">
-        <v>253000</v>
+        <v>253029</v>
       </c>
       <c r="J209" s="1">
         <v>4840.76</v>
@@ -12715,7 +13339,7 @@
         <v>4972.15</v>
       </c>
       <c r="M209" s="3">
-        <v>-101.62</v>
+        <v>-117.48</v>
       </c>
       <c r="N209" s="3">
         <v>-113.93</v>
@@ -12730,9 +13354,12 @@
         <v>403.76</v>
       </c>
       <c r="R209" s="3">
-        <v>-113.93</v>
-      </c>
-      <c r="S209" t="str">
+        <v>444.12</v>
+      </c>
+      <c r="S209" s="3">
+        <v>30.41</v>
+      </c>
+      <c r="T209" t="str">
         <v/>
       </c>
     </row>
@@ -12762,7 +13389,7 @@
         <v>-27.96</v>
       </c>
       <c r="I210" s="1">
-        <v>1537151</v>
+        <v>1537662</v>
       </c>
       <c r="J210" s="1">
         <v>1468.46</v>
@@ -12774,7 +13401,7 @@
         <v>1398.88</v>
       </c>
       <c r="M210" s="3">
-        <v>-73.04</v>
+        <v>-53.03</v>
       </c>
       <c r="N210" s="3">
         <v>-50.37</v>
@@ -12789,9 +13416,12 @@
         <v>9.95</v>
       </c>
       <c r="R210" s="3">
-        <v>-50.37</v>
-      </c>
-      <c r="S210" t="str">
+        <v>87.89</v>
+      </c>
+      <c r="S210" s="3">
+        <v>28.02</v>
+      </c>
+      <c r="T210" t="str">
         <v/>
       </c>
     </row>
@@ -12821,7 +13451,7 @@
         <v>-10.21</v>
       </c>
       <c r="I211" s="1">
-        <v>890123</v>
+        <v>890128</v>
       </c>
       <c r="J211" s="1">
         <v>1370.04</v>
@@ -12833,7 +13463,7 @@
         <v>1436.87</v>
       </c>
       <c r="M211" s="3">
-        <v>-1.1</v>
+        <v>-21.69</v>
       </c>
       <c r="N211" s="3">
         <v>-22.2</v>
@@ -12848,9 +13478,12 @@
         <v>29.63</v>
       </c>
       <c r="R211" s="3">
-        <v>-22.2</v>
-      </c>
-      <c r="S211" t="str">
+        <v>46.65</v>
+      </c>
+      <c r="S211" s="3">
+        <v>33.78</v>
+      </c>
+      <c r="T211" t="str">
         <v/>
       </c>
     </row>
@@ -12880,7 +13513,7 @@
         <v>8.18</v>
       </c>
       <c r="I212" s="1">
-        <v>521484788</v>
+        <v>521826051</v>
       </c>
       <c r="J212" s="1">
         <v>12.3</v>
@@ -12892,7 +13525,7 @@
         <v>13.84</v>
       </c>
       <c r="M212" s="3">
-        <v>0.23</v>
+        <v>-0.51</v>
       </c>
       <c r="N212" s="3">
         <v>-0.41</v>
@@ -12907,9 +13540,12 @@
         <v>0.82</v>
       </c>
       <c r="R212" s="3">
-        <v>-0.41</v>
-      </c>
-      <c r="S212" t="str">
+        <v>0.42</v>
+      </c>
+      <c r="S212" s="3">
+        <v>28.86</v>
+      </c>
+      <c r="T212" t="str">
         <v/>
       </c>
     </row>
@@ -12939,7 +13575,7 @@
         <v>-25.04</v>
       </c>
       <c r="I213" s="1">
-        <v>708171</v>
+        <v>708898</v>
       </c>
       <c r="J213" s="1">
         <v>2659.05</v>
@@ -12951,7 +13587,7 @@
         <v>2530.42</v>
       </c>
       <c r="M213" s="3">
-        <v>-73.97</v>
+        <v>-32.67</v>
       </c>
       <c r="N213" s="3">
         <v>-23.21</v>
@@ -12966,9 +13602,12 @@
         <v>-23.49</v>
       </c>
       <c r="R213" s="3">
-        <v>-23.21</v>
-      </c>
-      <c r="S213" t="str">
+        <v>43.89</v>
+      </c>
+      <c r="S213" s="3">
+        <v>26.83</v>
+      </c>
+      <c r="T213" t="str">
         <v/>
       </c>
     </row>
@@ -12998,7 +13637,7 @@
         <v>11.66</v>
       </c>
       <c r="I214" s="1">
-        <v>480216</v>
+        <v>480246</v>
       </c>
       <c r="J214" s="1">
         <v>3536.73</v>
@@ -13010,7 +13649,7 @@
         <v>3867.39</v>
       </c>
       <c r="M214" s="3">
-        <v>39.22</v>
+        <v>-79.14</v>
       </c>
       <c r="N214" s="3">
         <v>-58.54</v>
@@ -13025,9 +13664,12 @@
         <v>180.88</v>
       </c>
       <c r="R214" s="3">
-        <v>-58.54</v>
-      </c>
-      <c r="S214" t="str">
+        <v>175.77</v>
+      </c>
+      <c r="S214" s="3">
+        <v>32.38</v>
+      </c>
+      <c r="T214" t="str">
         <v/>
       </c>
     </row>
@@ -13057,7 +13699,7 @@
         <v>-2.25</v>
       </c>
       <c r="I215" s="1">
-        <v>6828702</v>
+        <v>6829571</v>
       </c>
       <c r="J215" s="1">
         <v>311.05</v>
@@ -13069,7 +13711,7 @@
         <v>331.5</v>
       </c>
       <c r="M215" s="3">
-        <v>2.82</v>
+        <v>-3.63</v>
       </c>
       <c r="N215" s="3">
         <v>-4.29</v>
@@ -13084,9 +13726,12 @@
         <v>33.67</v>
       </c>
       <c r="R215" s="3">
-        <v>-4.29</v>
-      </c>
-      <c r="S215" t="str">
+        <v>33.97</v>
+      </c>
+      <c r="S215" s="3">
+        <v>36.44</v>
+      </c>
+      <c r="T215" t="str">
         <v/>
       </c>
     </row>
@@ -13116,7 +13761,7 @@
         <v>26.88</v>
       </c>
       <c r="I216" s="1">
-        <v>651552</v>
+        <v>651592</v>
       </c>
       <c r="J216" s="1">
         <v>6652.72</v>
@@ -13128,7 +13773,7 @@
         <v>7234.01</v>
       </c>
       <c r="M216" s="3">
-        <v>66.84</v>
+        <v>-118.13</v>
       </c>
       <c r="N216" s="3">
         <v>-114.03</v>
@@ -13143,15 +13788,18 @@
         <v>409.75</v>
       </c>
       <c r="R216" s="3">
-        <v>-114.03</v>
-      </c>
-      <c r="S216" t="str">
+        <v>352.78</v>
+      </c>
+      <c r="S216" s="3">
+        <v>36.75</v>
+      </c>
+      <c r="T216" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S216"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T216"/>
   </ignoredErrors>
 </worksheet>
 </file>